--- a/Java Full Stack_ToC.xlsx
+++ b/Java Full Stack_ToC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RPS\premila\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\harman_training\Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A3D677-A274-48D2-A5CA-8D809F1D1B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3585DAB-E3FD-44F4-8FF8-2F556ED3F283}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{650FC967-2F93-46CA-B378-157C068E930D}"/>
+    <workbookView xWindow="3528" yWindow="1584" windowWidth="19512" windowHeight="10920" activeTab="2" xr2:uid="{650FC967-2F93-46CA-B378-157C068E930D}"/>
   </bookViews>
   <sheets>
     <sheet name="Course Outline" sheetId="5" r:id="rId1"/>
@@ -1723,20 +1723,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1744,17 +1738,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1765,8 +1759,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1777,8 +1777,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1788,6 +1797,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1801,11 +1816,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1816,26 +1834,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1855,9 +1855,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1895,7 +1895,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2001,7 +2001,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2143,7 +2143,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2152,29 +2152,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75EAAB05-1FFA-4AD2-8E44-B12AF1268528}">
   <dimension ref="B1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="26.7265625" customWidth="1"/>
-    <col min="5" max="5" width="61.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="61.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="2:5">
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="8" t="s">
         <v>165</v>
       </c>
@@ -2183,10 +2183,10 @@
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="18"/>
+      <c r="D3" s="15"/>
       <c r="E3" s="7" t="s">
         <v>177</v>
       </c>
@@ -2195,10 +2195,10 @@
       <c r="B4" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="18"/>
+      <c r="D4" s="15"/>
       <c r="E4" s="7" t="s">
         <v>167</v>
       </c>
@@ -2207,10 +2207,10 @@
       <c r="B5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="18"/>
+      <c r="D5" s="15"/>
       <c r="E5" s="7" t="s">
         <v>172</v>
       </c>
@@ -2219,65 +2219,65 @@
       <c r="B6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="18"/>
+      <c r="D6" s="15"/>
       <c r="E6" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="7" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="13" t="s">
@@ -2286,12 +2286,12 @@
       <c r="C19" s="13"/>
     </row>
     <row r="20" spans="2:5" ht="36" customHeight="1">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="13" t="s">
@@ -2330,12 +2330,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:D10"/>
@@ -2343,6 +2337,12 @@
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B14:E14"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2351,21 +2351,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5541A705-CAAD-4F33-B7C5-B23C70362015}">
   <dimension ref="A1:G79"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -2374,894 +2374,945 @@
       <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="16" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="16" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="16" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="16" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="23"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="23"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="23"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="23"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="16" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="23"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="16" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="23"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="16" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="23"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="23"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="23"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="23"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="16" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="23"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="23"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="23"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="23"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="23"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="23"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="23"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="26"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="23"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="16" t="s">
+      <c r="A29" s="26"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="23"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="16" t="s">
+      <c r="A30" s="26"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="16" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="16" t="s">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="17" t="s">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="18"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="16" t="s">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="16" t="s">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="16" t="s">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="16" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="16" t="s">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="16" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="16" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="16" t="s">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="16" t="s">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="16" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="16" t="s">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="16" t="s">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="21"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="16" t="s">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="16" t="s">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="17" t="s">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="18"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="17" t="s">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="18"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="16" t="s">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="16" t="s">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="16" t="s">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="16" t="s">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="16" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="16" t="s">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="16" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="16" t="s">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="16" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="16" t="s">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="16" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="16" t="s">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="21"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="16" t="s">
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="21"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="16" t="s">
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="21"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="16" t="s">
+      <c r="A67" s="22"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="16" t="s">
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="16" t="s">
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="16" t="s">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="16" t="s">
+      <c r="A71" s="22"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="16" t="s">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
-      <c r="C73" s="16" t="s">
+      <c r="A73" s="22"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21"/>
-      <c r="C74" s="16" t="s">
+      <c r="A74" s="22"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="16" t="s">
+      <c r="A75" s="22"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="16" t="s">
+      <c r="A76" s="22"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="16" t="s">
+      <c r="A77" s="22"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="21"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="16" t="s">
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="A66:A78"/>
+    <mergeCell ref="B66:B78"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="A52:A65"/>
+    <mergeCell ref="B52:B65"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="A31:A51"/>
+    <mergeCell ref="B31:B51"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="A11:A30"/>
     <mergeCell ref="B11:B30"/>
@@ -3278,68 +3329,17 @@
     <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="A52:A65"/>
-    <mergeCell ref="B52:B65"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="A31:A51"/>
-    <mergeCell ref="B31:B51"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="A66:A78"/>
-    <mergeCell ref="B66:B78"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3348,22 +3348,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144CF55E-ADAB-4A5A-B994-3C7076E84FC8}">
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.90625" customWidth="1"/>
-    <col min="7" max="7" width="29.26953125" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="7" max="7" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -3372,613 +3372,659 @@
       <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="16" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="16" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="16" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="16" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="16" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="21"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="21"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="21"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="21"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="22"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="21"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="16" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="21"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="16" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="21"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="16" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="21"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="22"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="21"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="21"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="21"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="21"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="21"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="21"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="21"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="22"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="21"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="22"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="21"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="21"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="16" t="s">
+      <c r="A29" s="22"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="21"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="16" t="s">
+      <c r="A30" s="22"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="21"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="16" t="s">
+      <c r="A31" s="22"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="21"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="16" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="21"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="16" t="s">
+      <c r="A33" s="22"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="21"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="16" t="s">
+      <c r="A34" s="22"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="21"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="16" t="s">
+      <c r="A35" s="22"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="22" t="s">
         <v>307</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="21"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="30"/>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="21"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="30"/>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="21"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="30"/>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="21"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="30"/>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="21"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="30"/>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="21"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="30"/>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="21"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="30"/>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="21"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="30"/>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="21"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="30"/>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="21"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="30"/>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="21"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="30"/>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="22" t="s">
         <v>321</v>
       </c>
       <c r="B48" s="30"/>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="21"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="30"/>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="21"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="30"/>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="21"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="30"/>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="21"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="30"/>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="21"/>
+      <c r="A53" s="22"/>
       <c r="B53" s="30"/>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="21"/>
+      <c r="A54" s="22"/>
       <c r="B54" s="31"/>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="A36:A47"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="B21:B35"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C16:G16"/>
     <mergeCell ref="A3:A20"/>
@@ -3995,52 +4041,6 @@
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="B21:B35"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="A36:A47"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4049,9 +4049,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3896E95E-BF9B-4333-B454-9FC8DC276F25}">
   <dimension ref="A1:H160"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="7" max="7" width="81.90625" customWidth="1"/>
+    <col min="7" max="7" width="81.88671875" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4059,14 +4059,14 @@
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4075,159 +4075,159 @@
       <c r="A2" s="29">
         <v>10</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="21" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="22" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="30"/>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="21"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="30"/>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="21"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="22"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="30"/>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="21"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="30"/>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="21"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="30"/>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="30"/>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="21"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="30"/>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="21"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="30"/>
       <c r="B10" t="s">
         <v>338</v>
       </c>
-      <c r="H10" s="21"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="30"/>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="21"/>
-    </row>
-    <row r="12" spans="1:8" ht="14.5" customHeight="1">
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="22"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.55" customHeight="1">
       <c r="A12" s="30"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="46" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="39" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="31"/>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="48"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="40"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="29">
         <v>11</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="35"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="29" t="s">
         <v>140</v>
       </c>
@@ -4246,190 +4246,190 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="30"/>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="35"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="30"/>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="30"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="30"/>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="30"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="30"/>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="35"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="38"/>
       <c r="H19" s="30"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="30"/>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
       <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="30"/>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="35"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="38"/>
       <c r="H21" s="30"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="30"/>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
       <c r="H22" s="30"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="30"/>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="35"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="38"/>
       <c r="H23" s="30"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="30"/>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="38"/>
       <c r="H24" s="30"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="30"/>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="35"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="38"/>
       <c r="H25" s="30"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="30"/>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="31"/>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="35"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="38"/>
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="36">
+      <c r="A28" s="41">
         <v>12</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="36" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="41" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="37"/>
-      <c r="B29" s="33" t="s">
+      <c r="A29" s="42"/>
+      <c r="B29" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="42"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="37"/>
-      <c r="B30" s="33" t="s">
+      <c r="A30" s="42"/>
+      <c r="B30" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="42"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="37"/>
+      <c r="A31" s="42"/>
       <c r="B31" s="4" t="s">
         <v>40</v>
       </c>
@@ -4438,70 +4438,70 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="37"/>
+      <c r="H31" s="42"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="37"/>
-      <c r="B32" s="33" t="s">
+      <c r="A32" s="42"/>
+      <c r="B32" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="42"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="37"/>
-      <c r="B33" s="33" t="s">
+      <c r="A33" s="42"/>
+      <c r="B33" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="42"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="37"/>
-      <c r="B34" s="33" t="s">
+      <c r="A34" s="42"/>
+      <c r="B34" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="42"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="37"/>
-      <c r="B35" s="33" t="s">
+      <c r="A35" s="42"/>
+      <c r="B35" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="42"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="37"/>
-      <c r="B36" s="33" t="s">
+      <c r="A36" s="42"/>
+      <c r="B36" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="42"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="37"/>
+      <c r="A37" s="42"/>
       <c r="B37" s="10" t="s">
         <v>344</v>
       </c>
@@ -4510,755 +4510,755 @@
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="12"/>
-      <c r="H37" s="37"/>
+      <c r="H37" s="42"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="37"/>
-      <c r="B38" s="33" t="s">
+      <c r="A38" s="42"/>
+      <c r="B38" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="42"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="37"/>
-      <c r="B39" s="33" t="s">
+      <c r="A39" s="42"/>
+      <c r="B39" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="42"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="37"/>
-      <c r="B40" s="33" t="s">
+      <c r="A40" s="42"/>
+      <c r="B40" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="42"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="38"/>
-      <c r="B41" s="33" t="s">
+      <c r="A41" s="43"/>
+      <c r="B41" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="38"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="43"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="36">
+      <c r="A42" s="41">
         <v>13</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="36" t="s">
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="41" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="37"/>
-      <c r="B43" s="33" t="s">
+      <c r="A43" s="42"/>
+      <c r="B43" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="42"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="37"/>
-      <c r="B44" s="33" t="s">
+      <c r="A44" s="42"/>
+      <c r="B44" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="42"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="37"/>
-      <c r="B45" s="33" t="s">
+      <c r="A45" s="42"/>
+      <c r="B45" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="42"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="37"/>
-      <c r="B46" s="33" t="s">
+      <c r="A46" s="42"/>
+      <c r="B46" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="42"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="37"/>
-      <c r="B47" s="33" t="s">
+      <c r="A47" s="42"/>
+      <c r="B47" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="42"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="37"/>
-      <c r="B48" s="33" t="s">
+      <c r="A48" s="42"/>
+      <c r="B48" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="42"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="37"/>
-      <c r="B49" s="33" t="s">
+      <c r="A49" s="42"/>
+      <c r="B49" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="42"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="37"/>
-      <c r="B50" s="33" t="s">
+      <c r="A50" s="42"/>
+      <c r="B50" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="42"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="37"/>
-      <c r="B51" s="33" t="s">
+      <c r="A51" s="42"/>
+      <c r="B51" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="42"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="37"/>
-      <c r="B52" s="33" t="s">
+      <c r="A52" s="42"/>
+      <c r="B52" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="42"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="37"/>
-      <c r="B53" s="33" t="s">
+      <c r="A53" s="42"/>
+      <c r="B53" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="37"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="42"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="37"/>
-      <c r="B54" s="33" t="s">
+      <c r="A54" s="42"/>
+      <c r="B54" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="42"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="37"/>
-      <c r="B55" s="33" t="s">
+      <c r="A55" s="42"/>
+      <c r="B55" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="37"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="42"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="37"/>
-      <c r="B56" s="33" t="s">
+      <c r="A56" s="42"/>
+      <c r="B56" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="38"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="43"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="37"/>
-      <c r="B57" s="33" t="s">
+      <c r="A57" s="42"/>
+      <c r="B57" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="36" t="s">
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="41" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="37"/>
-      <c r="B58" s="33" t="s">
+      <c r="A58" s="42"/>
+      <c r="B58" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="42"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="37"/>
-      <c r="B59" s="33" t="s">
+      <c r="A59" s="42"/>
+      <c r="B59" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="42"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="37"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="42"/>
+      <c r="B60" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="37"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="42"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="37"/>
-      <c r="B61" s="33" t="s">
+      <c r="A61" s="42"/>
+      <c r="B61" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="37"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="42"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="37"/>
-      <c r="B62" s="33" t="s">
+      <c r="A62" s="42"/>
+      <c r="B62" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="37"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="42"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="37"/>
-      <c r="B63" s="33" t="s">
+      <c r="A63" s="42"/>
+      <c r="B63" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="38"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="43"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="37">
+      <c r="A64" s="42">
         <v>14</v>
       </c>
-      <c r="B64" s="33" t="s">
+      <c r="B64" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="34"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="42" t="s">
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="48" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="37"/>
-      <c r="B65" s="33" t="s">
+      <c r="A65" s="42"/>
+      <c r="B65" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="34"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="43"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="49"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="37"/>
-      <c r="B66" s="33" t="s">
+      <c r="A66" s="42"/>
+      <c r="B66" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C66" s="34"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="43"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="49"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="37"/>
-      <c r="B67" s="33" t="s">
+      <c r="A67" s="42"/>
+      <c r="B67" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C67" s="34"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="43"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="49"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="37"/>
-      <c r="B68" s="33" t="s">
+      <c r="A68" s="42"/>
+      <c r="B68" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="34"/>
-      <c r="D68" s="34"/>
-      <c r="E68" s="34"/>
-      <c r="F68" s="34"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="43"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="49"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="37"/>
-      <c r="B69" s="33" t="s">
+      <c r="A69" s="42"/>
+      <c r="B69" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="43"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="49"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="37"/>
-      <c r="B70" s="33" t="s">
+      <c r="A70" s="42"/>
+      <c r="B70" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="43"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="49"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="37"/>
-      <c r="B71" s="33" t="s">
+      <c r="A71" s="42"/>
+      <c r="B71" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="43"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="49"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="37"/>
-      <c r="B72" s="33" t="s">
+      <c r="A72" s="42"/>
+      <c r="B72" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="C72" s="34"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="43"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="49"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="37"/>
-      <c r="B73" s="33" t="s">
+      <c r="A73" s="42"/>
+      <c r="B73" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="34"/>
-      <c r="F73" s="34"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="43"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="49"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="37"/>
-      <c r="B74" s="33" t="s">
+      <c r="A74" s="42"/>
+      <c r="B74" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="C74" s="34"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="34"/>
-      <c r="F74" s="34"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="43"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="49"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="37"/>
-      <c r="B75" s="33" t="s">
+      <c r="A75" s="42"/>
+      <c r="B75" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="34"/>
-      <c r="F75" s="34"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="44"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="50"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="37"/>
-      <c r="B76" s="33" t="s">
+      <c r="A76" s="42"/>
+      <c r="B76" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34"/>
-      <c r="E76" s="34"/>
-      <c r="F76" s="34"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="36" t="s">
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="41" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="37"/>
-      <c r="B77" s="33" t="s">
+      <c r="A77" s="42"/>
+      <c r="B77" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="34"/>
-      <c r="D77" s="34"/>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="42"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="37"/>
-      <c r="B78" s="33" t="s">
+      <c r="A78" s="42"/>
+      <c r="B78" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="34"/>
-      <c r="D78" s="34"/>
-      <c r="E78" s="34"/>
-      <c r="F78" s="34"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="42"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="37"/>
-      <c r="B79" s="33" t="s">
+      <c r="A79" s="42"/>
+      <c r="B79" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="34"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="34"/>
-      <c r="F79" s="34"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="42"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="37"/>
-      <c r="B80" s="33" t="s">
+      <c r="A80" s="42"/>
+      <c r="B80" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="34"/>
-      <c r="F80" s="34"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="42"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="37"/>
+      <c r="A81" s="42"/>
       <c r="B81" t="s">
         <v>341</v>
       </c>
-      <c r="H81" s="37"/>
+      <c r="H81" s="42"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="38"/>
-      <c r="B82" s="33" t="s">
+      <c r="A82" s="43"/>
+      <c r="B82" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="34"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="38"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="43"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="49">
+      <c r="A83" s="33">
         <v>15</v>
       </c>
-      <c r="B83" s="40" t="s">
+      <c r="B83" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="40"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="21" t="s">
+      <c r="C83" s="51"/>
+      <c r="D83" s="51"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="51"/>
+      <c r="G83" s="51"/>
+      <c r="H83" s="22" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="50"/>
-      <c r="B84" s="40" t="s">
+      <c r="A84" s="34"/>
+      <c r="B84" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="40"/>
-      <c r="D84" s="40"/>
-      <c r="E84" s="40"/>
-      <c r="F84" s="40"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="21"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="22"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="50"/>
-      <c r="B85" s="40" t="s">
+      <c r="A85" s="34"/>
+      <c r="B85" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="C85" s="40"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="21"/>
+      <c r="C85" s="51"/>
+      <c r="D85" s="51"/>
+      <c r="E85" s="51"/>
+      <c r="F85" s="51"/>
+      <c r="G85" s="51"/>
+      <c r="H85" s="22"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="50"/>
-      <c r="B86" s="40" t="s">
+      <c r="A86" s="34"/>
+      <c r="B86" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="40"/>
-      <c r="D86" s="40"/>
-      <c r="E86" s="40"/>
-      <c r="F86" s="40"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="21"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="22"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="50"/>
-      <c r="B87" s="40" t="s">
+      <c r="A87" s="34"/>
+      <c r="B87" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="C87" s="40"/>
-      <c r="D87" s="40"/>
-      <c r="E87" s="40"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="21"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="22"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="50"/>
-      <c r="B88" s="40" t="s">
+      <c r="A88" s="34"/>
+      <c r="B88" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="40"/>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="21"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="22"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="50"/>
-      <c r="B89" s="33" t="s">
+      <c r="A89" s="34"/>
+      <c r="B89" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="34"/>
-      <c r="D89" s="34"/>
-      <c r="E89" s="34"/>
-      <c r="F89" s="34"/>
-      <c r="G89" s="35"/>
-      <c r="H89" s="46" t="s">
+      <c r="C89" s="37"/>
+      <c r="D89" s="37"/>
+      <c r="E89" s="37"/>
+      <c r="F89" s="37"/>
+      <c r="G89" s="38"/>
+      <c r="H89" s="39" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="50"/>
-      <c r="B90" s="33" t="s">
+      <c r="A90" s="34"/>
+      <c r="B90" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C90" s="34"/>
-      <c r="D90" s="34"/>
-      <c r="E90" s="34"/>
-      <c r="F90" s="34"/>
-      <c r="G90" s="35"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="37"/>
+      <c r="E90" s="37"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="38"/>
       <c r="H90" s="47"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="50"/>
-      <c r="B91" s="33" t="s">
+      <c r="A91" s="34"/>
+      <c r="B91" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="34"/>
-      <c r="D91" s="34"/>
-      <c r="E91" s="34"/>
-      <c r="F91" s="34"/>
-      <c r="G91" s="35"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="38"/>
       <c r="H91" s="47"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="50"/>
-      <c r="B92" s="33" t="s">
+      <c r="A92" s="34"/>
+      <c r="B92" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="34"/>
-      <c r="D92" s="34"/>
-      <c r="E92" s="34"/>
-      <c r="F92" s="34"/>
-      <c r="G92" s="35"/>
+      <c r="C92" s="37"/>
+      <c r="D92" s="37"/>
+      <c r="E92" s="37"/>
+      <c r="F92" s="37"/>
+      <c r="G92" s="38"/>
       <c r="H92" s="47"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="50"/>
-      <c r="B93" s="33" t="s">
+      <c r="A93" s="34"/>
+      <c r="B93" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="34"/>
-      <c r="D93" s="34"/>
-      <c r="E93" s="34"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="35"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="37"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="38"/>
       <c r="H93" s="47"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="50"/>
-      <c r="B94" s="33" t="s">
+      <c r="A94" s="34"/>
+      <c r="B94" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C94" s="34"/>
-      <c r="D94" s="34"/>
-      <c r="E94" s="34"/>
-      <c r="F94" s="34"/>
-      <c r="G94" s="35"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="37"/>
+      <c r="F94" s="37"/>
+      <c r="G94" s="38"/>
       <c r="H94" s="47"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="50"/>
-      <c r="B95" s="33" t="s">
+      <c r="A95" s="34"/>
+      <c r="B95" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="34"/>
-      <c r="D95" s="34"/>
-      <c r="E95" s="34"/>
-      <c r="F95" s="34"/>
-      <c r="G95" s="35"/>
+      <c r="C95" s="37"/>
+      <c r="D95" s="37"/>
+      <c r="E95" s="37"/>
+      <c r="F95" s="37"/>
+      <c r="G95" s="38"/>
       <c r="H95" s="47"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="50"/>
-      <c r="B96" s="33" t="s">
+      <c r="A96" s="34"/>
+      <c r="B96" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="34"/>
-      <c r="D96" s="34"/>
-      <c r="E96" s="34"/>
-      <c r="F96" s="34"/>
-      <c r="G96" s="35"/>
+      <c r="C96" s="37"/>
+      <c r="D96" s="37"/>
+      <c r="E96" s="37"/>
+      <c r="F96" s="37"/>
+      <c r="G96" s="38"/>
       <c r="H96" s="47"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="50"/>
-      <c r="B97" s="33" t="s">
+      <c r="A97" s="34"/>
+      <c r="B97" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="34"/>
-      <c r="D97" s="34"/>
-      <c r="E97" s="34"/>
-      <c r="F97" s="34"/>
-      <c r="G97" s="35"/>
+      <c r="C97" s="37"/>
+      <c r="D97" s="37"/>
+      <c r="E97" s="37"/>
+      <c r="F97" s="37"/>
+      <c r="G97" s="38"/>
       <c r="H97" s="47"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="50"/>
-      <c r="B98" s="33" t="s">
+      <c r="A98" s="34"/>
+      <c r="B98" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C98" s="34"/>
-      <c r="D98" s="34"/>
-      <c r="E98" s="34"/>
-      <c r="F98" s="34"/>
-      <c r="G98" s="35"/>
+      <c r="C98" s="37"/>
+      <c r="D98" s="37"/>
+      <c r="E98" s="37"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="38"/>
       <c r="H98" s="47"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="50"/>
+      <c r="A99" s="34"/>
       <c r="B99" s="2" t="s">
         <v>100</v>
       </c>
@@ -5267,830 +5267,831 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-      <c r="H99" s="48"/>
+      <c r="H99" s="40"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="50">
+      <c r="A100" s="34">
         <v>16</v>
       </c>
-      <c r="B100" s="39" t="s">
+      <c r="B100" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C100" s="39"/>
-      <c r="D100" s="39"/>
-      <c r="E100" s="39"/>
-      <c r="F100" s="39"/>
-      <c r="G100" s="39"/>
-      <c r="H100" s="21" t="s">
+      <c r="C100" s="44"/>
+      <c r="D100" s="44"/>
+      <c r="E100" s="44"/>
+      <c r="F100" s="44"/>
+      <c r="G100" s="44"/>
+      <c r="H100" s="22" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="50"/>
-      <c r="B101" s="39" t="s">
+      <c r="A101" s="34"/>
+      <c r="B101" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="C101" s="39"/>
-      <c r="D101" s="39"/>
-      <c r="E101" s="39"/>
-      <c r="F101" s="39"/>
-      <c r="G101" s="39"/>
-      <c r="H101" s="21"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="44"/>
+      <c r="F101" s="44"/>
+      <c r="G101" s="44"/>
+      <c r="H101" s="22"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="50"/>
-      <c r="B102" s="39" t="s">
+      <c r="A102" s="34"/>
+      <c r="B102" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C102" s="39"/>
-      <c r="D102" s="39"/>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39"/>
-      <c r="G102" s="39"/>
-      <c r="H102" s="21"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="44"/>
+      <c r="F102" s="44"/>
+      <c r="G102" s="44"/>
+      <c r="H102" s="22"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="50"/>
-      <c r="B103" s="39" t="s">
+      <c r="A103" s="34"/>
+      <c r="B103" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C103" s="39"/>
-      <c r="D103" s="39"/>
-      <c r="E103" s="39"/>
-      <c r="F103" s="39"/>
-      <c r="G103" s="39"/>
-      <c r="H103" s="21"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="44"/>
+      <c r="F103" s="44"/>
+      <c r="G103" s="44"/>
+      <c r="H103" s="22"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="50"/>
-      <c r="B104" s="39" t="s">
+      <c r="A104" s="34"/>
+      <c r="B104" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C104" s="39"/>
-      <c r="D104" s="39"/>
-      <c r="E104" s="39"/>
-      <c r="F104" s="39"/>
-      <c r="G104" s="39"/>
-      <c r="H104" s="21"/>
+      <c r="C104" s="44"/>
+      <c r="D104" s="44"/>
+      <c r="E104" s="44"/>
+      <c r="F104" s="44"/>
+      <c r="G104" s="44"/>
+      <c r="H104" s="22"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="50"/>
-      <c r="B105" s="39" t="s">
+      <c r="A105" s="34"/>
+      <c r="B105" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="C105" s="39"/>
-      <c r="D105" s="39"/>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39"/>
-      <c r="G105" s="39"/>
-      <c r="H105" s="21"/>
+      <c r="C105" s="44"/>
+      <c r="D105" s="44"/>
+      <c r="E105" s="44"/>
+      <c r="F105" s="44"/>
+      <c r="G105" s="44"/>
+      <c r="H105" s="22"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="50"/>
-      <c r="B106" s="39" t="s">
+      <c r="A106" s="34"/>
+      <c r="B106" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="C106" s="39"/>
-      <c r="D106" s="39"/>
-      <c r="E106" s="39"/>
-      <c r="F106" s="39"/>
-      <c r="G106" s="39"/>
-      <c r="H106" s="21"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="44"/>
+      <c r="E106" s="44"/>
+      <c r="F106" s="44"/>
+      <c r="G106" s="44"/>
+      <c r="H106" s="22"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="50"/>
-      <c r="B107" s="39" t="s">
+      <c r="A107" s="34"/>
+      <c r="B107" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="C107" s="39"/>
-      <c r="D107" s="39"/>
-      <c r="E107" s="39"/>
-      <c r="F107" s="39"/>
-      <c r="G107" s="39"/>
-      <c r="H107" s="21"/>
+      <c r="C107" s="44"/>
+      <c r="D107" s="44"/>
+      <c r="E107" s="44"/>
+      <c r="F107" s="44"/>
+      <c r="G107" s="44"/>
+      <c r="H107" s="22"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="50"/>
-      <c r="B108" s="39" t="s">
+      <c r="A108" s="34"/>
+      <c r="B108" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="C108" s="39"/>
-      <c r="D108" s="39"/>
-      <c r="E108" s="39"/>
-      <c r="F108" s="39"/>
-      <c r="G108" s="39"/>
-      <c r="H108" s="21"/>
+      <c r="C108" s="44"/>
+      <c r="D108" s="44"/>
+      <c r="E108" s="44"/>
+      <c r="F108" s="44"/>
+      <c r="G108" s="44"/>
+      <c r="H108" s="22"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="50"/>
-      <c r="B109" s="39" t="s">
+      <c r="A109" s="34"/>
+      <c r="B109" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="C109" s="39"/>
-      <c r="D109" s="39"/>
-      <c r="E109" s="39"/>
-      <c r="F109" s="39"/>
-      <c r="G109" s="39"/>
-      <c r="H109" s="21"/>
+      <c r="C109" s="44"/>
+      <c r="D109" s="44"/>
+      <c r="E109" s="44"/>
+      <c r="F109" s="44"/>
+      <c r="G109" s="44"/>
+      <c r="H109" s="22"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="50"/>
-      <c r="B110" s="39" t="s">
+      <c r="A110" s="34"/>
+      <c r="B110" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C110" s="39"/>
-      <c r="D110" s="39"/>
-      <c r="E110" s="39"/>
-      <c r="F110" s="39"/>
-      <c r="G110" s="39"/>
-      <c r="H110" s="21"/>
+      <c r="C110" s="44"/>
+      <c r="D110" s="44"/>
+      <c r="E110" s="44"/>
+      <c r="F110" s="44"/>
+      <c r="G110" s="44"/>
+      <c r="H110" s="22"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="50"/>
-      <c r="B111" s="39" t="s">
+      <c r="A111" s="34"/>
+      <c r="B111" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="C111" s="39"/>
-      <c r="D111" s="39"/>
-      <c r="E111" s="39"/>
-      <c r="F111" s="39"/>
-      <c r="G111" s="39"/>
-      <c r="H111" s="21"/>
+      <c r="C111" s="44"/>
+      <c r="D111" s="44"/>
+      <c r="E111" s="44"/>
+      <c r="F111" s="44"/>
+      <c r="G111" s="44"/>
+      <c r="H111" s="22"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="50"/>
-      <c r="B112" s="39" t="s">
+      <c r="A112" s="34"/>
+      <c r="B112" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="C112" s="39"/>
-      <c r="D112" s="39"/>
-      <c r="E112" s="39"/>
-      <c r="F112" s="39"/>
-      <c r="G112" s="39"/>
-      <c r="H112" s="21"/>
+      <c r="C112" s="44"/>
+      <c r="D112" s="44"/>
+      <c r="E112" s="44"/>
+      <c r="F112" s="44"/>
+      <c r="G112" s="44"/>
+      <c r="H112" s="22"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="50"/>
-      <c r="B113" s="41" t="s">
+      <c r="A113" s="34"/>
+      <c r="B113" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="41"/>
-      <c r="E113" s="41"/>
-      <c r="F113" s="41"/>
-      <c r="G113" s="41"/>
-      <c r="H113" s="21"/>
+      <c r="C113" s="45"/>
+      <c r="D113" s="45"/>
+      <c r="E113" s="45"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="45"/>
+      <c r="H113" s="22"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="50"/>
-      <c r="B114" s="39" t="s">
+      <c r="A114" s="34"/>
+      <c r="B114" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="C114" s="39"/>
-      <c r="D114" s="39"/>
-      <c r="E114" s="39"/>
-      <c r="F114" s="39"/>
-      <c r="G114" s="39"/>
-      <c r="H114" s="21"/>
+      <c r="C114" s="44"/>
+      <c r="D114" s="44"/>
+      <c r="E114" s="44"/>
+      <c r="F114" s="44"/>
+      <c r="G114" s="44"/>
+      <c r="H114" s="22"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="50"/>
-      <c r="B115" s="39" t="s">
+      <c r="A115" s="34"/>
+      <c r="B115" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="C115" s="39"/>
-      <c r="D115" s="39"/>
-      <c r="E115" s="39"/>
-      <c r="F115" s="39"/>
-      <c r="G115" s="39"/>
-      <c r="H115" s="21"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="44"/>
+      <c r="F115" s="44"/>
+      <c r="G115" s="44"/>
+      <c r="H115" s="22"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="50"/>
-      <c r="B116" s="39" t="s">
+      <c r="A116" s="34"/>
+      <c r="B116" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="C116" s="39"/>
-      <c r="D116" s="39"/>
-      <c r="E116" s="39"/>
-      <c r="F116" s="39"/>
-      <c r="G116" s="39"/>
-      <c r="H116" s="21"/>
+      <c r="C116" s="44"/>
+      <c r="D116" s="44"/>
+      <c r="E116" s="44"/>
+      <c r="F116" s="44"/>
+      <c r="G116" s="44"/>
+      <c r="H116" s="22"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="50"/>
-      <c r="B117" s="39" t="s">
+      <c r="A117" s="34"/>
+      <c r="B117" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="C117" s="39"/>
-      <c r="D117" s="39"/>
-      <c r="E117" s="39"/>
-      <c r="F117" s="39"/>
-      <c r="G117" s="39"/>
-      <c r="H117" s="21"/>
+      <c r="C117" s="44"/>
+      <c r="D117" s="44"/>
+      <c r="E117" s="44"/>
+      <c r="F117" s="44"/>
+      <c r="G117" s="44"/>
+      <c r="H117" s="22"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="50"/>
-      <c r="B118" s="41" t="s">
+      <c r="A118" s="34"/>
+      <c r="B118" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C118" s="41"/>
-      <c r="D118" s="41"/>
-      <c r="E118" s="41"/>
-      <c r="F118" s="41"/>
-      <c r="G118" s="41"/>
+      <c r="C118" s="45"/>
+      <c r="D118" s="45"/>
+      <c r="E118" s="45"/>
+      <c r="F118" s="45"/>
+      <c r="G118" s="45"/>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="50"/>
-      <c r="B119" s="39" t="s">
+      <c r="A119" s="34"/>
+      <c r="B119" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="C119" s="39"/>
-      <c r="D119" s="39"/>
-      <c r="E119" s="39"/>
-      <c r="F119" s="39"/>
-      <c r="G119" s="39"/>
-      <c r="H119" s="21" t="s">
+      <c r="C119" s="44"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="44"/>
+      <c r="G119" s="44"/>
+      <c r="H119" s="22" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="50"/>
-      <c r="B120" s="39" t="s">
+      <c r="A120" s="34"/>
+      <c r="B120" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="C120" s="39"/>
-      <c r="D120" s="39"/>
-      <c r="E120" s="39"/>
-      <c r="F120" s="39"/>
-      <c r="G120" s="39"/>
-      <c r="H120" s="21"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="44"/>
+      <c r="F120" s="44"/>
+      <c r="G120" s="44"/>
+      <c r="H120" s="22"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="50"/>
-      <c r="B121" s="39" t="s">
+      <c r="A121" s="34"/>
+      <c r="B121" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C121" s="39"/>
-      <c r="D121" s="39"/>
-      <c r="E121" s="39"/>
-      <c r="F121" s="39"/>
-      <c r="G121" s="39"/>
-      <c r="H121" s="21"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="44"/>
+      <c r="E121" s="44"/>
+      <c r="F121" s="44"/>
+      <c r="G121" s="44"/>
+      <c r="H121" s="22"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="50"/>
-      <c r="B122" s="39" t="s">
+      <c r="A122" s="34"/>
+      <c r="B122" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="C122" s="39"/>
-      <c r="D122" s="39"/>
-      <c r="E122" s="39"/>
-      <c r="F122" s="39"/>
-      <c r="G122" s="39"/>
-      <c r="H122" s="21"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="44"/>
+      <c r="F122" s="44"/>
+      <c r="G122" s="44"/>
+      <c r="H122" s="22"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="50"/>
-      <c r="B123" s="39" t="s">
+      <c r="A123" s="34"/>
+      <c r="B123" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="C123" s="39"/>
-      <c r="D123" s="39"/>
-      <c r="E123" s="39"/>
-      <c r="F123" s="39"/>
-      <c r="G123" s="39"/>
-      <c r="H123" s="21"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="44"/>
+      <c r="F123" s="44"/>
+      <c r="G123" s="44"/>
+      <c r="H123" s="22"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="50"/>
-      <c r="B124" s="39" t="s">
+      <c r="A124" s="34"/>
+      <c r="B124" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
-      <c r="E124" s="39"/>
-      <c r="F124" s="39"/>
-      <c r="G124" s="39"/>
-      <c r="H124" s="21"/>
+      <c r="C124" s="44"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="44"/>
+      <c r="F124" s="44"/>
+      <c r="G124" s="44"/>
+      <c r="H124" s="22"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="50"/>
-      <c r="B125" s="39" t="s">
+      <c r="A125" s="34"/>
+      <c r="B125" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="C125" s="39"/>
-      <c r="D125" s="39"/>
-      <c r="E125" s="39"/>
-      <c r="F125" s="39"/>
-      <c r="G125" s="39"/>
-      <c r="H125" s="21"/>
+      <c r="C125" s="44"/>
+      <c r="D125" s="44"/>
+      <c r="E125" s="44"/>
+      <c r="F125" s="44"/>
+      <c r="G125" s="44"/>
+      <c r="H125" s="22"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="50"/>
-      <c r="B126" s="16" t="s">
+      <c r="A126" s="34"/>
+      <c r="B126" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C126" s="16"/>
-      <c r="D126" s="16"/>
-      <c r="E126" s="16"/>
-      <c r="F126" s="16"/>
-      <c r="G126" s="16"/>
-      <c r="H126" s="21" t="s">
+      <c r="C126" s="20"/>
+      <c r="D126" s="20"/>
+      <c r="E126" s="20"/>
+      <c r="F126" s="20"/>
+      <c r="G126" s="20"/>
+      <c r="H126" s="22" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="50"/>
-      <c r="B127" s="16" t="s">
+      <c r="A127" s="34"/>
+      <c r="B127" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="C127" s="16"/>
-      <c r="D127" s="16"/>
-      <c r="E127" s="16"/>
-      <c r="F127" s="16"/>
-      <c r="G127" s="16"/>
-      <c r="H127" s="21"/>
+      <c r="C127" s="20"/>
+      <c r="D127" s="20"/>
+      <c r="E127" s="20"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="20"/>
+      <c r="H127" s="22"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="50"/>
-      <c r="B128" s="16" t="s">
+      <c r="A128" s="34"/>
+      <c r="B128" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="C128" s="16"/>
-      <c r="D128" s="16"/>
-      <c r="E128" s="16"/>
-      <c r="F128" s="16"/>
-      <c r="G128" s="16"/>
-      <c r="H128" s="21"/>
+      <c r="C128" s="20"/>
+      <c r="D128" s="20"/>
+      <c r="E128" s="20"/>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20"/>
+      <c r="H128" s="22"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="50"/>
-      <c r="B129" s="16" t="s">
+      <c r="A129" s="34"/>
+      <c r="B129" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C129" s="16"/>
-      <c r="D129" s="16"/>
-      <c r="E129" s="16"/>
-      <c r="F129" s="16"/>
-      <c r="G129" s="16"/>
-      <c r="H129" s="21"/>
+      <c r="C129" s="20"/>
+      <c r="D129" s="20"/>
+      <c r="E129" s="20"/>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="22"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="50"/>
-      <c r="B130" s="16" t="s">
+      <c r="A130" s="34"/>
+      <c r="B130" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C130" s="16"/>
-      <c r="D130" s="16"/>
-      <c r="E130" s="16"/>
-      <c r="F130" s="16"/>
-      <c r="G130" s="16"/>
-      <c r="H130" s="21"/>
+      <c r="C130" s="20"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="20"/>
+      <c r="F130" s="20"/>
+      <c r="G130" s="20"/>
+      <c r="H130" s="22"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="50"/>
-      <c r="B131" s="16" t="s">
+      <c r="A131" s="34"/>
+      <c r="B131" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="C131" s="16"/>
-      <c r="D131" s="16"/>
-      <c r="E131" s="16"/>
-      <c r="F131" s="16"/>
-      <c r="G131" s="16"/>
-      <c r="H131" s="21"/>
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="20"/>
+      <c r="G131" s="20"/>
+      <c r="H131" s="22"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="50"/>
-      <c r="B132" s="16" t="s">
+      <c r="A132" s="34"/>
+      <c r="B132" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="C132" s="16"/>
-      <c r="D132" s="16"/>
-      <c r="E132" s="16"/>
-      <c r="F132" s="16"/>
-      <c r="G132" s="16"/>
-      <c r="H132" s="21" t="s">
+      <c r="C132" s="20"/>
+      <c r="D132" s="20"/>
+      <c r="E132" s="20"/>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="22" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="50"/>
-      <c r="B133" s="16" t="s">
+      <c r="A133" s="34"/>
+      <c r="B133" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C133" s="16"/>
-      <c r="D133" s="16"/>
-      <c r="E133" s="16"/>
-      <c r="F133" s="16"/>
-      <c r="G133" s="16"/>
-      <c r="H133" s="21"/>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
+      <c r="E133" s="20"/>
+      <c r="F133" s="20"/>
+      <c r="G133" s="20"/>
+      <c r="H133" s="22"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="50"/>
-      <c r="B134" s="16" t="s">
+      <c r="A134" s="34"/>
+      <c r="B134" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C134" s="16"/>
-      <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
-      <c r="F134" s="16"/>
-      <c r="G134" s="16"/>
-      <c r="H134" s="21"/>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20"/>
+      <c r="G134" s="20"/>
+      <c r="H134" s="22"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="50"/>
-      <c r="B135" s="16" t="s">
+      <c r="A135" s="34"/>
+      <c r="B135" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="C135" s="16"/>
-      <c r="D135" s="16"/>
-      <c r="E135" s="16"/>
-      <c r="F135" s="16"/>
-      <c r="G135" s="16"/>
-      <c r="H135" s="21"/>
+      <c r="C135" s="20"/>
+      <c r="D135" s="20"/>
+      <c r="E135" s="20"/>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="22"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="51"/>
-      <c r="B136" s="16" t="s">
+      <c r="A136" s="35"/>
+      <c r="B136" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C136" s="16"/>
-      <c r="D136" s="16"/>
-      <c r="E136" s="16"/>
-      <c r="F136" s="16"/>
-      <c r="G136" s="16"/>
-      <c r="H136" s="21"/>
+      <c r="C136" s="20"/>
+      <c r="D136" s="20"/>
+      <c r="E136" s="20"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20"/>
+      <c r="H136" s="22"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="29">
         <v>17</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C137" s="16"/>
-      <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="16"/>
-      <c r="G137" s="16"/>
-      <c r="H137" s="32" t="s">
+      <c r="C137" s="20"/>
+      <c r="D137" s="20"/>
+      <c r="E137" s="20"/>
+      <c r="F137" s="20"/>
+      <c r="G137" s="20"/>
+      <c r="H137" s="28" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="30"/>
-      <c r="B138" s="16" t="s">
+      <c r="B138" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C138" s="16"/>
-      <c r="D138" s="16"/>
-      <c r="E138" s="16"/>
-      <c r="F138" s="16"/>
-      <c r="G138" s="16"/>
-      <c r="H138" s="32"/>
+      <c r="C138" s="20"/>
+      <c r="D138" s="20"/>
+      <c r="E138" s="20"/>
+      <c r="F138" s="20"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="28"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="30"/>
-      <c r="B139" s="16" t="s">
+      <c r="B139" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C139" s="16"/>
-      <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="16"/>
-      <c r="G139" s="16"/>
-      <c r="H139" s="32"/>
+      <c r="C139" s="20"/>
+      <c r="D139" s="20"/>
+      <c r="E139" s="20"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="20"/>
+      <c r="H139" s="28"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="30"/>
-      <c r="B140" s="16" t="s">
+      <c r="B140" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C140" s="16"/>
-      <c r="D140" s="16"/>
-      <c r="E140" s="16"/>
-      <c r="F140" s="16"/>
-      <c r="G140" s="16"/>
-      <c r="H140" s="32"/>
+      <c r="C140" s="20"/>
+      <c r="D140" s="20"/>
+      <c r="E140" s="20"/>
+      <c r="F140" s="20"/>
+      <c r="G140" s="20"/>
+      <c r="H140" s="28"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="30"/>
-      <c r="B141" s="16" t="s">
+      <c r="B141" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C141" s="16"/>
-      <c r="D141" s="16"/>
-      <c r="E141" s="16"/>
-      <c r="F141" s="16"/>
-      <c r="G141" s="16"/>
-      <c r="H141" s="32"/>
+      <c r="C141" s="20"/>
+      <c r="D141" s="20"/>
+      <c r="E141" s="20"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="28"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="30"/>
-      <c r="B142" s="16" t="s">
+      <c r="B142" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C142" s="16"/>
-      <c r="D142" s="16"/>
-      <c r="E142" s="16"/>
-      <c r="F142" s="16"/>
-      <c r="G142" s="16"/>
-      <c r="H142" s="32"/>
+      <c r="C142" s="20"/>
+      <c r="D142" s="20"/>
+      <c r="E142" s="20"/>
+      <c r="F142" s="20"/>
+      <c r="G142" s="20"/>
+      <c r="H142" s="28"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="30"/>
-      <c r="B143" s="16" t="s">
+      <c r="B143" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C143" s="16"/>
-      <c r="D143" s="16"/>
-      <c r="E143" s="16"/>
-      <c r="F143" s="16"/>
-      <c r="G143" s="16"/>
-      <c r="H143" s="32"/>
+      <c r="C143" s="20"/>
+      <c r="D143" s="20"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="20"/>
+      <c r="G143" s="20"/>
+      <c r="H143" s="28"/>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="30"/>
-      <c r="B144" s="16" t="s">
+      <c r="B144" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C144" s="16"/>
-      <c r="D144" s="16"/>
-      <c r="E144" s="16"/>
-      <c r="F144" s="16"/>
-      <c r="G144" s="16"/>
-      <c r="H144" s="32"/>
+      <c r="C144" s="20"/>
+      <c r="D144" s="20"/>
+      <c r="E144" s="20"/>
+      <c r="F144" s="20"/>
+      <c r="G144" s="20"/>
+      <c r="H144" s="28"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="30"/>
-      <c r="B145" s="16" t="s">
+      <c r="B145" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C145" s="16"/>
-      <c r="D145" s="16"/>
-      <c r="E145" s="16"/>
-      <c r="F145" s="16"/>
-      <c r="G145" s="16"/>
-      <c r="H145" s="32"/>
+      <c r="C145" s="20"/>
+      <c r="D145" s="20"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="20"/>
+      <c r="G145" s="20"/>
+      <c r="H145" s="28"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="30"/>
-      <c r="B146" s="16" t="s">
+      <c r="B146" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C146" s="16"/>
-      <c r="D146" s="16"/>
-      <c r="E146" s="16"/>
-      <c r="F146" s="16"/>
-      <c r="G146" s="16"/>
-      <c r="H146" s="32"/>
+      <c r="C146" s="20"/>
+      <c r="D146" s="20"/>
+      <c r="E146" s="20"/>
+      <c r="F146" s="20"/>
+      <c r="G146" s="20"/>
+      <c r="H146" s="28"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="30"/>
-      <c r="B147" s="16" t="s">
+      <c r="B147" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C147" s="16"/>
-      <c r="D147" s="16"/>
-      <c r="E147" s="16"/>
-      <c r="F147" s="16"/>
-      <c r="G147" s="16"/>
-      <c r="H147" s="32"/>
+      <c r="C147" s="20"/>
+      <c r="D147" s="20"/>
+      <c r="E147" s="20"/>
+      <c r="F147" s="20"/>
+      <c r="G147" s="20"/>
+      <c r="H147" s="28"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="30"/>
-      <c r="B148" s="16" t="s">
+      <c r="B148" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C148" s="16"/>
-      <c r="D148" s="16"/>
-      <c r="E148" s="16"/>
-      <c r="F148" s="16"/>
-      <c r="G148" s="16"/>
-      <c r="H148" s="32"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20"/>
+      <c r="E148" s="20"/>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="28"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="30"/>
-      <c r="B149" s="16" t="s">
+      <c r="B149" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C149" s="16"/>
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="16"/>
-      <c r="G149" s="16"/>
-      <c r="H149" s="32"/>
+      <c r="C149" s="20"/>
+      <c r="D149" s="20"/>
+      <c r="E149" s="20"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="20"/>
+      <c r="H149" s="28"/>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="30"/>
-      <c r="B150" s="16" t="s">
+      <c r="B150" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C150" s="16"/>
-      <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
-      <c r="F150" s="16"/>
-      <c r="G150" s="16"/>
-      <c r="H150" s="32"/>
+      <c r="C150" s="20"/>
+      <c r="D150" s="20"/>
+      <c r="E150" s="20"/>
+      <c r="F150" s="20"/>
+      <c r="G150" s="20"/>
+      <c r="H150" s="28"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="30"/>
-      <c r="B151" s="16" t="s">
+      <c r="B151" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C151" s="16"/>
-      <c r="D151" s="16"/>
-      <c r="E151" s="16"/>
-      <c r="F151" s="16"/>
-      <c r="G151" s="16"/>
-      <c r="H151" s="32"/>
+      <c r="C151" s="20"/>
+      <c r="D151" s="20"/>
+      <c r="E151" s="20"/>
+      <c r="F151" s="20"/>
+      <c r="G151" s="20"/>
+      <c r="H151" s="28"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="30"/>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C152" s="16"/>
-      <c r="D152" s="16"/>
-      <c r="E152" s="16"/>
-      <c r="F152" s="16"/>
-      <c r="G152" s="16"/>
-      <c r="H152" s="32"/>
+      <c r="C152" s="20"/>
+      <c r="D152" s="20"/>
+      <c r="E152" s="20"/>
+      <c r="F152" s="20"/>
+      <c r="G152" s="20"/>
+      <c r="H152" s="28"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="30"/>
-      <c r="B153" s="16" t="s">
+      <c r="B153" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C153" s="16"/>
-      <c r="D153" s="16"/>
-      <c r="E153" s="16"/>
-      <c r="F153" s="16"/>
-      <c r="G153" s="16"/>
-      <c r="H153" s="46"/>
+      <c r="C153" s="20"/>
+      <c r="D153" s="20"/>
+      <c r="E153" s="20"/>
+      <c r="F153" s="20"/>
+      <c r="G153" s="20"/>
+      <c r="H153" s="39"/>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="30"/>
-      <c r="B154" s="16" t="s">
+      <c r="B154" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C154" s="16"/>
-      <c r="D154" s="16"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="16"/>
-      <c r="G154" s="16"/>
-      <c r="H154" s="32" t="s">
+      <c r="C154" s="20"/>
+      <c r="D154" s="20"/>
+      <c r="E154" s="20"/>
+      <c r="F154" s="20"/>
+      <c r="G154" s="20"/>
+      <c r="H154" s="28" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="30"/>
-      <c r="B155" s="16" t="s">
+      <c r="B155" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C155" s="16"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="16"/>
-      <c r="H155" s="32"/>
+      <c r="C155" s="20"/>
+      <c r="D155" s="20"/>
+      <c r="E155" s="20"/>
+      <c r="F155" s="20"/>
+      <c r="G155" s="20"/>
+      <c r="H155" s="28"/>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="30"/>
-      <c r="B156" s="16" t="s">
+      <c r="B156" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C156" s="16"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="16"/>
-      <c r="G156" s="16"/>
-      <c r="H156" s="32"/>
+      <c r="C156" s="20"/>
+      <c r="D156" s="20"/>
+      <c r="E156" s="20"/>
+      <c r="F156" s="20"/>
+      <c r="G156" s="20"/>
+      <c r="H156" s="28"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="30"/>
-      <c r="B157" s="16" t="s">
+      <c r="B157" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C157" s="16"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="16"/>
-      <c r="G157" s="16"/>
-      <c r="H157" s="32"/>
+      <c r="C157" s="20"/>
+      <c r="D157" s="20"/>
+      <c r="E157" s="20"/>
+      <c r="F157" s="20"/>
+      <c r="G157" s="20"/>
+      <c r="H157" s="28"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="30"/>
-      <c r="B158" s="16" t="s">
+      <c r="B158" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C158" s="16"/>
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="16"/>
-      <c r="G158" s="16"/>
-      <c r="H158" s="32"/>
+      <c r="C158" s="20"/>
+      <c r="D158" s="20"/>
+      <c r="E158" s="20"/>
+      <c r="F158" s="20"/>
+      <c r="G158" s="20"/>
+      <c r="H158" s="28"/>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="31"/>
-      <c r="B159" s="16" t="s">
+      <c r="B159" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C159" s="16"/>
-      <c r="D159" s="16"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="16"/>
-      <c r="G159" s="16"/>
-      <c r="H159" s="32"/>
+      <c r="C159" s="20"/>
+      <c r="D159" s="20"/>
+      <c r="E159" s="20"/>
+      <c r="F159" s="20"/>
+      <c r="G159" s="20"/>
+      <c r="H159" s="28"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="15" t="s">
+      <c r="A160" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B160" s="15"/>
-      <c r="C160" s="15"/>
-      <c r="D160" s="15"/>
-      <c r="E160" s="15"/>
-      <c r="F160" s="15"/>
-      <c r="G160" s="15"/>
-      <c r="H160" s="15"/>
+      <c r="B160" s="16"/>
+      <c r="C160" s="16"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="16"/>
+      <c r="F160" s="16"/>
+      <c r="G160" s="16"/>
+      <c r="H160" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="A83:A99"/>
-    <mergeCell ref="A100:A136"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H2:H11"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="H14:H27"/>
-    <mergeCell ref="A14:A27"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B155:G155"/>
-    <mergeCell ref="B156:G156"/>
-    <mergeCell ref="B157:G157"/>
-    <mergeCell ref="B158:G158"/>
-    <mergeCell ref="B159:G159"/>
-    <mergeCell ref="H154:H159"/>
-    <mergeCell ref="H126:H131"/>
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="B137:G137"/>
-    <mergeCell ref="B138:G138"/>
-    <mergeCell ref="H137:H153"/>
-    <mergeCell ref="B139:G139"/>
-    <mergeCell ref="B140:G140"/>
-    <mergeCell ref="B141:G141"/>
-    <mergeCell ref="B142:G142"/>
-    <mergeCell ref="B143:G143"/>
-    <mergeCell ref="B144:G144"/>
-    <mergeCell ref="B145:G145"/>
-    <mergeCell ref="A42:A63"/>
-    <mergeCell ref="A64:A82"/>
-    <mergeCell ref="B146:G146"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="B148:G148"/>
-    <mergeCell ref="B149:G149"/>
-    <mergeCell ref="B150:G150"/>
-    <mergeCell ref="B151:G151"/>
-    <mergeCell ref="B152:G152"/>
-    <mergeCell ref="B153:G153"/>
-    <mergeCell ref="B154:G154"/>
-    <mergeCell ref="B132:G132"/>
-    <mergeCell ref="B133:G133"/>
-    <mergeCell ref="B134:G134"/>
-    <mergeCell ref="B135:G135"/>
-    <mergeCell ref="B136:G136"/>
-    <mergeCell ref="B126:G126"/>
-    <mergeCell ref="B127:G127"/>
-    <mergeCell ref="B128:G128"/>
-    <mergeCell ref="B129:G129"/>
-    <mergeCell ref="B130:G130"/>
-    <mergeCell ref="B131:G131"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="B117:G117"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="B119:G119"/>
-    <mergeCell ref="B108:G108"/>
-    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A28:A41"/>
+    <mergeCell ref="H28:H41"/>
+    <mergeCell ref="A137:A159"/>
+    <mergeCell ref="A160:H160"/>
+    <mergeCell ref="H119:H125"/>
+    <mergeCell ref="B120:G120"/>
+    <mergeCell ref="B121:G121"/>
+    <mergeCell ref="B122:G122"/>
+    <mergeCell ref="B123:G123"/>
+    <mergeCell ref="B124:G124"/>
+    <mergeCell ref="B125:G125"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="H100:H118"/>
+    <mergeCell ref="B101:G101"/>
+    <mergeCell ref="B102:G102"/>
+    <mergeCell ref="B103:G103"/>
+    <mergeCell ref="B83:G83"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="B85:G85"/>
+    <mergeCell ref="B86:G86"/>
+    <mergeCell ref="B104:G104"/>
+    <mergeCell ref="B87:G87"/>
+    <mergeCell ref="B88:G88"/>
+    <mergeCell ref="H83:H88"/>
+    <mergeCell ref="B110:G110"/>
+    <mergeCell ref="B111:G111"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B97:G97"/>
+    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B113:G113"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="H76:H82"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="B79:G79"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="B82:G82"/>
+    <mergeCell ref="H64:H75"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B93:G93"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B105:G105"/>
+    <mergeCell ref="B106:G106"/>
+    <mergeCell ref="B107:G107"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H42:H56"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B89:G89"/>
     <mergeCell ref="B90:G90"/>
@@ -6115,6 +6116,78 @@
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B91:G91"/>
+    <mergeCell ref="B159:G159"/>
+    <mergeCell ref="H154:H159"/>
+    <mergeCell ref="H126:H131"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="B137:G137"/>
+    <mergeCell ref="B138:G138"/>
+    <mergeCell ref="H137:H153"/>
+    <mergeCell ref="B139:G139"/>
+    <mergeCell ref="B140:G140"/>
+    <mergeCell ref="B141:G141"/>
+    <mergeCell ref="B142:G142"/>
+    <mergeCell ref="B143:G143"/>
+    <mergeCell ref="B144:G144"/>
+    <mergeCell ref="B145:G145"/>
+    <mergeCell ref="B146:G146"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="B148:G148"/>
+    <mergeCell ref="B149:G149"/>
+    <mergeCell ref="B150:G150"/>
+    <mergeCell ref="B151:G151"/>
+    <mergeCell ref="B152:G152"/>
+    <mergeCell ref="B153:G153"/>
+    <mergeCell ref="B154:G154"/>
+    <mergeCell ref="B132:G132"/>
+    <mergeCell ref="H14:H27"/>
+    <mergeCell ref="A14:A27"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B155:G155"/>
+    <mergeCell ref="B156:G156"/>
+    <mergeCell ref="B157:G157"/>
+    <mergeCell ref="B158:G158"/>
+    <mergeCell ref="A42:A63"/>
+    <mergeCell ref="A64:A82"/>
+    <mergeCell ref="B133:G133"/>
+    <mergeCell ref="B134:G134"/>
+    <mergeCell ref="B135:G135"/>
+    <mergeCell ref="B136:G136"/>
+    <mergeCell ref="B126:G126"/>
+    <mergeCell ref="B127:G127"/>
+    <mergeCell ref="B128:G128"/>
+    <mergeCell ref="B129:G129"/>
+    <mergeCell ref="B130:G130"/>
+    <mergeCell ref="B131:G131"/>
+    <mergeCell ref="B114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H2:H11"/>
+    <mergeCell ref="A83:A99"/>
+    <mergeCell ref="A100:A136"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B117:G117"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="B119:G119"/>
+    <mergeCell ref="B108:G108"/>
+    <mergeCell ref="B109:G109"/>
     <mergeCell ref="B29:G29"/>
     <mergeCell ref="B30:G30"/>
     <mergeCell ref="B32:G32"/>
@@ -6124,79 +6197,6 @@
     <mergeCell ref="B69:G69"/>
     <mergeCell ref="B70:G70"/>
     <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H42:H56"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B113:G113"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="H76:H82"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="B79:G79"/>
-    <mergeCell ref="B80:G80"/>
-    <mergeCell ref="B82:G82"/>
-    <mergeCell ref="H64:H75"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B68:G68"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B92:G92"/>
-    <mergeCell ref="B93:G93"/>
-    <mergeCell ref="B94:G94"/>
-    <mergeCell ref="B105:G105"/>
-    <mergeCell ref="B106:G106"/>
-    <mergeCell ref="B107:G107"/>
-    <mergeCell ref="B87:G87"/>
-    <mergeCell ref="B88:G88"/>
-    <mergeCell ref="H83:H88"/>
-    <mergeCell ref="B110:G110"/>
-    <mergeCell ref="B111:G111"/>
-    <mergeCell ref="B112:G112"/>
-    <mergeCell ref="B95:G95"/>
-    <mergeCell ref="B96:G96"/>
-    <mergeCell ref="B97:G97"/>
-    <mergeCell ref="B98:G98"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="A28:A41"/>
-    <mergeCell ref="H28:H41"/>
-    <mergeCell ref="A137:A159"/>
-    <mergeCell ref="A160:H160"/>
-    <mergeCell ref="H119:H125"/>
-    <mergeCell ref="B120:G120"/>
-    <mergeCell ref="B121:G121"/>
-    <mergeCell ref="B122:G122"/>
-    <mergeCell ref="B123:G123"/>
-    <mergeCell ref="B124:G124"/>
-    <mergeCell ref="B125:G125"/>
-    <mergeCell ref="B100:G100"/>
-    <mergeCell ref="H100:H118"/>
-    <mergeCell ref="B101:G101"/>
-    <mergeCell ref="B102:G102"/>
-    <mergeCell ref="B103:G103"/>
-    <mergeCell ref="B83:G83"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="B85:G85"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="B104:G104"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Java Full Stack_ToC.xlsx
+++ b/Java Full Stack_ToC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\harman_training\Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3585DAB-E3FD-44F4-8FF8-2F556ED3F283}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3895D586-BDBE-4E41-A28B-4ACB68351BB8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3528" yWindow="1584" windowWidth="19512" windowHeight="10920" activeTab="2" xr2:uid="{650FC967-2F93-46CA-B378-157C068E930D}"/>
+    <workbookView xWindow="3528" yWindow="1584" windowWidth="19512" windowHeight="10920" activeTab="3" xr2:uid="{650FC967-2F93-46CA-B378-157C068E930D}"/>
   </bookViews>
   <sheets>
     <sheet name="Course Outline" sheetId="5" r:id="rId1"/>
@@ -18,28 +18,17 @@
     <sheet name="Day 6 - 9" sheetId="7" r:id="rId3"/>
     <sheet name="Day 10 - 17" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="358">
   <si>
     <t>Technology</t>
   </si>
@@ -1499,6 +1488,9 @@
   </si>
   <si>
     <t>Design Patterns Introduction - Singleton,Factory, Adaptor, Observer</t>
+  </si>
+  <si>
+    <t>sprinig security jwt</t>
   </si>
 </sst>
 </file>
@@ -1723,14 +1715,20 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1738,17 +1736,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1759,14 +1757,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1777,17 +1769,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1797,12 +1780,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1816,14 +1793,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1834,8 +1808,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2160,21 +2152,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="2:5">
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="8" t="s">
         <v>165</v>
       </c>
@@ -2183,10 +2175,10 @@
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="7" t="s">
         <v>177</v>
       </c>
@@ -2195,10 +2187,10 @@
       <c r="B4" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="7" t="s">
         <v>167</v>
       </c>
@@ -2207,10 +2199,10 @@
       <c r="B5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="7" t="s">
         <v>172</v>
       </c>
@@ -2219,65 +2211,65 @@
       <c r="B6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="7" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="13" t="s">
@@ -2286,12 +2278,12 @@
       <c r="C19" s="13"/>
     </row>
     <row r="20" spans="2:5" ht="36" customHeight="1">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="13" t="s">
@@ -2330,6 +2322,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:D10"/>
@@ -2337,12 +2335,6 @@
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2357,15 +2349,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -2374,883 +2366,956 @@
       <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="25" t="s">
         <v>333</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="25"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="20" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="20" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="20" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="20" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="20" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="20" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="26"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="20" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="26"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="20" t="s">
+      <c r="A13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="26"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="20" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="26"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="20" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="26"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="20" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="26"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="20" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="26"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="20" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="26"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="20" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="26"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="20" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="26"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="20" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="26"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="20" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="26"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="20" t="s">
+      <c r="A23" s="23"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="26"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="20" t="s">
+      <c r="A24" s="23"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="26"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="20" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="26"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="20" t="s">
+      <c r="A26" s="23"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="26"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="20" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="26"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="20" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="26"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="20" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="26"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="20" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="20" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="20" t="s">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="18"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="20" t="s">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="20" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="20" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="20" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="20" t="s">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="20" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="20" t="s">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="20" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="20" t="s">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="20" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="20" t="s">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="20" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="20" t="s">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="20" t="s">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="18"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="18"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="22"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="20" t="s">
+      <c r="A51" s="21"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="20" t="s">
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="20" t="s">
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="20" t="s">
+      <c r="A55" s="21"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="20" t="s">
+      <c r="A56" s="21"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="20" t="s">
+      <c r="A57" s="21"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="20" t="s">
+      <c r="A58" s="21"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="20" t="s">
+      <c r="A59" s="21"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="22"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="20" t="s">
+      <c r="A60" s="21"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="20" t="s">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="20" t="s">
+      <c r="A62" s="21"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="20" t="s">
+      <c r="A63" s="21"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="20" t="s">
+      <c r="A64" s="21"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="20" t="s">
+      <c r="A65" s="21"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="22"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="20" t="s">
+      <c r="A67" s="21"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="20" t="s">
+      <c r="A68" s="21"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="22"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="20" t="s">
+      <c r="A69" s="21"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="22"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="20" t="s">
+      <c r="A70" s="21"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="22"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="20" t="s">
+      <c r="A71" s="21"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="22"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="20" t="s">
+      <c r="A72" s="21"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="22"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="20" t="s">
+      <c r="A73" s="21"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="22"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="20" t="s">
+      <c r="A74" s="21"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="22"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="20" t="s">
+      <c r="A75" s="21"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="22"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="20" t="s">
+      <c r="A76" s="21"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="22"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="20" t="s">
+      <c r="A77" s="21"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="22"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="20" t="s">
+      <c r="A78" s="21"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A11:A30"/>
+    <mergeCell ref="B11:B30"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="A52:A65"/>
+    <mergeCell ref="B52:B65"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="A31:A51"/>
+    <mergeCell ref="B31:B51"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C64:G64"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A79:G79"/>
     <mergeCell ref="C73:G73"/>
@@ -3267,71 +3332,653 @@
     <mergeCell ref="C68:G68"/>
     <mergeCell ref="C69:G69"/>
     <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="A52:A65"/>
-    <mergeCell ref="B52:B65"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="A31:A51"/>
-    <mergeCell ref="B31:B51"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A11:A30"/>
-    <mergeCell ref="B11:B30"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144CF55E-ADAB-4A5A-B994-3C7076E84FC8}">
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="7" max="7" width="29.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="21"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="21"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="21"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="21"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="21"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="21"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="21"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="21"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="21"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="21"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="21"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="21"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="21"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="21"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="21"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="21"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="21"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="21"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="21"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="21"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="21"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="21"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="21"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="21"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="21"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="21"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="21"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="21"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="21"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="21"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="21"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="21"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="21"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="21"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="21"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="21"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="21"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="21"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="21"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="21"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="21"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="21"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="B48" s="30"/>
+      <c r="C48" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="21"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="21"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="21"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="21"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="21"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="21"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="62">
+    <mergeCell ref="C2:G2"/>
     <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="A3:A20"/>
+    <mergeCell ref="B3:B20"/>
+    <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
@@ -3339,646 +3986,40 @@
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144CF55E-ADAB-4A5A-B994-3C7076E84FC8}">
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="29.88671875" customWidth="1"/>
-    <col min="7" max="7" width="29.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="22"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="22"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="22"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="22"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="22"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="22"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="22"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="22"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="22"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="22"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="22"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="22"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="22"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="22"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="22"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="22"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="22"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="22"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="22"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="22"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="22"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="22"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="22"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="22"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="22"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="22"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="22"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="22"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="22"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="22"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="B36" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="22"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="22"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="22"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="22"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="22"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="22"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="22"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="22"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="22"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="22"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="22"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="B48" s="30"/>
-      <c r="C48" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="22"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="22"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="22"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="22"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="22"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="22"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="62">
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="B21:B35"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="A36:A47"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C54:G54"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="C45:G45"/>
@@ -3995,52 +4036,6 @@
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="C29:G29"/>
-    <mergeCell ref="A36:A47"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="B21:B35"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A3:A20"/>
-    <mergeCell ref="B3:B20"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4059,14 +4054,14 @@
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4075,159 +4070,159 @@
       <c r="A2" s="29">
         <v>10</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="22" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="30"/>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="22"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="30"/>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="22"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="30"/>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="21"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="30"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="30"/>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="22"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="30"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="22"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="30"/>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="22"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="30"/>
       <c r="B10" t="s">
         <v>338</v>
       </c>
-      <c r="H10" s="22"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="30"/>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="22"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:8" ht="14.55" customHeight="1">
       <c r="A12" s="30"/>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="39" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="46" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="31"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="40"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="48"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="29">
         <v>11</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="29" t="s">
         <v>140</v>
       </c>
@@ -4246,190 +4241,190 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="30"/>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="30"/>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="30"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="30"/>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="30"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="30"/>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="30"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="30"/>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="30"/>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
       <c r="H21" s="30"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="30"/>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="30"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="30"/>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="30"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="30"/>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
       <c r="H24" s="30"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="30"/>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
       <c r="H25" s="30"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="30"/>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="31"/>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="41">
+      <c r="A28" s="36">
         <v>12</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="41" t="s">
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="42"/>
-      <c r="B29" s="36" t="s">
+      <c r="A29" s="37"/>
+      <c r="B29" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="42"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="37"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="42"/>
-      <c r="B30" s="36" t="s">
+      <c r="A30" s="37"/>
+      <c r="B30" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="42"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="37"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="42"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="4" t="s">
         <v>40</v>
       </c>
@@ -4438,70 +4433,70 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="42"/>
+      <c r="H31" s="37"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="42"/>
-      <c r="B32" s="36" t="s">
+      <c r="A32" s="37"/>
+      <c r="B32" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="42"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="37"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="42"/>
-      <c r="B33" s="36" t="s">
+      <c r="A33" s="37"/>
+      <c r="B33" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="42"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="37"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="42"/>
-      <c r="B34" s="36" t="s">
+      <c r="A34" s="37"/>
+      <c r="B34" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="42"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="37"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="42"/>
-      <c r="B35" s="36" t="s">
+      <c r="A35" s="37"/>
+      <c r="B35" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="42"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="37"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="42"/>
-      <c r="B36" s="36" t="s">
+      <c r="A36" s="37"/>
+      <c r="B36" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="42"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="37"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="42"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="10" t="s">
         <v>344</v>
       </c>
@@ -4510,755 +4505,755 @@
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="12"/>
-      <c r="H37" s="42"/>
+      <c r="H37" s="37"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="42"/>
-      <c r="B38" s="36" t="s">
+      <c r="A38" s="37"/>
+      <c r="B38" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="42"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="37"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="42"/>
-      <c r="B39" s="36" t="s">
+      <c r="A39" s="37"/>
+      <c r="B39" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="42"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="37"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="42"/>
-      <c r="B40" s="36" t="s">
+      <c r="A40" s="37"/>
+      <c r="B40" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="42"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="37"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="43"/>
-      <c r="B41" s="36" t="s">
+      <c r="A41" s="38"/>
+      <c r="B41" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="43"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="38"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="41">
+      <c r="A42" s="36">
         <v>13</v>
       </c>
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="41" t="s">
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="36" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="42"/>
-      <c r="B43" s="36" t="s">
+      <c r="A43" s="37"/>
+      <c r="B43" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="42"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="37"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="42"/>
-      <c r="B44" s="36" t="s">
+      <c r="A44" s="37"/>
+      <c r="B44" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="42"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="37"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="42"/>
-      <c r="B45" s="36" t="s">
+      <c r="A45" s="37"/>
+      <c r="B45" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="42"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="37"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="42"/>
-      <c r="B46" s="36" t="s">
+      <c r="A46" s="37"/>
+      <c r="B46" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="42"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="37"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="42"/>
-      <c r="B47" s="36" t="s">
+      <c r="A47" s="37"/>
+      <c r="B47" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="42"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="37"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="42"/>
-      <c r="B48" s="36" t="s">
+      <c r="A48" s="37"/>
+      <c r="B48" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="42"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="37"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="42"/>
-      <c r="B49" s="36" t="s">
+      <c r="A49" s="37"/>
+      <c r="B49" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="42"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="37"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="42"/>
-      <c r="B50" s="36" t="s">
+      <c r="A50" s="37"/>
+      <c r="B50" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="42"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="37"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="42"/>
-      <c r="B51" s="36" t="s">
+      <c r="A51" s="37"/>
+      <c r="B51" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="42"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="37"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="42"/>
-      <c r="B52" s="36" t="s">
+      <c r="A52" s="37"/>
+      <c r="B52" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="42"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="37"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="42"/>
-      <c r="B53" s="36" t="s">
+      <c r="A53" s="37"/>
+      <c r="B53" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="42"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="37"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="42"/>
-      <c r="B54" s="36" t="s">
+      <c r="A54" s="37"/>
+      <c r="B54" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="42"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="37"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="42"/>
-      <c r="B55" s="36" t="s">
+      <c r="A55" s="37"/>
+      <c r="B55" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="42"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="37"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="42"/>
-      <c r="B56" s="36" t="s">
+      <c r="A56" s="37"/>
+      <c r="B56" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="43"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="38"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="42"/>
-      <c r="B57" s="36" t="s">
+      <c r="A57" s="37"/>
+      <c r="B57" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="41" t="s">
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="36" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="42"/>
-      <c r="B58" s="36" t="s">
+      <c r="A58" s="37"/>
+      <c r="B58" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="42"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="37"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="42"/>
-      <c r="B59" s="36" t="s">
+      <c r="A59" s="37"/>
+      <c r="B59" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="42"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="37"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="42"/>
-      <c r="B60" s="36" t="s">
+      <c r="A60" s="37"/>
+      <c r="B60" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="42"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="37"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="42"/>
-      <c r="B61" s="36" t="s">
+      <c r="A61" s="37"/>
+      <c r="B61" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="42"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="37"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="42"/>
-      <c r="B62" s="36" t="s">
+      <c r="A62" s="37"/>
+      <c r="B62" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="42"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="37"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="42"/>
-      <c r="B63" s="36" t="s">
+      <c r="A63" s="37"/>
+      <c r="B63" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="43"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="38"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="42">
+      <c r="A64" s="37">
         <v>14</v>
       </c>
-      <c r="B64" s="36" t="s">
+      <c r="B64" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="48" t="s">
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="42" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="42"/>
-      <c r="B65" s="36" t="s">
+      <c r="A65" s="37"/>
+      <c r="B65" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="49"/>
+      <c r="C65" s="34"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="43"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="42"/>
-      <c r="B66" s="36" t="s">
+      <c r="A66" s="37"/>
+      <c r="B66" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="49"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="43"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="42"/>
-      <c r="B67" s="36" t="s">
+      <c r="A67" s="37"/>
+      <c r="B67" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="49"/>
+      <c r="C67" s="34"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="43"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="42"/>
-      <c r="B68" s="36" t="s">
+      <c r="A68" s="37"/>
+      <c r="B68" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="49"/>
+      <c r="C68" s="34"/>
+      <c r="D68" s="34"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="43"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="42"/>
-      <c r="B69" s="36" t="s">
+      <c r="A69" s="37"/>
+      <c r="B69" s="33" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="49"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="43"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="42"/>
-      <c r="B70" s="36" t="s">
+      <c r="A70" s="37"/>
+      <c r="B70" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="49"/>
+      <c r="C70" s="34"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="34"/>
+      <c r="F70" s="34"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="43"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="42"/>
-      <c r="B71" s="36" t="s">
+      <c r="A71" s="37"/>
+      <c r="B71" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="49"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="43"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="42"/>
-      <c r="B72" s="36" t="s">
+      <c r="A72" s="37"/>
+      <c r="B72" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="49"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="43"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="42"/>
-      <c r="B73" s="36" t="s">
+      <c r="A73" s="37"/>
+      <c r="B73" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="49"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="34"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="43"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="42"/>
-      <c r="B74" s="36" t="s">
+      <c r="A74" s="37"/>
+      <c r="B74" s="33" t="s">
         <v>340</v>
       </c>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="49"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="34"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="43"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="42"/>
-      <c r="B75" s="36" t="s">
+      <c r="A75" s="37"/>
+      <c r="B75" s="33" t="s">
         <v>342</v>
       </c>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="50"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="44"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="42"/>
-      <c r="B76" s="36" t="s">
+      <c r="A76" s="37"/>
+      <c r="B76" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="41" t="s">
+      <c r="C76" s="34"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="34"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="36" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="42"/>
-      <c r="B77" s="36" t="s">
+      <c r="A77" s="37"/>
+      <c r="B77" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="42"/>
+      <c r="C77" s="34"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="37"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="42"/>
-      <c r="B78" s="36" t="s">
+      <c r="A78" s="37"/>
+      <c r="B78" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="42"/>
+      <c r="C78" s="34"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="37"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="42"/>
-      <c r="B79" s="36" t="s">
+      <c r="A79" s="37"/>
+      <c r="B79" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="42"/>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="37"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="42"/>
-      <c r="B80" s="36" t="s">
+      <c r="A80" s="37"/>
+      <c r="B80" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="42"/>
+      <c r="C80" s="34"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="35"/>
+      <c r="H80" s="37"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="42"/>
+      <c r="A81" s="37"/>
       <c r="B81" t="s">
         <v>341</v>
       </c>
-      <c r="H81" s="42"/>
+      <c r="H81" s="37"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="43"/>
-      <c r="B82" s="36" t="s">
+      <c r="A82" s="38"/>
+      <c r="B82" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="43"/>
+      <c r="C82" s="34"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="38"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="33">
+      <c r="A83" s="49">
         <v>15</v>
       </c>
-      <c r="B83" s="51" t="s">
+      <c r="B83" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="51"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="22" t="s">
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="34"/>
-      <c r="B84" s="51" t="s">
+      <c r="A84" s="50"/>
+      <c r="B84" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="51"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="22"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="21"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="34"/>
-      <c r="B85" s="51" t="s">
+      <c r="A85" s="50"/>
+      <c r="B85" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="C85" s="51"/>
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="51"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="22"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="21"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="34"/>
-      <c r="B86" s="51" t="s">
+      <c r="A86" s="50"/>
+      <c r="B86" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="22"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="21"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="34"/>
-      <c r="B87" s="51" t="s">
+      <c r="A87" s="50"/>
+      <c r="B87" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="22"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="21"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="34"/>
-      <c r="B88" s="51" t="s">
+      <c r="A88" s="50"/>
+      <c r="B88" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="22"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="21"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="34"/>
-      <c r="B89" s="36" t="s">
+      <c r="A89" s="50"/>
+      <c r="B89" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
-      <c r="G89" s="38"/>
-      <c r="H89" s="39" t="s">
+      <c r="C89" s="34"/>
+      <c r="D89" s="34"/>
+      <c r="E89" s="34"/>
+      <c r="F89" s="34"/>
+      <c r="G89" s="35"/>
+      <c r="H89" s="46" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="34"/>
-      <c r="B90" s="36" t="s">
+      <c r="A90" s="50"/>
+      <c r="B90" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="38"/>
+      <c r="C90" s="34"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="34"/>
+      <c r="F90" s="34"/>
+      <c r="G90" s="35"/>
       <c r="H90" s="47"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="34"/>
-      <c r="B91" s="36" t="s">
+      <c r="A91" s="50"/>
+      <c r="B91" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="38"/>
+      <c r="C91" s="34"/>
+      <c r="D91" s="34"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="34"/>
+      <c r="G91" s="35"/>
       <c r="H91" s="47"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="34"/>
-      <c r="B92" s="36" t="s">
+      <c r="A92" s="50"/>
+      <c r="B92" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="38"/>
+      <c r="C92" s="34"/>
+      <c r="D92" s="34"/>
+      <c r="E92" s="34"/>
+      <c r="F92" s="34"/>
+      <c r="G92" s="35"/>
       <c r="H92" s="47"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="34"/>
-      <c r="B93" s="36" t="s">
+      <c r="A93" s="50"/>
+      <c r="B93" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="37"/>
-      <c r="F93" s="37"/>
-      <c r="G93" s="38"/>
+      <c r="C93" s="34"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="34"/>
+      <c r="F93" s="34"/>
+      <c r="G93" s="35"/>
       <c r="H93" s="47"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="34"/>
-      <c r="B94" s="36" t="s">
+      <c r="A94" s="50"/>
+      <c r="B94" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C94" s="37"/>
-      <c r="D94" s="37"/>
-      <c r="E94" s="37"/>
-      <c r="F94" s="37"/>
-      <c r="G94" s="38"/>
+      <c r="C94" s="34"/>
+      <c r="D94" s="34"/>
+      <c r="E94" s="34"/>
+      <c r="F94" s="34"/>
+      <c r="G94" s="35"/>
       <c r="H94" s="47"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="34"/>
-      <c r="B95" s="36" t="s">
+      <c r="A95" s="50"/>
+      <c r="B95" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="37"/>
-      <c r="D95" s="37"/>
-      <c r="E95" s="37"/>
-      <c r="F95" s="37"/>
-      <c r="G95" s="38"/>
+      <c r="C95" s="34"/>
+      <c r="D95" s="34"/>
+      <c r="E95" s="34"/>
+      <c r="F95" s="34"/>
+      <c r="G95" s="35"/>
       <c r="H95" s="47"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="34"/>
-      <c r="B96" s="36" t="s">
+      <c r="A96" s="50"/>
+      <c r="B96" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="37"/>
-      <c r="D96" s="37"/>
-      <c r="E96" s="37"/>
-      <c r="F96" s="37"/>
-      <c r="G96" s="38"/>
+      <c r="C96" s="34"/>
+      <c r="D96" s="34"/>
+      <c r="E96" s="34"/>
+      <c r="F96" s="34"/>
+      <c r="G96" s="35"/>
       <c r="H96" s="47"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="34"/>
-      <c r="B97" s="36" t="s">
+      <c r="A97" s="50"/>
+      <c r="B97" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="37"/>
-      <c r="D97" s="37"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37"/>
-      <c r="G97" s="38"/>
+      <c r="C97" s="34"/>
+      <c r="D97" s="34"/>
+      <c r="E97" s="34"/>
+      <c r="F97" s="34"/>
+      <c r="G97" s="35"/>
       <c r="H97" s="47"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="34"/>
-      <c r="B98" s="36" t="s">
+      <c r="A98" s="50"/>
+      <c r="B98" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
-      <c r="G98" s="38"/>
+      <c r="C98" s="34"/>
+      <c r="D98" s="34"/>
+      <c r="E98" s="34"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="35"/>
       <c r="H98" s="47"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="34"/>
+      <c r="A99" s="50"/>
       <c r="B99" s="2" t="s">
         <v>100</v>
       </c>
@@ -5267,758 +5262,912 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-      <c r="H99" s="40"/>
+      <c r="H99" s="48"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="34">
+      <c r="A100" s="50">
         <v>16</v>
       </c>
-      <c r="B100" s="44" t="s">
+      <c r="B100" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="C100" s="44"/>
-      <c r="D100" s="44"/>
-      <c r="E100" s="44"/>
-      <c r="F100" s="44"/>
-      <c r="G100" s="44"/>
-      <c r="H100" s="22" t="s">
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="34"/>
-      <c r="B101" s="44" t="s">
+      <c r="A101" s="50"/>
+      <c r="B101" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C101" s="44"/>
-      <c r="D101" s="44"/>
-      <c r="E101" s="44"/>
-      <c r="F101" s="44"/>
-      <c r="G101" s="44"/>
-      <c r="H101" s="22"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="21"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="34"/>
-      <c r="B102" s="44" t="s">
+      <c r="A102" s="50"/>
+      <c r="B102" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C102" s="44"/>
-      <c r="D102" s="44"/>
-      <c r="E102" s="44"/>
-      <c r="F102" s="44"/>
-      <c r="G102" s="44"/>
-      <c r="H102" s="22"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="39"/>
+      <c r="G102" s="39"/>
+      <c r="H102" s="21"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="34"/>
-      <c r="B103" s="44" t="s">
+      <c r="A103" s="50"/>
+      <c r="B103" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C103" s="44"/>
-      <c r="D103" s="44"/>
-      <c r="E103" s="44"/>
-      <c r="F103" s="44"/>
-      <c r="G103" s="44"/>
-      <c r="H103" s="22"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="39"/>
+      <c r="E103" s="39"/>
+      <c r="F103" s="39"/>
+      <c r="G103" s="39"/>
+      <c r="H103" s="21"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="34"/>
-      <c r="B104" s="44" t="s">
+      <c r="A104" s="50"/>
+      <c r="B104" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C104" s="44"/>
-      <c r="D104" s="44"/>
-      <c r="E104" s="44"/>
-      <c r="F104" s="44"/>
-      <c r="G104" s="44"/>
-      <c r="H104" s="22"/>
+      <c r="C104" s="39"/>
+      <c r="D104" s="39"/>
+      <c r="E104" s="39"/>
+      <c r="F104" s="39"/>
+      <c r="G104" s="39"/>
+      <c r="H104" s="21"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="34"/>
-      <c r="B105" s="44" t="s">
+      <c r="A105" s="50"/>
+      <c r="B105" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C105" s="44"/>
-      <c r="D105" s="44"/>
-      <c r="E105" s="44"/>
-      <c r="F105" s="44"/>
-      <c r="G105" s="44"/>
-      <c r="H105" s="22"/>
+      <c r="C105" s="39"/>
+      <c r="D105" s="39"/>
+      <c r="E105" s="39"/>
+      <c r="F105" s="39"/>
+      <c r="G105" s="39"/>
+      <c r="H105" s="21"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="34"/>
-      <c r="B106" s="44" t="s">
+      <c r="A106" s="50"/>
+      <c r="B106" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C106" s="44"/>
-      <c r="D106" s="44"/>
-      <c r="E106" s="44"/>
-      <c r="F106" s="44"/>
-      <c r="G106" s="44"/>
-      <c r="H106" s="22"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="39"/>
+      <c r="F106" s="39"/>
+      <c r="G106" s="39"/>
+      <c r="H106" s="21"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="34"/>
-      <c r="B107" s="44" t="s">
+      <c r="A107" s="50"/>
+      <c r="B107" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C107" s="44"/>
-      <c r="D107" s="44"/>
-      <c r="E107" s="44"/>
-      <c r="F107" s="44"/>
-      <c r="G107" s="44"/>
-      <c r="H107" s="22"/>
+      <c r="C107" s="39"/>
+      <c r="D107" s="39"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="39"/>
+      <c r="G107" s="39"/>
+      <c r="H107" s="21"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="34"/>
-      <c r="B108" s="44" t="s">
+      <c r="A108" s="50"/>
+      <c r="B108" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="C108" s="44"/>
-      <c r="D108" s="44"/>
-      <c r="E108" s="44"/>
-      <c r="F108" s="44"/>
-      <c r="G108" s="44"/>
-      <c r="H108" s="22"/>
+      <c r="C108" s="39"/>
+      <c r="D108" s="39"/>
+      <c r="E108" s="39"/>
+      <c r="F108" s="39"/>
+      <c r="G108" s="39"/>
+      <c r="H108" s="21"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="34"/>
-      <c r="B109" s="44" t="s">
+      <c r="A109" s="50"/>
+      <c r="B109" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C109" s="44"/>
-      <c r="D109" s="44"/>
-      <c r="E109" s="44"/>
-      <c r="F109" s="44"/>
-      <c r="G109" s="44"/>
-      <c r="H109" s="22"/>
+      <c r="C109" s="39"/>
+      <c r="D109" s="39"/>
+      <c r="E109" s="39"/>
+      <c r="F109" s="39"/>
+      <c r="G109" s="39"/>
+      <c r="H109" s="21"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="34"/>
-      <c r="B110" s="44" t="s">
+      <c r="A110" s="50"/>
+      <c r="B110" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="C110" s="44"/>
-      <c r="D110" s="44"/>
-      <c r="E110" s="44"/>
-      <c r="F110" s="44"/>
-      <c r="G110" s="44"/>
-      <c r="H110" s="22"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="39"/>
+      <c r="G110" s="39"/>
+      <c r="H110" s="21"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="34"/>
-      <c r="B111" s="44" t="s">
+      <c r="A111" s="50"/>
+      <c r="B111" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C111" s="44"/>
-      <c r="D111" s="44"/>
-      <c r="E111" s="44"/>
-      <c r="F111" s="44"/>
-      <c r="G111" s="44"/>
-      <c r="H111" s="22"/>
+      <c r="C111" s="39"/>
+      <c r="D111" s="39"/>
+      <c r="E111" s="39"/>
+      <c r="F111" s="39"/>
+      <c r="G111" s="39"/>
+      <c r="H111" s="21"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="34"/>
-      <c r="B112" s="44" t="s">
+      <c r="A112" s="50"/>
+      <c r="B112" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C112" s="44"/>
-      <c r="D112" s="44"/>
-      <c r="E112" s="44"/>
-      <c r="F112" s="44"/>
-      <c r="G112" s="44"/>
-      <c r="H112" s="22"/>
+      <c r="C112" s="39"/>
+      <c r="D112" s="39"/>
+      <c r="E112" s="39"/>
+      <c r="F112" s="39"/>
+      <c r="G112" s="39"/>
+      <c r="H112" s="21"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="34"/>
-      <c r="B113" s="45" t="s">
+      <c r="A113" s="50"/>
+      <c r="B113" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="C113" s="45"/>
-      <c r="D113" s="45"/>
-      <c r="E113" s="45"/>
-      <c r="F113" s="45"/>
-      <c r="G113" s="45"/>
-      <c r="H113" s="22"/>
+      <c r="C113" s="41"/>
+      <c r="D113" s="41"/>
+      <c r="E113" s="41"/>
+      <c r="F113" s="41"/>
+      <c r="G113" s="41"/>
+      <c r="H113" s="21"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="34"/>
-      <c r="B114" s="44" t="s">
+      <c r="A114" s="50"/>
+      <c r="B114" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C114" s="44"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="22"/>
+      <c r="C114" s="39"/>
+      <c r="D114" s="39"/>
+      <c r="E114" s="39"/>
+      <c r="F114" s="39"/>
+      <c r="G114" s="39"/>
+      <c r="H114" s="21"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="34"/>
-      <c r="B115" s="44" t="s">
+      <c r="A115" s="50"/>
+      <c r="B115" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C115" s="44"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="44"/>
-      <c r="F115" s="44"/>
-      <c r="G115" s="44"/>
-      <c r="H115" s="22"/>
+      <c r="C115" s="39"/>
+      <c r="D115" s="39"/>
+      <c r="E115" s="39"/>
+      <c r="F115" s="39"/>
+      <c r="G115" s="39"/>
+      <c r="H115" s="21"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="34"/>
-      <c r="B116" s="44" t="s">
+      <c r="A116" s="50"/>
+      <c r="B116" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="C116" s="44"/>
-      <c r="D116" s="44"/>
-      <c r="E116" s="44"/>
-      <c r="F116" s="44"/>
-      <c r="G116" s="44"/>
-      <c r="H116" s="22"/>
+      <c r="C116" s="39"/>
+      <c r="D116" s="39"/>
+      <c r="E116" s="39"/>
+      <c r="F116" s="39"/>
+      <c r="G116" s="39"/>
+      <c r="H116" s="21"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="34"/>
-      <c r="B117" s="44" t="s">
+      <c r="A117" s="50"/>
+      <c r="B117" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C117" s="44"/>
-      <c r="D117" s="44"/>
-      <c r="E117" s="44"/>
-      <c r="F117" s="44"/>
-      <c r="G117" s="44"/>
-      <c r="H117" s="22"/>
+      <c r="C117" s="39"/>
+      <c r="D117" s="39"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="39"/>
+      <c r="G117" s="39"/>
+      <c r="H117" s="21"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="34"/>
-      <c r="B118" s="45" t="s">
+      <c r="A118" s="50"/>
+      <c r="B118" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C118" s="45"/>
-      <c r="D118" s="45"/>
-      <c r="E118" s="45"/>
-      <c r="F118" s="45"/>
-      <c r="G118" s="45"/>
+      <c r="C118" s="41"/>
+      <c r="D118" s="41"/>
+      <c r="E118" s="41"/>
+      <c r="F118" s="41"/>
+      <c r="G118" s="41"/>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="34"/>
-      <c r="B119" s="44" t="s">
+      <c r="A119" s="50"/>
+      <c r="B119" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C119" s="44"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="44"/>
-      <c r="F119" s="44"/>
-      <c r="G119" s="44"/>
-      <c r="H119" s="22" t="s">
+      <c r="C119" s="39"/>
+      <c r="D119" s="39"/>
+      <c r="E119" s="39"/>
+      <c r="F119" s="39"/>
+      <c r="G119" s="39"/>
+      <c r="H119" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="34"/>
-      <c r="B120" s="44" t="s">
+      <c r="A120" s="50"/>
+      <c r="B120" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="C120" s="44"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="44"/>
-      <c r="F120" s="44"/>
-      <c r="G120" s="44"/>
-      <c r="H120" s="22"/>
+      <c r="C120" s="39"/>
+      <c r="D120" s="39"/>
+      <c r="E120" s="39"/>
+      <c r="F120" s="39"/>
+      <c r="G120" s="39"/>
+      <c r="H120" s="21"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="34"/>
-      <c r="B121" s="44" t="s">
+      <c r="A121" s="50"/>
+      <c r="B121" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C121" s="44"/>
-      <c r="D121" s="44"/>
-      <c r="E121" s="44"/>
-      <c r="F121" s="44"/>
-      <c r="G121" s="44"/>
-      <c r="H121" s="22"/>
+      <c r="C121" s="39"/>
+      <c r="D121" s="39"/>
+      <c r="E121" s="39"/>
+      <c r="F121" s="39"/>
+      <c r="G121" s="39"/>
+      <c r="H121" s="21"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="34"/>
-      <c r="B122" s="44" t="s">
+      <c r="A122" s="50"/>
+      <c r="B122" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C122" s="44"/>
-      <c r="D122" s="44"/>
-      <c r="E122" s="44"/>
-      <c r="F122" s="44"/>
-      <c r="G122" s="44"/>
-      <c r="H122" s="22"/>
+      <c r="C122" s="39"/>
+      <c r="D122" s="39"/>
+      <c r="E122" s="39"/>
+      <c r="F122" s="39"/>
+      <c r="G122" s="39"/>
+      <c r="H122" s="21"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="34"/>
-      <c r="B123" s="44" t="s">
+      <c r="A123" s="50"/>
+      <c r="B123" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="C123" s="44"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="44"/>
-      <c r="F123" s="44"/>
-      <c r="G123" s="44"/>
-      <c r="H123" s="22"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="39"/>
+      <c r="E123" s="39"/>
+      <c r="F123" s="39"/>
+      <c r="G123" s="39"/>
+      <c r="H123" s="21"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="34"/>
-      <c r="B124" s="44" t="s">
+      <c r="A124" s="50"/>
+      <c r="B124" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="C124" s="44"/>
-      <c r="D124" s="44"/>
-      <c r="E124" s="44"/>
-      <c r="F124" s="44"/>
-      <c r="G124" s="44"/>
-      <c r="H124" s="22"/>
+      <c r="C124" s="39"/>
+      <c r="D124" s="39"/>
+      <c r="E124" s="39"/>
+      <c r="F124" s="39"/>
+      <c r="G124" s="39"/>
+      <c r="H124" s="21"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="34"/>
-      <c r="B125" s="44" t="s">
+      <c r="A125" s="50"/>
+      <c r="B125" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="C125" s="44"/>
-      <c r="D125" s="44"/>
-      <c r="E125" s="44"/>
-      <c r="F125" s="44"/>
-      <c r="G125" s="44"/>
-      <c r="H125" s="22"/>
+      <c r="C125" s="39"/>
+      <c r="D125" s="39"/>
+      <c r="E125" s="39"/>
+      <c r="F125" s="39"/>
+      <c r="G125" s="39"/>
+      <c r="H125" s="21"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="34"/>
-      <c r="B126" s="20" t="s">
+      <c r="A126" s="50"/>
+      <c r="B126" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C126" s="20"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="22" t="s">
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="16"/>
+      <c r="G126" s="16"/>
+      <c r="H126" s="21" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="34"/>
-      <c r="B127" s="20" t="s">
+      <c r="A127" s="50"/>
+      <c r="B127" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C127" s="20"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="20"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="22"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="16"/>
+      <c r="G127" s="16"/>
+      <c r="H127" s="21"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="34"/>
-      <c r="B128" s="20" t="s">
+      <c r="A128" s="50"/>
+      <c r="B128" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="22"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="16"/>
+      <c r="F128" s="16"/>
+      <c r="G128" s="16"/>
+      <c r="H128" s="21"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="34"/>
-      <c r="B129" s="20" t="s">
+      <c r="A129" s="50"/>
+      <c r="B129" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="22"/>
+      <c r="C129" s="16"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="16"/>
+      <c r="F129" s="16"/>
+      <c r="G129" s="16"/>
+      <c r="H129" s="21"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="34"/>
-      <c r="B130" s="20" t="s">
+      <c r="A130" s="50"/>
+      <c r="B130" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C130" s="20"/>
-      <c r="D130" s="20"/>
-      <c r="E130" s="20"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="22"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="16"/>
+      <c r="G130" s="16"/>
+      <c r="H130" s="21"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="34"/>
-      <c r="B131" s="20" t="s">
+      <c r="A131" s="50"/>
+      <c r="B131" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C131" s="20"/>
-      <c r="D131" s="20"/>
-      <c r="E131" s="20"/>
-      <c r="F131" s="20"/>
-      <c r="G131" s="20"/>
-      <c r="H131" s="22"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
+      <c r="F131" s="16"/>
+      <c r="G131" s="16"/>
+      <c r="H131" s="21"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="34"/>
-      <c r="B132" s="20" t="s">
+      <c r="A132" s="50"/>
+      <c r="B132" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C132" s="20"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="20"/>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="22" t="s">
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="16"/>
+      <c r="G132" s="16"/>
+      <c r="H132" s="21" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="34"/>
-      <c r="B133" s="20" t="s">
+      <c r="A133" s="50"/>
+      <c r="B133" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C133" s="20"/>
-      <c r="D133" s="20"/>
-      <c r="E133" s="20"/>
-      <c r="F133" s="20"/>
-      <c r="G133" s="20"/>
-      <c r="H133" s="22"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="16"/>
+      <c r="F133" s="16"/>
+      <c r="G133" s="16"/>
+      <c r="H133" s="21"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="34"/>
-      <c r="B134" s="20" t="s">
+      <c r="A134" s="50"/>
+      <c r="B134" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C134" s="20"/>
-      <c r="D134" s="20"/>
-      <c r="E134" s="20"/>
-      <c r="F134" s="20"/>
-      <c r="G134" s="20"/>
-      <c r="H134" s="22"/>
+      <c r="C134" s="16"/>
+      <c r="D134" s="16"/>
+      <c r="E134" s="16"/>
+      <c r="F134" s="16"/>
+      <c r="G134" s="16"/>
+      <c r="H134" s="21"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="34"/>
-      <c r="B135" s="20" t="s">
+      <c r="A135" s="50"/>
+      <c r="B135" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C135" s="20"/>
-      <c r="D135" s="20"/>
-      <c r="E135" s="20"/>
-      <c r="F135" s="20"/>
-      <c r="G135" s="20"/>
-      <c r="H135" s="22"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="16"/>
+      <c r="F135" s="16"/>
+      <c r="G135" s="16"/>
+      <c r="H135" s="21"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="35"/>
-      <c r="B136" s="20" t="s">
+      <c r="A136" s="51"/>
+      <c r="B136" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C136" s="20"/>
-      <c r="D136" s="20"/>
-      <c r="E136" s="20"/>
-      <c r="F136" s="20"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="22"/>
+      <c r="C136" s="16"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="16"/>
+      <c r="F136" s="16"/>
+      <c r="G136" s="16"/>
+      <c r="H136" s="21"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="29">
         <v>17</v>
       </c>
-      <c r="B137" s="20" t="s">
+      <c r="B137" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C137" s="20"/>
-      <c r="D137" s="20"/>
-      <c r="E137" s="20"/>
-      <c r="F137" s="20"/>
-      <c r="G137" s="20"/>
-      <c r="H137" s="28" t="s">
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
+      <c r="H137" s="32" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="30"/>
-      <c r="B138" s="20" t="s">
+      <c r="B138" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C138" s="20"/>
-      <c r="D138" s="20"/>
-      <c r="E138" s="20"/>
-      <c r="F138" s="20"/>
-      <c r="G138" s="20"/>
-      <c r="H138" s="28"/>
+      <c r="C138" s="16"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="16"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="16"/>
+      <c r="H138" s="32"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="30"/>
-      <c r="B139" s="20" t="s">
+      <c r="B139" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C139" s="20"/>
-      <c r="D139" s="20"/>
-      <c r="E139" s="20"/>
-      <c r="F139" s="20"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="28"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="16"/>
+      <c r="H139" s="32"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="30"/>
-      <c r="B140" s="20" t="s">
+      <c r="B140" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C140" s="20"/>
-      <c r="D140" s="20"/>
-      <c r="E140" s="20"/>
-      <c r="F140" s="20"/>
-      <c r="G140" s="20"/>
-      <c r="H140" s="28"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
+      <c r="H140" s="32"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="30"/>
-      <c r="B141" s="20" t="s">
+      <c r="B141" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C141" s="20"/>
-      <c r="D141" s="20"/>
-      <c r="E141" s="20"/>
-      <c r="F141" s="20"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="28"/>
+      <c r="C141" s="16"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="16"/>
+      <c r="F141" s="16"/>
+      <c r="G141" s="16"/>
+      <c r="H141" s="32"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="30"/>
-      <c r="B142" s="20" t="s">
+      <c r="B142" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C142" s="20"/>
-      <c r="D142" s="20"/>
-      <c r="E142" s="20"/>
-      <c r="F142" s="20"/>
-      <c r="G142" s="20"/>
-      <c r="H142" s="28"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="16"/>
+      <c r="G142" s="16"/>
+      <c r="H142" s="32"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="30"/>
-      <c r="B143" s="20" t="s">
+      <c r="B143" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C143" s="20"/>
-      <c r="D143" s="20"/>
-      <c r="E143" s="20"/>
-      <c r="F143" s="20"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="28"/>
+      <c r="C143" s="16"/>
+      <c r="D143" s="16"/>
+      <c r="E143" s="16"/>
+      <c r="F143" s="16"/>
+      <c r="G143" s="16"/>
+      <c r="H143" s="32"/>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="30"/>
-      <c r="B144" s="20" t="s">
+      <c r="B144" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C144" s="20"/>
-      <c r="D144" s="20"/>
-      <c r="E144" s="20"/>
-      <c r="F144" s="20"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="28"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="16"/>
+      <c r="E144" s="16"/>
+      <c r="F144" s="16"/>
+      <c r="G144" s="16"/>
+      <c r="H144" s="32"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="30"/>
-      <c r="B145" s="20" t="s">
+      <c r="B145" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C145" s="20"/>
-      <c r="D145" s="20"/>
-      <c r="E145" s="20"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="28"/>
+      <c r="C145" s="16"/>
+      <c r="D145" s="16"/>
+      <c r="E145" s="16"/>
+      <c r="F145" s="16"/>
+      <c r="G145" s="16"/>
+      <c r="H145" s="32"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="30"/>
-      <c r="B146" s="20" t="s">
+      <c r="B146" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C146" s="20"/>
-      <c r="D146" s="20"/>
-      <c r="E146" s="20"/>
-      <c r="F146" s="20"/>
-      <c r="G146" s="20"/>
-      <c r="H146" s="28"/>
+      <c r="C146" s="16"/>
+      <c r="D146" s="16"/>
+      <c r="E146" s="16"/>
+      <c r="F146" s="16"/>
+      <c r="G146" s="16"/>
+      <c r="H146" s="32"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="30"/>
-      <c r="B147" s="20" t="s">
+      <c r="B147" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C147" s="20"/>
-      <c r="D147" s="20"/>
-      <c r="E147" s="20"/>
-      <c r="F147" s="20"/>
-      <c r="G147" s="20"/>
-      <c r="H147" s="28"/>
+      <c r="C147" s="16"/>
+      <c r="D147" s="16"/>
+      <c r="E147" s="16"/>
+      <c r="F147" s="16"/>
+      <c r="G147" s="16"/>
+      <c r="H147" s="32"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="30"/>
-      <c r="B148" s="20" t="s">
+      <c r="B148" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C148" s="20"/>
-      <c r="D148" s="20"/>
-      <c r="E148" s="20"/>
-      <c r="F148" s="20"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="28"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="16"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
+      <c r="H148" s="32"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="30"/>
-      <c r="B149" s="20" t="s">
+      <c r="B149" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C149" s="20"/>
-      <c r="D149" s="20"/>
-      <c r="E149" s="20"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="20"/>
-      <c r="H149" s="28"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
+      <c r="H149" s="32"/>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="30"/>
-      <c r="B150" s="20" t="s">
+      <c r="B150" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C150" s="20"/>
-      <c r="D150" s="20"/>
-      <c r="E150" s="20"/>
-      <c r="F150" s="20"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="28"/>
+      <c r="C150" s="16"/>
+      <c r="D150" s="16"/>
+      <c r="E150" s="16"/>
+      <c r="F150" s="16"/>
+      <c r="G150" s="16"/>
+      <c r="H150" s="32"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="30"/>
-      <c r="B151" s="20" t="s">
+      <c r="B151" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C151" s="20"/>
-      <c r="D151" s="20"/>
-      <c r="E151" s="20"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="20"/>
-      <c r="H151" s="28"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="16"/>
+      <c r="E151" s="16"/>
+      <c r="F151" s="16"/>
+      <c r="G151" s="16"/>
+      <c r="H151" s="32"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="30"/>
-      <c r="B152" s="20" t="s">
+      <c r="B152" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C152" s="20"/>
-      <c r="D152" s="20"/>
-      <c r="E152" s="20"/>
-      <c r="F152" s="20"/>
-      <c r="G152" s="20"/>
-      <c r="H152" s="28"/>
+      <c r="C152" s="16"/>
+      <c r="D152" s="16"/>
+      <c r="E152" s="16"/>
+      <c r="F152" s="16"/>
+      <c r="G152" s="16"/>
+      <c r="H152" s="32"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="30"/>
-      <c r="B153" s="20" t="s">
+      <c r="B153" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C153" s="20"/>
-      <c r="D153" s="20"/>
-      <c r="E153" s="20"/>
-      <c r="F153" s="20"/>
-      <c r="G153" s="20"/>
-      <c r="H153" s="39"/>
+      <c r="C153" s="16"/>
+      <c r="D153" s="16"/>
+      <c r="E153" s="16"/>
+      <c r="F153" s="16"/>
+      <c r="G153" s="16"/>
+      <c r="H153" s="46"/>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="30"/>
-      <c r="B154" s="20" t="s">
+      <c r="B154" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C154" s="20"/>
-      <c r="D154" s="20"/>
-      <c r="E154" s="20"/>
-      <c r="F154" s="20"/>
-      <c r="G154" s="20"/>
-      <c r="H154" s="28" t="s">
+      <c r="C154" s="16"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="16"/>
+      <c r="F154" s="16"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="32" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="30"/>
-      <c r="B155" s="20" t="s">
+      <c r="B155" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C155" s="20"/>
-      <c r="D155" s="20"/>
-      <c r="E155" s="20"/>
-      <c r="F155" s="20"/>
-      <c r="G155" s="20"/>
-      <c r="H155" s="28"/>
+      <c r="C155" s="16"/>
+      <c r="D155" s="16"/>
+      <c r="E155" s="16"/>
+      <c r="F155" s="16"/>
+      <c r="G155" s="16"/>
+      <c r="H155" s="32"/>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="30"/>
-      <c r="B156" s="20" t="s">
+      <c r="B156" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C156" s="20"/>
-      <c r="D156" s="20"/>
-      <c r="E156" s="20"/>
-      <c r="F156" s="20"/>
-      <c r="G156" s="20"/>
-      <c r="H156" s="28"/>
+      <c r="C156" s="16"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="16"/>
+      <c r="F156" s="16"/>
+      <c r="G156" s="16"/>
+      <c r="H156" s="32"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="30"/>
-      <c r="B157" s="20" t="s">
+      <c r="B157" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C157" s="20"/>
-      <c r="D157" s="20"/>
-      <c r="E157" s="20"/>
-      <c r="F157" s="20"/>
-      <c r="G157" s="20"/>
-      <c r="H157" s="28"/>
+      <c r="C157" s="16"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="16"/>
+      <c r="F157" s="16"/>
+      <c r="G157" s="16"/>
+      <c r="H157" s="32"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="30"/>
-      <c r="B158" s="20" t="s">
+      <c r="B158" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C158" s="20"/>
-      <c r="D158" s="20"/>
-      <c r="E158" s="20"/>
-      <c r="F158" s="20"/>
-      <c r="G158" s="20"/>
-      <c r="H158" s="28"/>
+      <c r="C158" s="16"/>
+      <c r="D158" s="16"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="16"/>
+      <c r="G158" s="16"/>
+      <c r="H158" s="32"/>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="31"/>
-      <c r="B159" s="20" t="s">
+      <c r="B159" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C159" s="20"/>
-      <c r="D159" s="20"/>
-      <c r="E159" s="20"/>
-      <c r="F159" s="20"/>
-      <c r="G159" s="20"/>
-      <c r="H159" s="28"/>
+      <c r="C159" s="16"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="16"/>
+      <c r="F159" s="16"/>
+      <c r="G159" s="16"/>
+      <c r="H159" s="32"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B160" s="16"/>
-      <c r="C160" s="16"/>
-      <c r="D160" s="16"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="16"/>
-      <c r="G160" s="16"/>
-      <c r="H160" s="16"/>
+      <c r="B160" s="15"/>
+      <c r="C160" s="15"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="15"/>
+      <c r="F160" s="15"/>
+      <c r="G160" s="15"/>
+      <c r="H160" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="A83:A99"/>
+    <mergeCell ref="A100:A136"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B117:G117"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="B119:G119"/>
+    <mergeCell ref="B108:G108"/>
+    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H2:H11"/>
+    <mergeCell ref="H14:H27"/>
+    <mergeCell ref="A14:A27"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B155:G155"/>
+    <mergeCell ref="B156:G156"/>
+    <mergeCell ref="B157:G157"/>
+    <mergeCell ref="B158:G158"/>
+    <mergeCell ref="A42:A63"/>
+    <mergeCell ref="A64:A82"/>
+    <mergeCell ref="B133:G133"/>
+    <mergeCell ref="B134:G134"/>
+    <mergeCell ref="B135:G135"/>
+    <mergeCell ref="B136:G136"/>
+    <mergeCell ref="B126:G126"/>
+    <mergeCell ref="B127:G127"/>
+    <mergeCell ref="B128:G128"/>
+    <mergeCell ref="B129:G129"/>
+    <mergeCell ref="B130:G130"/>
+    <mergeCell ref="B131:G131"/>
+    <mergeCell ref="B114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="B159:G159"/>
+    <mergeCell ref="H154:H159"/>
+    <mergeCell ref="H126:H131"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="B137:G137"/>
+    <mergeCell ref="B138:G138"/>
+    <mergeCell ref="H137:H153"/>
+    <mergeCell ref="B139:G139"/>
+    <mergeCell ref="B140:G140"/>
+    <mergeCell ref="B141:G141"/>
+    <mergeCell ref="B142:G142"/>
+    <mergeCell ref="B143:G143"/>
+    <mergeCell ref="B144:G144"/>
+    <mergeCell ref="B145:G145"/>
+    <mergeCell ref="B146:G146"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="B148:G148"/>
+    <mergeCell ref="B149:G149"/>
+    <mergeCell ref="B150:G150"/>
+    <mergeCell ref="B151:G151"/>
+    <mergeCell ref="B152:G152"/>
+    <mergeCell ref="B153:G153"/>
+    <mergeCell ref="B154:G154"/>
+    <mergeCell ref="B132:G132"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B89:G89"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="H89:H99"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="H57:H63"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B91:G91"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H42:H56"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="H76:H82"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="B79:G79"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="B82:G82"/>
+    <mergeCell ref="H64:H75"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="H83:H88"/>
+    <mergeCell ref="B110:G110"/>
+    <mergeCell ref="B111:G111"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B97:G97"/>
+    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B113:G113"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B93:G93"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B105:G105"/>
+    <mergeCell ref="B106:G106"/>
+    <mergeCell ref="B107:G107"/>
     <mergeCell ref="B28:G28"/>
     <mergeCell ref="A28:A41"/>
     <mergeCell ref="H28:H41"/>
@@ -6043,160 +6192,6 @@
     <mergeCell ref="B104:G104"/>
     <mergeCell ref="B87:G87"/>
     <mergeCell ref="B88:G88"/>
-    <mergeCell ref="H83:H88"/>
-    <mergeCell ref="B110:G110"/>
-    <mergeCell ref="B111:G111"/>
-    <mergeCell ref="B112:G112"/>
-    <mergeCell ref="B95:G95"/>
-    <mergeCell ref="B96:G96"/>
-    <mergeCell ref="B97:G97"/>
-    <mergeCell ref="B98:G98"/>
-    <mergeCell ref="B113:G113"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="H76:H82"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="B79:G79"/>
-    <mergeCell ref="B80:G80"/>
-    <mergeCell ref="B82:G82"/>
-    <mergeCell ref="H64:H75"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B68:G68"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B92:G92"/>
-    <mergeCell ref="B93:G93"/>
-    <mergeCell ref="B94:G94"/>
-    <mergeCell ref="B105:G105"/>
-    <mergeCell ref="B106:G106"/>
-    <mergeCell ref="B107:G107"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H42:H56"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B89:G89"/>
-    <mergeCell ref="B90:G90"/>
-    <mergeCell ref="H89:H99"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="H57:H63"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B91:G91"/>
-    <mergeCell ref="B159:G159"/>
-    <mergeCell ref="H154:H159"/>
-    <mergeCell ref="H126:H131"/>
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="B137:G137"/>
-    <mergeCell ref="B138:G138"/>
-    <mergeCell ref="H137:H153"/>
-    <mergeCell ref="B139:G139"/>
-    <mergeCell ref="B140:G140"/>
-    <mergeCell ref="B141:G141"/>
-    <mergeCell ref="B142:G142"/>
-    <mergeCell ref="B143:G143"/>
-    <mergeCell ref="B144:G144"/>
-    <mergeCell ref="B145:G145"/>
-    <mergeCell ref="B146:G146"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="B148:G148"/>
-    <mergeCell ref="B149:G149"/>
-    <mergeCell ref="B150:G150"/>
-    <mergeCell ref="B151:G151"/>
-    <mergeCell ref="B152:G152"/>
-    <mergeCell ref="B153:G153"/>
-    <mergeCell ref="B154:G154"/>
-    <mergeCell ref="B132:G132"/>
-    <mergeCell ref="H14:H27"/>
-    <mergeCell ref="A14:A27"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B155:G155"/>
-    <mergeCell ref="B156:G156"/>
-    <mergeCell ref="B157:G157"/>
-    <mergeCell ref="B158:G158"/>
-    <mergeCell ref="A42:A63"/>
-    <mergeCell ref="A64:A82"/>
-    <mergeCell ref="B133:G133"/>
-    <mergeCell ref="B134:G134"/>
-    <mergeCell ref="B135:G135"/>
-    <mergeCell ref="B136:G136"/>
-    <mergeCell ref="B126:G126"/>
-    <mergeCell ref="B127:G127"/>
-    <mergeCell ref="B128:G128"/>
-    <mergeCell ref="B129:G129"/>
-    <mergeCell ref="B130:G130"/>
-    <mergeCell ref="B131:G131"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H2:H11"/>
-    <mergeCell ref="A83:A99"/>
-    <mergeCell ref="A100:A136"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B117:G117"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="B119:G119"/>
-    <mergeCell ref="B108:G108"/>
-    <mergeCell ref="B109:G109"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B42:G42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Java Full Stack_ToC.xlsx
+++ b/Java Full Stack_ToC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\harman_training\Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3895D586-BDBE-4E41-A28B-4ACB68351BB8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB58E9D0-52BD-4BAD-BD4F-453E685A564E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3528" yWindow="1584" windowWidth="19512" windowHeight="10920" activeTab="3" xr2:uid="{650FC967-2F93-46CA-B378-157C068E930D}"/>
   </bookViews>
@@ -1715,20 +1715,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1736,17 +1730,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1757,8 +1751,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1769,8 +1769,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1781,6 +1790,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1790,14 +1811,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1808,26 +1826,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2152,21 +2152,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="2:5">
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="8" t="s">
         <v>165</v>
       </c>
@@ -2175,10 +2175,10 @@
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="18"/>
+      <c r="D3" s="15"/>
       <c r="E3" s="7" t="s">
         <v>177</v>
       </c>
@@ -2187,10 +2187,10 @@
       <c r="B4" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="18"/>
+      <c r="D4" s="15"/>
       <c r="E4" s="7" t="s">
         <v>167</v>
       </c>
@@ -2199,10 +2199,10 @@
       <c r="B5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="18"/>
+      <c r="D5" s="15"/>
       <c r="E5" s="7" t="s">
         <v>172</v>
       </c>
@@ -2211,65 +2211,65 @@
       <c r="B6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="18"/>
+      <c r="D6" s="15"/>
       <c r="E6" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="7" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="13" t="s">
@@ -2278,12 +2278,12 @@
       <c r="C19" s="13"/>
     </row>
     <row r="20" spans="2:5" ht="36" customHeight="1">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="13" t="s">
@@ -2322,12 +2322,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:D10"/>
@@ -2335,6 +2329,12 @@
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B14:E14"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2349,15 +2349,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -2366,894 +2366,945 @@
       <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="16" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="16" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="16" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="16" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="23"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="23"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="23"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="23"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="16" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="23"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="16" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="23"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="16" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="23"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="23"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="23"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="23"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="16" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="23"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="23"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="23"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="23"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="23"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="23"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="23"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="26"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="23"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="16" t="s">
+      <c r="A29" s="26"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="23"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="16" t="s">
+      <c r="A30" s="26"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="16" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="16" t="s">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="17" t="s">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="18"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="16" t="s">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="16" t="s">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="16" t="s">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="16" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="16" t="s">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="16" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="16" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="16" t="s">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="16" t="s">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="16" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="16" t="s">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="16" t="s">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="21"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="16" t="s">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="16" t="s">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="17" t="s">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="18"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="17" t="s">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="18"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="16" t="s">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="16" t="s">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="16" t="s">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="16" t="s">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="16" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="16" t="s">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="16" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="16" t="s">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="16" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="16" t="s">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="16" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="16" t="s">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="21"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="16" t="s">
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="21"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="16" t="s">
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="21"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="16" t="s">
+      <c r="A67" s="22"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="16" t="s">
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="16" t="s">
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="16" t="s">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="16" t="s">
+      <c r="A71" s="22"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="16" t="s">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
-      <c r="C73" s="16" t="s">
+      <c r="A73" s="22"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21"/>
-      <c r="C74" s="16" t="s">
+      <c r="A74" s="22"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="16" t="s">
+      <c r="A75" s="22"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="16" t="s">
+      <c r="A76" s="22"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="16" t="s">
+      <c r="A77" s="22"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="21"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="16" t="s">
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="A66:A78"/>
+    <mergeCell ref="B66:B78"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="A52:A65"/>
+    <mergeCell ref="B52:B65"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="A31:A51"/>
+    <mergeCell ref="B31:B51"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="A11:A30"/>
     <mergeCell ref="B11:B30"/>
@@ -3270,68 +3321,17 @@
     <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="A52:A65"/>
-    <mergeCell ref="B52:B65"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="A31:A51"/>
-    <mergeCell ref="B31:B51"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="A66:A78"/>
-    <mergeCell ref="B66:B78"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3347,15 +3347,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -3364,616 +3364,662 @@
       <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="16" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="16" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="16" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="16" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="16" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="21"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="21"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="21"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="21"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="22"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="21"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="16" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="21"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="16" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="21"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="16" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="21"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="22"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="21"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="21"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="21"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="21"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="21"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="21"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="21"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="22"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="21"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="22"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="21"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="21"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="16" t="s">
+      <c r="A29" s="22"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="21"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="16" t="s">
+      <c r="A30" s="22"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="21"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="16" t="s">
+      <c r="A31" s="22"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="21"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="16" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="21"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="16" t="s">
+      <c r="A33" s="22"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="21"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="16" t="s">
+      <c r="A34" s="22"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="21"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="16" t="s">
+      <c r="A35" s="22"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="22" t="s">
         <v>307</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="21"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="30"/>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="21"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="30"/>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="21"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="30"/>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="21"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="30"/>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="21"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="30"/>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="21"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="30"/>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="21"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="30"/>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="21"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="30"/>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="21"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="30"/>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="21"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="30"/>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="21"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="30"/>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="22" t="s">
         <v>321</v>
       </c>
       <c r="B48" s="30"/>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="21"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="30"/>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
       <c r="H49" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="21"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="30"/>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="21"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="30"/>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="21"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="30"/>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="21"/>
+      <c r="A53" s="22"/>
       <c r="B53" s="30"/>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="21"/>
+      <c r="A54" s="22"/>
       <c r="B54" s="31"/>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="A36:A47"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="B21:B35"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C16:G16"/>
     <mergeCell ref="A3:A20"/>
@@ -3990,52 +4036,6 @@
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="B21:B35"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="A36:A47"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4054,14 +4054,14 @@
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4070,159 +4070,159 @@
       <c r="A2" s="29">
         <v>10</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="21" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="22" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="30"/>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="21"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="30"/>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="21"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="22"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="30"/>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="21"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="30"/>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="21"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="30"/>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="30"/>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="21"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="30"/>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="21"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="30"/>
       <c r="B10" t="s">
         <v>338</v>
       </c>
-      <c r="H10" s="21"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="30"/>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="21"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="1:8" ht="14.55" customHeight="1">
       <c r="A12" s="30"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="46" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="41" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="31"/>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="48"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="42"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="29">
         <v>11</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="35"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="29" t="s">
         <v>140</v>
       </c>
@@ -4241,190 +4241,190 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="30"/>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="35"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="30"/>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="30"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="30"/>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="30"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="30"/>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="35"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="38"/>
       <c r="H19" s="30"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="30"/>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
       <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="30"/>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="35"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="38"/>
       <c r="H21" s="30"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="30"/>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
       <c r="H22" s="30"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="30"/>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="35"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="38"/>
       <c r="H23" s="30"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="30"/>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="38"/>
       <c r="H24" s="30"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="30"/>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="35"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="38"/>
       <c r="H25" s="30"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="30"/>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="31"/>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="35"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="38"/>
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="36">
+      <c r="A28" s="43">
         <v>12</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="36" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="43" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="37"/>
-      <c r="B29" s="33" t="s">
+      <c r="A29" s="44"/>
+      <c r="B29" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="44"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="37"/>
-      <c r="B30" s="33" t="s">
+      <c r="A30" s="44"/>
+      <c r="B30" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="44"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="37"/>
+      <c r="A31" s="44"/>
       <c r="B31" s="4" t="s">
         <v>40</v>
       </c>
@@ -4433,70 +4433,70 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="37"/>
+      <c r="H31" s="44"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="37"/>
-      <c r="B32" s="33" t="s">
+      <c r="A32" s="44"/>
+      <c r="B32" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="44"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="37"/>
-      <c r="B33" s="33" t="s">
+      <c r="A33" s="44"/>
+      <c r="B33" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="44"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="37"/>
-      <c r="B34" s="33" t="s">
+      <c r="A34" s="44"/>
+      <c r="B34" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="44"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="37"/>
-      <c r="B35" s="33" t="s">
+      <c r="A35" s="44"/>
+      <c r="B35" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="44"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="37"/>
-      <c r="B36" s="33" t="s">
+      <c r="A36" s="44"/>
+      <c r="B36" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="44"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="37"/>
+      <c r="A37" s="44"/>
       <c r="B37" s="10" t="s">
         <v>344</v>
       </c>
@@ -4505,755 +4505,755 @@
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="12"/>
-      <c r="H37" s="37"/>
+      <c r="H37" s="44"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="37"/>
-      <c r="B38" s="33" t="s">
+      <c r="A38" s="44"/>
+      <c r="B38" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="44"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="37"/>
-      <c r="B39" s="33" t="s">
+      <c r="A39" s="44"/>
+      <c r="B39" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="44"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="37"/>
-      <c r="B40" s="33" t="s">
+      <c r="A40" s="44"/>
+      <c r="B40" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="44"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="38"/>
-      <c r="B41" s="33" t="s">
+      <c r="A41" s="45"/>
+      <c r="B41" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="38"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="45"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="36">
+      <c r="A42" s="43">
         <v>13</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="36" t="s">
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="43" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="37"/>
-      <c r="B43" s="33" t="s">
+      <c r="A43" s="44"/>
+      <c r="B43" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="44"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="37"/>
-      <c r="B44" s="33" t="s">
+      <c r="A44" s="44"/>
+      <c r="B44" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="37"/>
-      <c r="B45" s="33" t="s">
+      <c r="A45" s="44"/>
+      <c r="B45" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="37"/>
-      <c r="B46" s="33" t="s">
+      <c r="A46" s="44"/>
+      <c r="B46" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="37"/>
-      <c r="B47" s="33" t="s">
+      <c r="A47" s="44"/>
+      <c r="B47" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="44"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="37"/>
-      <c r="B48" s="33" t="s">
+      <c r="A48" s="44"/>
+      <c r="B48" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="44"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="37"/>
-      <c r="B49" s="33" t="s">
+      <c r="A49" s="44"/>
+      <c r="B49" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="44"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="37"/>
-      <c r="B50" s="33" t="s">
+      <c r="A50" s="44"/>
+      <c r="B50" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="44"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="37"/>
-      <c r="B51" s="33" t="s">
+      <c r="A51" s="44"/>
+      <c r="B51" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="44"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="37"/>
-      <c r="B52" s="33" t="s">
+      <c r="A52" s="44"/>
+      <c r="B52" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="44"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="37"/>
-      <c r="B53" s="33" t="s">
+      <c r="A53" s="44"/>
+      <c r="B53" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="37"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="44"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="37"/>
-      <c r="B54" s="33" t="s">
+      <c r="A54" s="44"/>
+      <c r="B54" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="44"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="37"/>
-      <c r="B55" s="33" t="s">
+      <c r="A55" s="44"/>
+      <c r="B55" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="37"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="44"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="37"/>
-      <c r="B56" s="33" t="s">
+      <c r="A56" s="44"/>
+      <c r="B56" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="38"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="45"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="37"/>
-      <c r="B57" s="33" t="s">
+      <c r="A57" s="44"/>
+      <c r="B57" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="36" t="s">
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="43" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="37"/>
-      <c r="B58" s="33" t="s">
+      <c r="A58" s="44"/>
+      <c r="B58" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="44"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="37"/>
-      <c r="B59" s="33" t="s">
+      <c r="A59" s="44"/>
+      <c r="B59" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="44"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="37"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="44"/>
+      <c r="B60" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="37"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="44"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="37"/>
-      <c r="B61" s="33" t="s">
+      <c r="A61" s="44"/>
+      <c r="B61" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="37"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="44"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="37"/>
-      <c r="B62" s="33" t="s">
+      <c r="A62" s="44"/>
+      <c r="B62" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="37"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="44"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="37"/>
-      <c r="B63" s="33" t="s">
+      <c r="A63" s="44"/>
+      <c r="B63" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="38"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="45"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="37">
+      <c r="A64" s="44">
         <v>14</v>
       </c>
-      <c r="B64" s="33" t="s">
+      <c r="B64" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="34"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="42" t="s">
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="48" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="37"/>
-      <c r="B65" s="33" t="s">
+      <c r="A65" s="44"/>
+      <c r="B65" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="34"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="43"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="49"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="37"/>
-      <c r="B66" s="33" t="s">
+      <c r="A66" s="44"/>
+      <c r="B66" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C66" s="34"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="43"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="49"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="37"/>
-      <c r="B67" s="33" t="s">
+      <c r="A67" s="44"/>
+      <c r="B67" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C67" s="34"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="43"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="49"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="37"/>
-      <c r="B68" s="33" t="s">
+      <c r="A68" s="44"/>
+      <c r="B68" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="34"/>
-      <c r="D68" s="34"/>
-      <c r="E68" s="34"/>
-      <c r="F68" s="34"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="43"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="49"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="37"/>
-      <c r="B69" s="33" t="s">
+      <c r="A69" s="44"/>
+      <c r="B69" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="43"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="49"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="37"/>
-      <c r="B70" s="33" t="s">
+      <c r="A70" s="44"/>
+      <c r="B70" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="43"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="49"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="37"/>
-      <c r="B71" s="33" t="s">
+      <c r="A71" s="44"/>
+      <c r="B71" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="43"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="49"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="37"/>
-      <c r="B72" s="33" t="s">
+      <c r="A72" s="44"/>
+      <c r="B72" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="C72" s="34"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="43"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="49"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="37"/>
-      <c r="B73" s="33" t="s">
+      <c r="A73" s="44"/>
+      <c r="B73" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="34"/>
-      <c r="F73" s="34"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="43"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="49"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="37"/>
-      <c r="B74" s="33" t="s">
+      <c r="A74" s="44"/>
+      <c r="B74" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="C74" s="34"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="34"/>
-      <c r="F74" s="34"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="43"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="49"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="37"/>
-      <c r="B75" s="33" t="s">
+      <c r="A75" s="44"/>
+      <c r="B75" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="34"/>
-      <c r="F75" s="34"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="44"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="50"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="37"/>
-      <c r="B76" s="33" t="s">
+      <c r="A76" s="44"/>
+      <c r="B76" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34"/>
-      <c r="E76" s="34"/>
-      <c r="F76" s="34"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="36" t="s">
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="43" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="37"/>
-      <c r="B77" s="33" t="s">
+      <c r="A77" s="44"/>
+      <c r="B77" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="34"/>
-      <c r="D77" s="34"/>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="44"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="37"/>
-      <c r="B78" s="33" t="s">
+      <c r="A78" s="44"/>
+      <c r="B78" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="34"/>
-      <c r="D78" s="34"/>
-      <c r="E78" s="34"/>
-      <c r="F78" s="34"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="44"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="37"/>
-      <c r="B79" s="33" t="s">
+      <c r="A79" s="44"/>
+      <c r="B79" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="34"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="34"/>
-      <c r="F79" s="34"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="44"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="37"/>
-      <c r="B80" s="33" t="s">
+      <c r="A80" s="44"/>
+      <c r="B80" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="34"/>
-      <c r="F80" s="34"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="44"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="37"/>
+      <c r="A81" s="44"/>
       <c r="B81" t="s">
         <v>341</v>
       </c>
-      <c r="H81" s="37"/>
+      <c r="H81" s="44"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="38"/>
-      <c r="B82" s="33" t="s">
+      <c r="A82" s="45"/>
+      <c r="B82" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="34"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="38"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="45"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="49">
+      <c r="A83" s="33">
         <v>15</v>
       </c>
-      <c r="B83" s="40" t="s">
+      <c r="B83" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="40"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="21" t="s">
+      <c r="C83" s="51"/>
+      <c r="D83" s="51"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="51"/>
+      <c r="G83" s="51"/>
+      <c r="H83" s="22" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="50"/>
-      <c r="B84" s="40" t="s">
+      <c r="A84" s="34"/>
+      <c r="B84" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="40"/>
-      <c r="D84" s="40"/>
-      <c r="E84" s="40"/>
-      <c r="F84" s="40"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="21"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="22"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="50"/>
-      <c r="B85" s="40" t="s">
+      <c r="A85" s="34"/>
+      <c r="B85" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="C85" s="40"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="21"/>
+      <c r="C85" s="51"/>
+      <c r="D85" s="51"/>
+      <c r="E85" s="51"/>
+      <c r="F85" s="51"/>
+      <c r="G85" s="51"/>
+      <c r="H85" s="22"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="50"/>
-      <c r="B86" s="40" t="s">
+      <c r="A86" s="34"/>
+      <c r="B86" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="40"/>
-      <c r="D86" s="40"/>
-      <c r="E86" s="40"/>
-      <c r="F86" s="40"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="21"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="22"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="50"/>
-      <c r="B87" s="40" t="s">
+      <c r="A87" s="34"/>
+      <c r="B87" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="C87" s="40"/>
-      <c r="D87" s="40"/>
-      <c r="E87" s="40"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="21"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="22"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="50"/>
-      <c r="B88" s="40" t="s">
+      <c r="A88" s="34"/>
+      <c r="B88" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="40"/>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="21"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="22"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="50"/>
-      <c r="B89" s="33" t="s">
+      <c r="A89" s="34"/>
+      <c r="B89" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="34"/>
-      <c r="D89" s="34"/>
-      <c r="E89" s="34"/>
-      <c r="F89" s="34"/>
-      <c r="G89" s="35"/>
-      <c r="H89" s="46" t="s">
+      <c r="C89" s="37"/>
+      <c r="D89" s="37"/>
+      <c r="E89" s="37"/>
+      <c r="F89" s="37"/>
+      <c r="G89" s="38"/>
+      <c r="H89" s="41" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="50"/>
-      <c r="B90" s="33" t="s">
+      <c r="A90" s="34"/>
+      <c r="B90" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C90" s="34"/>
-      <c r="D90" s="34"/>
-      <c r="E90" s="34"/>
-      <c r="F90" s="34"/>
-      <c r="G90" s="35"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="37"/>
+      <c r="E90" s="37"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="38"/>
       <c r="H90" s="47"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="50"/>
-      <c r="B91" s="33" t="s">
+      <c r="A91" s="34"/>
+      <c r="B91" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="34"/>
-      <c r="D91" s="34"/>
-      <c r="E91" s="34"/>
-      <c r="F91" s="34"/>
-      <c r="G91" s="35"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="38"/>
       <c r="H91" s="47"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="50"/>
-      <c r="B92" s="33" t="s">
+      <c r="A92" s="34"/>
+      <c r="B92" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="34"/>
-      <c r="D92" s="34"/>
-      <c r="E92" s="34"/>
-      <c r="F92" s="34"/>
-      <c r="G92" s="35"/>
+      <c r="C92" s="37"/>
+      <c r="D92" s="37"/>
+      <c r="E92" s="37"/>
+      <c r="F92" s="37"/>
+      <c r="G92" s="38"/>
       <c r="H92" s="47"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="50"/>
-      <c r="B93" s="33" t="s">
+      <c r="A93" s="34"/>
+      <c r="B93" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="34"/>
-      <c r="D93" s="34"/>
-      <c r="E93" s="34"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="35"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="37"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="38"/>
       <c r="H93" s="47"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="50"/>
-      <c r="B94" s="33" t="s">
+      <c r="A94" s="34"/>
+      <c r="B94" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C94" s="34"/>
-      <c r="D94" s="34"/>
-      <c r="E94" s="34"/>
-      <c r="F94" s="34"/>
-      <c r="G94" s="35"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="37"/>
+      <c r="F94" s="37"/>
+      <c r="G94" s="38"/>
       <c r="H94" s="47"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="50"/>
-      <c r="B95" s="33" t="s">
+      <c r="A95" s="34"/>
+      <c r="B95" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="34"/>
-      <c r="D95" s="34"/>
-      <c r="E95" s="34"/>
-      <c r="F95" s="34"/>
-      <c r="G95" s="35"/>
+      <c r="C95" s="37"/>
+      <c r="D95" s="37"/>
+      <c r="E95" s="37"/>
+      <c r="F95" s="37"/>
+      <c r="G95" s="38"/>
       <c r="H95" s="47"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="50"/>
-      <c r="B96" s="33" t="s">
+      <c r="A96" s="34"/>
+      <c r="B96" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="34"/>
-      <c r="D96" s="34"/>
-      <c r="E96" s="34"/>
-      <c r="F96" s="34"/>
-      <c r="G96" s="35"/>
+      <c r="C96" s="37"/>
+      <c r="D96" s="37"/>
+      <c r="E96" s="37"/>
+      <c r="F96" s="37"/>
+      <c r="G96" s="38"/>
       <c r="H96" s="47"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="50"/>
-      <c r="B97" s="33" t="s">
+      <c r="A97" s="34"/>
+      <c r="B97" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="34"/>
-      <c r="D97" s="34"/>
-      <c r="E97" s="34"/>
-      <c r="F97" s="34"/>
-      <c r="G97" s="35"/>
+      <c r="C97" s="37"/>
+      <c r="D97" s="37"/>
+      <c r="E97" s="37"/>
+      <c r="F97" s="37"/>
+      <c r="G97" s="38"/>
       <c r="H97" s="47"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="50"/>
-      <c r="B98" s="33" t="s">
+      <c r="A98" s="34"/>
+      <c r="B98" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C98" s="34"/>
-      <c r="D98" s="34"/>
-      <c r="E98" s="34"/>
-      <c r="F98" s="34"/>
-      <c r="G98" s="35"/>
+      <c r="C98" s="37"/>
+      <c r="D98" s="37"/>
+      <c r="E98" s="37"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="38"/>
       <c r="H98" s="47"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="50"/>
+      <c r="A99" s="34"/>
       <c r="B99" s="2" t="s">
         <v>100</v>
       </c>
@@ -5262,10 +5262,10 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-      <c r="H99" s="48"/>
+      <c r="H99" s="42"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="50">
+      <c r="A100" s="34">
         <v>16</v>
       </c>
       <c r="B100" s="39" t="s">
@@ -5276,12 +5276,12 @@
       <c r="E100" s="39"/>
       <c r="F100" s="39"/>
       <c r="G100" s="39"/>
-      <c r="H100" s="21" t="s">
+      <c r="H100" s="22" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="50"/>
+      <c r="A101" s="34"/>
       <c r="B101" s="39" t="s">
         <v>56</v>
       </c>
@@ -5290,10 +5290,10 @@
       <c r="E101" s="39"/>
       <c r="F101" s="39"/>
       <c r="G101" s="39"/>
-      <c r="H101" s="21"/>
+      <c r="H101" s="22"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="50"/>
+      <c r="A102" s="34"/>
       <c r="B102" s="39" t="s">
         <v>57</v>
       </c>
@@ -5302,10 +5302,10 @@
       <c r="E102" s="39"/>
       <c r="F102" s="39"/>
       <c r="G102" s="39"/>
-      <c r="H102" s="21"/>
+      <c r="H102" s="22"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="50"/>
+      <c r="A103" s="34"/>
       <c r="B103" s="39" t="s">
         <v>58</v>
       </c>
@@ -5314,10 +5314,10 @@
       <c r="E103" s="39"/>
       <c r="F103" s="39"/>
       <c r="G103" s="39"/>
-      <c r="H103" s="21"/>
+      <c r="H103" s="22"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="50"/>
+      <c r="A104" s="34"/>
       <c r="B104" s="39" t="s">
         <v>59</v>
       </c>
@@ -5326,10 +5326,10 @@
       <c r="E104" s="39"/>
       <c r="F104" s="39"/>
       <c r="G104" s="39"/>
-      <c r="H104" s="21"/>
+      <c r="H104" s="22"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="50"/>
+      <c r="A105" s="34"/>
       <c r="B105" s="39" t="s">
         <v>60</v>
       </c>
@@ -5338,10 +5338,10 @@
       <c r="E105" s="39"/>
       <c r="F105" s="39"/>
       <c r="G105" s="39"/>
-      <c r="H105" s="21"/>
+      <c r="H105" s="22"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="50"/>
+      <c r="A106" s="34"/>
       <c r="B106" s="39" t="s">
         <v>61</v>
       </c>
@@ -5350,10 +5350,10 @@
       <c r="E106" s="39"/>
       <c r="F106" s="39"/>
       <c r="G106" s="39"/>
-      <c r="H106" s="21"/>
+      <c r="H106" s="22"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="50"/>
+      <c r="A107" s="34"/>
       <c r="B107" s="39" t="s">
         <v>62</v>
       </c>
@@ -5362,10 +5362,10 @@
       <c r="E107" s="39"/>
       <c r="F107" s="39"/>
       <c r="G107" s="39"/>
-      <c r="H107" s="21"/>
+      <c r="H107" s="22"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="50"/>
+      <c r="A108" s="34"/>
       <c r="B108" s="39" t="s">
         <v>63</v>
       </c>
@@ -5374,10 +5374,10 @@
       <c r="E108" s="39"/>
       <c r="F108" s="39"/>
       <c r="G108" s="39"/>
-      <c r="H108" s="21"/>
+      <c r="H108" s="22"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="50"/>
+      <c r="A109" s="34"/>
       <c r="B109" s="39" t="s">
         <v>65</v>
       </c>
@@ -5386,10 +5386,10 @@
       <c r="E109" s="39"/>
       <c r="F109" s="39"/>
       <c r="G109" s="39"/>
-      <c r="H109" s="21"/>
+      <c r="H109" s="22"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="50"/>
+      <c r="A110" s="34"/>
       <c r="B110" s="39" t="s">
         <v>66</v>
       </c>
@@ -5398,10 +5398,10 @@
       <c r="E110" s="39"/>
       <c r="F110" s="39"/>
       <c r="G110" s="39"/>
-      <c r="H110" s="21"/>
+      <c r="H110" s="22"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="50"/>
+      <c r="A111" s="34"/>
       <c r="B111" s="39" t="s">
         <v>67</v>
       </c>
@@ -5410,10 +5410,10 @@
       <c r="E111" s="39"/>
       <c r="F111" s="39"/>
       <c r="G111" s="39"/>
-      <c r="H111" s="21"/>
+      <c r="H111" s="22"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="50"/>
+      <c r="A112" s="34"/>
       <c r="B112" s="39" t="s">
         <v>69</v>
       </c>
@@ -5422,22 +5422,22 @@
       <c r="E112" s="39"/>
       <c r="F112" s="39"/>
       <c r="G112" s="39"/>
-      <c r="H112" s="21"/>
+      <c r="H112" s="22"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="50"/>
-      <c r="B113" s="41" t="s">
+      <c r="A113" s="34"/>
+      <c r="B113" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="41"/>
-      <c r="E113" s="41"/>
-      <c r="F113" s="41"/>
-      <c r="G113" s="41"/>
-      <c r="H113" s="21"/>
+      <c r="C113" s="40"/>
+      <c r="D113" s="40"/>
+      <c r="E113" s="40"/>
+      <c r="F113" s="40"/>
+      <c r="G113" s="40"/>
+      <c r="H113" s="22"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="50"/>
+      <c r="A114" s="34"/>
       <c r="B114" s="39" t="s">
         <v>68</v>
       </c>
@@ -5446,10 +5446,10 @@
       <c r="E114" s="39"/>
       <c r="F114" s="39"/>
       <c r="G114" s="39"/>
-      <c r="H114" s="21"/>
+      <c r="H114" s="22"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="50"/>
+      <c r="A115" s="34"/>
       <c r="B115" s="39" t="s">
         <v>71</v>
       </c>
@@ -5458,10 +5458,10 @@
       <c r="E115" s="39"/>
       <c r="F115" s="39"/>
       <c r="G115" s="39"/>
-      <c r="H115" s="21"/>
+      <c r="H115" s="22"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="50"/>
+      <c r="A116" s="34"/>
       <c r="B116" s="39" t="s">
         <v>72</v>
       </c>
@@ -5470,10 +5470,10 @@
       <c r="E116" s="39"/>
       <c r="F116" s="39"/>
       <c r="G116" s="39"/>
-      <c r="H116" s="21"/>
+      <c r="H116" s="22"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="50"/>
+      <c r="A117" s="34"/>
       <c r="B117" s="39" t="s">
         <v>73</v>
       </c>
@@ -5482,22 +5482,22 @@
       <c r="E117" s="39"/>
       <c r="F117" s="39"/>
       <c r="G117" s="39"/>
-      <c r="H117" s="21"/>
+      <c r="H117" s="22"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="50"/>
-      <c r="B118" s="41" t="s">
+      <c r="A118" s="34"/>
+      <c r="B118" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C118" s="41"/>
-      <c r="D118" s="41"/>
-      <c r="E118" s="41"/>
-      <c r="F118" s="41"/>
-      <c r="G118" s="41"/>
+      <c r="C118" s="40"/>
+      <c r="D118" s="40"/>
+      <c r="E118" s="40"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="40"/>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="50"/>
+      <c r="A119" s="34"/>
       <c r="B119" s="39" t="s">
         <v>75</v>
       </c>
@@ -5506,12 +5506,12 @@
       <c r="E119" s="39"/>
       <c r="F119" s="39"/>
       <c r="G119" s="39"/>
-      <c r="H119" s="21" t="s">
+      <c r="H119" s="22" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="50"/>
+      <c r="A120" s="34"/>
       <c r="B120" s="39" t="s">
         <v>76</v>
       </c>
@@ -5520,10 +5520,10 @@
       <c r="E120" s="39"/>
       <c r="F120" s="39"/>
       <c r="G120" s="39"/>
-      <c r="H120" s="21"/>
+      <c r="H120" s="22"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="50"/>
+      <c r="A121" s="34"/>
       <c r="B121" s="39" t="s">
         <v>77</v>
       </c>
@@ -5532,10 +5532,10 @@
       <c r="E121" s="39"/>
       <c r="F121" s="39"/>
       <c r="G121" s="39"/>
-      <c r="H121" s="21"/>
+      <c r="H121" s="22"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="50"/>
+      <c r="A122" s="34"/>
       <c r="B122" s="39" t="s">
         <v>78</v>
       </c>
@@ -5544,10 +5544,10 @@
       <c r="E122" s="39"/>
       <c r="F122" s="39"/>
       <c r="G122" s="39"/>
-      <c r="H122" s="21"/>
+      <c r="H122" s="22"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="50"/>
+      <c r="A123" s="34"/>
       <c r="B123" s="39" t="s">
         <v>79</v>
       </c>
@@ -5556,10 +5556,10 @@
       <c r="E123" s="39"/>
       <c r="F123" s="39"/>
       <c r="G123" s="39"/>
-      <c r="H123" s="21"/>
+      <c r="H123" s="22"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="50"/>
+      <c r="A124" s="34"/>
       <c r="B124" s="39" t="s">
         <v>80</v>
       </c>
@@ -5568,10 +5568,10 @@
       <c r="E124" s="39"/>
       <c r="F124" s="39"/>
       <c r="G124" s="39"/>
-      <c r="H124" s="21"/>
+      <c r="H124" s="22"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="50"/>
+      <c r="A125" s="34"/>
       <c r="B125" s="39" t="s">
         <v>81</v>
       </c>
@@ -5580,440 +5580,594 @@
       <c r="E125" s="39"/>
       <c r="F125" s="39"/>
       <c r="G125" s="39"/>
-      <c r="H125" s="21"/>
+      <c r="H125" s="22"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="50"/>
-      <c r="B126" s="16" t="s">
+      <c r="A126" s="34"/>
+      <c r="B126" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C126" s="16"/>
-      <c r="D126" s="16"/>
-      <c r="E126" s="16"/>
-      <c r="F126" s="16"/>
-      <c r="G126" s="16"/>
-      <c r="H126" s="21" t="s">
+      <c r="C126" s="20"/>
+      <c r="D126" s="20"/>
+      <c r="E126" s="20"/>
+      <c r="F126" s="20"/>
+      <c r="G126" s="20"/>
+      <c r="H126" s="22" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="50"/>
-      <c r="B127" s="16" t="s">
+      <c r="A127" s="34"/>
+      <c r="B127" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="C127" s="16"/>
-      <c r="D127" s="16"/>
-      <c r="E127" s="16"/>
-      <c r="F127" s="16"/>
-      <c r="G127" s="16"/>
-      <c r="H127" s="21"/>
+      <c r="C127" s="20"/>
+      <c r="D127" s="20"/>
+      <c r="E127" s="20"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="20"/>
+      <c r="H127" s="22"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="50"/>
-      <c r="B128" s="16" t="s">
+      <c r="A128" s="34"/>
+      <c r="B128" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="C128" s="16"/>
-      <c r="D128" s="16"/>
-      <c r="E128" s="16"/>
-      <c r="F128" s="16"/>
-      <c r="G128" s="16"/>
-      <c r="H128" s="21"/>
+      <c r="C128" s="20"/>
+      <c r="D128" s="20"/>
+      <c r="E128" s="20"/>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20"/>
+      <c r="H128" s="22"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="50"/>
-      <c r="B129" s="16" t="s">
+      <c r="A129" s="34"/>
+      <c r="B129" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C129" s="16"/>
-      <c r="D129" s="16"/>
-      <c r="E129" s="16"/>
-      <c r="F129" s="16"/>
-      <c r="G129" s="16"/>
-      <c r="H129" s="21"/>
+      <c r="C129" s="20"/>
+      <c r="D129" s="20"/>
+      <c r="E129" s="20"/>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="22"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="50"/>
-      <c r="B130" s="16" t="s">
+      <c r="A130" s="34"/>
+      <c r="B130" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C130" s="16"/>
-      <c r="D130" s="16"/>
-      <c r="E130" s="16"/>
-      <c r="F130" s="16"/>
-      <c r="G130" s="16"/>
-      <c r="H130" s="21"/>
+      <c r="C130" s="20"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="20"/>
+      <c r="F130" s="20"/>
+      <c r="G130" s="20"/>
+      <c r="H130" s="22"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="50"/>
-      <c r="B131" s="16" t="s">
+      <c r="A131" s="34"/>
+      <c r="B131" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="C131" s="16"/>
-      <c r="D131" s="16"/>
-      <c r="E131" s="16"/>
-      <c r="F131" s="16"/>
-      <c r="G131" s="16"/>
-      <c r="H131" s="21"/>
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="20"/>
+      <c r="G131" s="20"/>
+      <c r="H131" s="22"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="50"/>
-      <c r="B132" s="16" t="s">
+      <c r="A132" s="34"/>
+      <c r="B132" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="C132" s="16"/>
-      <c r="D132" s="16"/>
-      <c r="E132" s="16"/>
-      <c r="F132" s="16"/>
-      <c r="G132" s="16"/>
-      <c r="H132" s="21" t="s">
+      <c r="C132" s="20"/>
+      <c r="D132" s="20"/>
+      <c r="E132" s="20"/>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="22" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="50"/>
-      <c r="B133" s="16" t="s">
+      <c r="A133" s="34"/>
+      <c r="B133" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C133" s="16"/>
-      <c r="D133" s="16"/>
-      <c r="E133" s="16"/>
-      <c r="F133" s="16"/>
-      <c r="G133" s="16"/>
-      <c r="H133" s="21"/>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
+      <c r="E133" s="20"/>
+      <c r="F133" s="20"/>
+      <c r="G133" s="20"/>
+      <c r="H133" s="22"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="50"/>
-      <c r="B134" s="16" t="s">
+      <c r="A134" s="34"/>
+      <c r="B134" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C134" s="16"/>
-      <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
-      <c r="F134" s="16"/>
-      <c r="G134" s="16"/>
-      <c r="H134" s="21"/>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20"/>
+      <c r="G134" s="20"/>
+      <c r="H134" s="22"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="50"/>
-      <c r="B135" s="16" t="s">
+      <c r="A135" s="34"/>
+      <c r="B135" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="C135" s="16"/>
-      <c r="D135" s="16"/>
-      <c r="E135" s="16"/>
-      <c r="F135" s="16"/>
-      <c r="G135" s="16"/>
-      <c r="H135" s="21"/>
+      <c r="C135" s="20"/>
+      <c r="D135" s="20"/>
+      <c r="E135" s="20"/>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="22"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="51"/>
-      <c r="B136" s="16" t="s">
+      <c r="A136" s="35"/>
+      <c r="B136" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C136" s="16"/>
-      <c r="D136" s="16"/>
-      <c r="E136" s="16"/>
-      <c r="F136" s="16"/>
-      <c r="G136" s="16"/>
-      <c r="H136" s="21"/>
+      <c r="C136" s="20"/>
+      <c r="D136" s="20"/>
+      <c r="E136" s="20"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20"/>
+      <c r="H136" s="22"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="29">
         <v>17</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C137" s="16"/>
-      <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="16"/>
-      <c r="G137" s="16"/>
-      <c r="H137" s="32" t="s">
+      <c r="C137" s="20"/>
+      <c r="D137" s="20"/>
+      <c r="E137" s="20"/>
+      <c r="F137" s="20"/>
+      <c r="G137" s="20"/>
+      <c r="H137" s="28" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="30"/>
-      <c r="B138" s="16" t="s">
+      <c r="B138" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C138" s="16"/>
-      <c r="D138" s="16"/>
-      <c r="E138" s="16"/>
-      <c r="F138" s="16"/>
-      <c r="G138" s="16"/>
-      <c r="H138" s="32"/>
+      <c r="C138" s="20"/>
+      <c r="D138" s="20"/>
+      <c r="E138" s="20"/>
+      <c r="F138" s="20"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="28"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="30"/>
-      <c r="B139" s="16" t="s">
+      <c r="B139" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C139" s="16"/>
-      <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="16"/>
-      <c r="G139" s="16"/>
-      <c r="H139" s="32"/>
+      <c r="C139" s="20"/>
+      <c r="D139" s="20"/>
+      <c r="E139" s="20"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="20"/>
+      <c r="H139" s="28"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="30"/>
-      <c r="B140" s="16" t="s">
+      <c r="B140" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C140" s="16"/>
-      <c r="D140" s="16"/>
-      <c r="E140" s="16"/>
-      <c r="F140" s="16"/>
-      <c r="G140" s="16"/>
-      <c r="H140" s="32"/>
+      <c r="C140" s="20"/>
+      <c r="D140" s="20"/>
+      <c r="E140" s="20"/>
+      <c r="F140" s="20"/>
+      <c r="G140" s="20"/>
+      <c r="H140" s="28"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="30"/>
-      <c r="B141" s="16" t="s">
+      <c r="B141" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C141" s="16"/>
-      <c r="D141" s="16"/>
-      <c r="E141" s="16"/>
-      <c r="F141" s="16"/>
-      <c r="G141" s="16"/>
-      <c r="H141" s="32"/>
+      <c r="C141" s="20"/>
+      <c r="D141" s="20"/>
+      <c r="E141" s="20"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="28"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="30"/>
-      <c r="B142" s="16" t="s">
+      <c r="B142" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C142" s="16"/>
-      <c r="D142" s="16"/>
-      <c r="E142" s="16"/>
-      <c r="F142" s="16"/>
-      <c r="G142" s="16"/>
-      <c r="H142" s="32"/>
+      <c r="C142" s="20"/>
+      <c r="D142" s="20"/>
+      <c r="E142" s="20"/>
+      <c r="F142" s="20"/>
+      <c r="G142" s="20"/>
+      <c r="H142" s="28"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="30"/>
-      <c r="B143" s="16" t="s">
+      <c r="B143" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C143" s="16"/>
-      <c r="D143" s="16"/>
-      <c r="E143" s="16"/>
-      <c r="F143" s="16"/>
-      <c r="G143" s="16"/>
-      <c r="H143" s="32"/>
+      <c r="C143" s="20"/>
+      <c r="D143" s="20"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="20"/>
+      <c r="G143" s="20"/>
+      <c r="H143" s="28"/>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="30"/>
-      <c r="B144" s="16" t="s">
+      <c r="B144" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C144" s="16"/>
-      <c r="D144" s="16"/>
-      <c r="E144" s="16"/>
-      <c r="F144" s="16"/>
-      <c r="G144" s="16"/>
-      <c r="H144" s="32"/>
+      <c r="C144" s="20"/>
+      <c r="D144" s="20"/>
+      <c r="E144" s="20"/>
+      <c r="F144" s="20"/>
+      <c r="G144" s="20"/>
+      <c r="H144" s="28"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="30"/>
-      <c r="B145" s="16" t="s">
+      <c r="B145" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C145" s="16"/>
-      <c r="D145" s="16"/>
-      <c r="E145" s="16"/>
-      <c r="F145" s="16"/>
-      <c r="G145" s="16"/>
-      <c r="H145" s="32"/>
+      <c r="C145" s="20"/>
+      <c r="D145" s="20"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="20"/>
+      <c r="G145" s="20"/>
+      <c r="H145" s="28"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="30"/>
-      <c r="B146" s="16" t="s">
+      <c r="B146" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C146" s="16"/>
-      <c r="D146" s="16"/>
-      <c r="E146" s="16"/>
-      <c r="F146" s="16"/>
-      <c r="G146" s="16"/>
-      <c r="H146" s="32"/>
+      <c r="C146" s="20"/>
+      <c r="D146" s="20"/>
+      <c r="E146" s="20"/>
+      <c r="F146" s="20"/>
+      <c r="G146" s="20"/>
+      <c r="H146" s="28"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="30"/>
-      <c r="B147" s="16" t="s">
+      <c r="B147" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C147" s="16"/>
-      <c r="D147" s="16"/>
-      <c r="E147" s="16"/>
-      <c r="F147" s="16"/>
-      <c r="G147" s="16"/>
-      <c r="H147" s="32"/>
+      <c r="C147" s="20"/>
+      <c r="D147" s="20"/>
+      <c r="E147" s="20"/>
+      <c r="F147" s="20"/>
+      <c r="G147" s="20"/>
+      <c r="H147" s="28"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="30"/>
-      <c r="B148" s="16" t="s">
+      <c r="B148" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C148" s="16"/>
-      <c r="D148" s="16"/>
-      <c r="E148" s="16"/>
-      <c r="F148" s="16"/>
-      <c r="G148" s="16"/>
-      <c r="H148" s="32"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20"/>
+      <c r="E148" s="20"/>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="28"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="30"/>
-      <c r="B149" s="16" t="s">
+      <c r="B149" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C149" s="16"/>
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="16"/>
-      <c r="G149" s="16"/>
-      <c r="H149" s="32"/>
+      <c r="C149" s="20"/>
+      <c r="D149" s="20"/>
+      <c r="E149" s="20"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="20"/>
+      <c r="H149" s="28"/>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="30"/>
-      <c r="B150" s="16" t="s">
+      <c r="B150" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C150" s="16"/>
-      <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
-      <c r="F150" s="16"/>
-      <c r="G150" s="16"/>
-      <c r="H150" s="32"/>
+      <c r="C150" s="20"/>
+      <c r="D150" s="20"/>
+      <c r="E150" s="20"/>
+      <c r="F150" s="20"/>
+      <c r="G150" s="20"/>
+      <c r="H150" s="28"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="30"/>
-      <c r="B151" s="16" t="s">
+      <c r="B151" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C151" s="16"/>
-      <c r="D151" s="16"/>
-      <c r="E151" s="16"/>
-      <c r="F151" s="16"/>
-      <c r="G151" s="16"/>
-      <c r="H151" s="32"/>
+      <c r="C151" s="20"/>
+      <c r="D151" s="20"/>
+      <c r="E151" s="20"/>
+      <c r="F151" s="20"/>
+      <c r="G151" s="20"/>
+      <c r="H151" s="28"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="30"/>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C152" s="16"/>
-      <c r="D152" s="16"/>
-      <c r="E152" s="16"/>
-      <c r="F152" s="16"/>
-      <c r="G152" s="16"/>
-      <c r="H152" s="32"/>
+      <c r="C152" s="20"/>
+      <c r="D152" s="20"/>
+      <c r="E152" s="20"/>
+      <c r="F152" s="20"/>
+      <c r="G152" s="20"/>
+      <c r="H152" s="28"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="30"/>
-      <c r="B153" s="16" t="s">
+      <c r="B153" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C153" s="16"/>
-      <c r="D153" s="16"/>
-      <c r="E153" s="16"/>
-      <c r="F153" s="16"/>
-      <c r="G153" s="16"/>
-      <c r="H153" s="46"/>
+      <c r="C153" s="20"/>
+      <c r="D153" s="20"/>
+      <c r="E153" s="20"/>
+      <c r="F153" s="20"/>
+      <c r="G153" s="20"/>
+      <c r="H153" s="41"/>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="30"/>
-      <c r="B154" s="16" t="s">
+      <c r="B154" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C154" s="16"/>
-      <c r="D154" s="16"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="16"/>
-      <c r="G154" s="16"/>
-      <c r="H154" s="32" t="s">
+      <c r="C154" s="20"/>
+      <c r="D154" s="20"/>
+      <c r="E154" s="20"/>
+      <c r="F154" s="20"/>
+      <c r="G154" s="20"/>
+      <c r="H154" s="28" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="30"/>
-      <c r="B155" s="16" t="s">
+      <c r="B155" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C155" s="16"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="16"/>
-      <c r="H155" s="32"/>
+      <c r="C155" s="20"/>
+      <c r="D155" s="20"/>
+      <c r="E155" s="20"/>
+      <c r="F155" s="20"/>
+      <c r="G155" s="20"/>
+      <c r="H155" s="28"/>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="30"/>
-      <c r="B156" s="16" t="s">
+      <c r="B156" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C156" s="16"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="16"/>
-      <c r="G156" s="16"/>
-      <c r="H156" s="32"/>
+      <c r="C156" s="20"/>
+      <c r="D156" s="20"/>
+      <c r="E156" s="20"/>
+      <c r="F156" s="20"/>
+      <c r="G156" s="20"/>
+      <c r="H156" s="28"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="30"/>
-      <c r="B157" s="16" t="s">
+      <c r="B157" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C157" s="16"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="16"/>
-      <c r="G157" s="16"/>
-      <c r="H157" s="32"/>
+      <c r="C157" s="20"/>
+      <c r="D157" s="20"/>
+      <c r="E157" s="20"/>
+      <c r="F157" s="20"/>
+      <c r="G157" s="20"/>
+      <c r="H157" s="28"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="30"/>
-      <c r="B158" s="16" t="s">
+      <c r="B158" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C158" s="16"/>
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="16"/>
-      <c r="G158" s="16"/>
-      <c r="H158" s="32"/>
+      <c r="C158" s="20"/>
+      <c r="D158" s="20"/>
+      <c r="E158" s="20"/>
+      <c r="F158" s="20"/>
+      <c r="G158" s="20"/>
+      <c r="H158" s="28"/>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="31"/>
-      <c r="B159" s="16" t="s">
+      <c r="B159" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C159" s="16"/>
-      <c r="D159" s="16"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="16"/>
-      <c r="G159" s="16"/>
-      <c r="H159" s="32"/>
+      <c r="C159" s="20"/>
+      <c r="D159" s="20"/>
+      <c r="E159" s="20"/>
+      <c r="F159" s="20"/>
+      <c r="G159" s="20"/>
+      <c r="H159" s="28"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="15" t="s">
+      <c r="A160" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B160" s="15"/>
-      <c r="C160" s="15"/>
-      <c r="D160" s="15"/>
-      <c r="E160" s="15"/>
-      <c r="F160" s="15"/>
-      <c r="G160" s="15"/>
-      <c r="H160" s="15"/>
+      <c r="B160" s="16"/>
+      <c r="C160" s="16"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="16"/>
+      <c r="F160" s="16"/>
+      <c r="G160" s="16"/>
+      <c r="H160" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A28:A41"/>
+    <mergeCell ref="H28:H41"/>
+    <mergeCell ref="A137:A159"/>
+    <mergeCell ref="A160:H160"/>
+    <mergeCell ref="H119:H125"/>
+    <mergeCell ref="B120:G120"/>
+    <mergeCell ref="B121:G121"/>
+    <mergeCell ref="B122:G122"/>
+    <mergeCell ref="B123:G123"/>
+    <mergeCell ref="B124:G124"/>
+    <mergeCell ref="B125:G125"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="H100:H118"/>
+    <mergeCell ref="B101:G101"/>
+    <mergeCell ref="B102:G102"/>
+    <mergeCell ref="B103:G103"/>
+    <mergeCell ref="B83:G83"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="B85:G85"/>
+    <mergeCell ref="B86:G86"/>
+    <mergeCell ref="B104:G104"/>
+    <mergeCell ref="B87:G87"/>
+    <mergeCell ref="B88:G88"/>
+    <mergeCell ref="H83:H88"/>
+    <mergeCell ref="B110:G110"/>
+    <mergeCell ref="B111:G111"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B97:G97"/>
+    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B113:G113"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B93:G93"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B105:G105"/>
+    <mergeCell ref="B106:G106"/>
+    <mergeCell ref="B107:G107"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="H76:H82"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="B79:G79"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="B82:G82"/>
+    <mergeCell ref="H64:H75"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H42:H56"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B89:G89"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="H89:H99"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="H57:H63"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B91:G91"/>
+    <mergeCell ref="B159:G159"/>
+    <mergeCell ref="H154:H159"/>
+    <mergeCell ref="H126:H131"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="B137:G137"/>
+    <mergeCell ref="B138:G138"/>
+    <mergeCell ref="H137:H153"/>
+    <mergeCell ref="B139:G139"/>
+    <mergeCell ref="B140:G140"/>
+    <mergeCell ref="B141:G141"/>
+    <mergeCell ref="B142:G142"/>
+    <mergeCell ref="B143:G143"/>
+    <mergeCell ref="B144:G144"/>
+    <mergeCell ref="B145:G145"/>
+    <mergeCell ref="B146:G146"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="B148:G148"/>
+    <mergeCell ref="B149:G149"/>
+    <mergeCell ref="B150:G150"/>
+    <mergeCell ref="B151:G151"/>
+    <mergeCell ref="B152:G152"/>
+    <mergeCell ref="B153:G153"/>
+    <mergeCell ref="B154:G154"/>
+    <mergeCell ref="B132:G132"/>
+    <mergeCell ref="H14:H27"/>
+    <mergeCell ref="A14:A27"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B155:G155"/>
+    <mergeCell ref="B156:G156"/>
+    <mergeCell ref="B157:G157"/>
+    <mergeCell ref="B158:G158"/>
+    <mergeCell ref="A42:A63"/>
+    <mergeCell ref="A64:A82"/>
+    <mergeCell ref="B133:G133"/>
+    <mergeCell ref="B134:G134"/>
+    <mergeCell ref="B135:G135"/>
+    <mergeCell ref="B136:G136"/>
+    <mergeCell ref="B126:G126"/>
+    <mergeCell ref="B127:G127"/>
+    <mergeCell ref="B128:G128"/>
+    <mergeCell ref="B129:G129"/>
+    <mergeCell ref="B130:G130"/>
+    <mergeCell ref="B131:G131"/>
+    <mergeCell ref="B114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H2:H11"/>
     <mergeCell ref="A83:A99"/>
     <mergeCell ref="A100:A136"/>
     <mergeCell ref="B11:G11"/>
@@ -6038,160 +6192,6 @@
     <mergeCell ref="B69:G69"/>
     <mergeCell ref="B70:G70"/>
     <mergeCell ref="B42:G42"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H2:H11"/>
-    <mergeCell ref="H14:H27"/>
-    <mergeCell ref="A14:A27"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B155:G155"/>
-    <mergeCell ref="B156:G156"/>
-    <mergeCell ref="B157:G157"/>
-    <mergeCell ref="B158:G158"/>
-    <mergeCell ref="A42:A63"/>
-    <mergeCell ref="A64:A82"/>
-    <mergeCell ref="B133:G133"/>
-    <mergeCell ref="B134:G134"/>
-    <mergeCell ref="B135:G135"/>
-    <mergeCell ref="B136:G136"/>
-    <mergeCell ref="B126:G126"/>
-    <mergeCell ref="B127:G127"/>
-    <mergeCell ref="B128:G128"/>
-    <mergeCell ref="B129:G129"/>
-    <mergeCell ref="B130:G130"/>
-    <mergeCell ref="B131:G131"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="B159:G159"/>
-    <mergeCell ref="H154:H159"/>
-    <mergeCell ref="H126:H131"/>
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="B137:G137"/>
-    <mergeCell ref="B138:G138"/>
-    <mergeCell ref="H137:H153"/>
-    <mergeCell ref="B139:G139"/>
-    <mergeCell ref="B140:G140"/>
-    <mergeCell ref="B141:G141"/>
-    <mergeCell ref="B142:G142"/>
-    <mergeCell ref="B143:G143"/>
-    <mergeCell ref="B144:G144"/>
-    <mergeCell ref="B145:G145"/>
-    <mergeCell ref="B146:G146"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="B148:G148"/>
-    <mergeCell ref="B149:G149"/>
-    <mergeCell ref="B150:G150"/>
-    <mergeCell ref="B151:G151"/>
-    <mergeCell ref="B152:G152"/>
-    <mergeCell ref="B153:G153"/>
-    <mergeCell ref="B154:G154"/>
-    <mergeCell ref="B132:G132"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B89:G89"/>
-    <mergeCell ref="B90:G90"/>
-    <mergeCell ref="H89:H99"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="H57:H63"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B91:G91"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H42:H56"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="H76:H82"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="B79:G79"/>
-    <mergeCell ref="B80:G80"/>
-    <mergeCell ref="B82:G82"/>
-    <mergeCell ref="H64:H75"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B68:G68"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="H83:H88"/>
-    <mergeCell ref="B110:G110"/>
-    <mergeCell ref="B111:G111"/>
-    <mergeCell ref="B112:G112"/>
-    <mergeCell ref="B95:G95"/>
-    <mergeCell ref="B96:G96"/>
-    <mergeCell ref="B97:G97"/>
-    <mergeCell ref="B98:G98"/>
-    <mergeCell ref="B113:G113"/>
-    <mergeCell ref="B92:G92"/>
-    <mergeCell ref="B93:G93"/>
-    <mergeCell ref="B94:G94"/>
-    <mergeCell ref="B105:G105"/>
-    <mergeCell ref="B106:G106"/>
-    <mergeCell ref="B107:G107"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="A28:A41"/>
-    <mergeCell ref="H28:H41"/>
-    <mergeCell ref="A137:A159"/>
-    <mergeCell ref="A160:H160"/>
-    <mergeCell ref="H119:H125"/>
-    <mergeCell ref="B120:G120"/>
-    <mergeCell ref="B121:G121"/>
-    <mergeCell ref="B122:G122"/>
-    <mergeCell ref="B123:G123"/>
-    <mergeCell ref="B124:G124"/>
-    <mergeCell ref="B125:G125"/>
-    <mergeCell ref="B100:G100"/>
-    <mergeCell ref="H100:H118"/>
-    <mergeCell ref="B101:G101"/>
-    <mergeCell ref="B102:G102"/>
-    <mergeCell ref="B103:G103"/>
-    <mergeCell ref="B83:G83"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="B85:G85"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="B104:G104"/>
-    <mergeCell ref="B87:G87"/>
-    <mergeCell ref="B88:G88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Java Full Stack_ToC.xlsx
+++ b/Java Full Stack_ToC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\harman_training\Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB58E9D0-52BD-4BAD-BD4F-453E685A564E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E80A9FF-6DD3-47ED-98A5-7949E0D8992F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3528" yWindow="1584" windowWidth="19512" windowHeight="10920" activeTab="3" xr2:uid="{650FC967-2F93-46CA-B378-157C068E930D}"/>
   </bookViews>
@@ -1688,7 +1688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1715,14 +1715,20 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1730,17 +1736,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1751,14 +1757,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1769,8 +1769,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1781,53 +1829,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2152,21 +2155,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="2:5">
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="8" t="s">
         <v>165</v>
       </c>
@@ -2175,10 +2178,10 @@
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="7" t="s">
         <v>177</v>
       </c>
@@ -2187,10 +2190,10 @@
       <c r="B4" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="7" t="s">
         <v>167</v>
       </c>
@@ -2199,10 +2202,10 @@
       <c r="B5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="7" t="s">
         <v>172</v>
       </c>
@@ -2211,65 +2214,65 @@
       <c r="B6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="7" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="13" t="s">
@@ -2278,12 +2281,12 @@
       <c r="C19" s="13"/>
     </row>
     <row r="20" spans="2:5" ht="36" customHeight="1">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="13" t="s">
@@ -2322,6 +2325,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:D10"/>
@@ -2329,12 +2338,6 @@
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2349,15 +2352,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -2366,883 +2369,956 @@
       <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="25" t="s">
         <v>333</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="25"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="20" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="20" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="20" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="20" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="20" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="20" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="26"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="20" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="26"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="20" t="s">
+      <c r="A13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="26"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="20" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="26"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="20" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="26"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="20" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="26"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="20" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="26"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="20" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="26"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="20" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="26"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="20" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="26"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="20" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="26"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="20" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="26"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="20" t="s">
+      <c r="A23" s="23"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="26"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="20" t="s">
+      <c r="A24" s="23"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="26"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="20" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="26"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="20" t="s">
+      <c r="A26" s="23"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="26"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="20" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="26"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="20" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="26"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="20" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="26"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="20" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="20" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="20" t="s">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="18"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="20" t="s">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="20" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="20" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="20" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="20" t="s">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="20" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="20" t="s">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="20" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="20" t="s">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="20" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="20" t="s">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="20" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="20" t="s">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="20" t="s">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="18"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="18"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="22"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="20" t="s">
+      <c r="A51" s="21"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="20" t="s">
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="20" t="s">
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="20" t="s">
+      <c r="A55" s="21"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="20" t="s">
+      <c r="A56" s="21"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="20" t="s">
+      <c r="A57" s="21"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="20" t="s">
+      <c r="A58" s="21"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="20" t="s">
+      <c r="A59" s="21"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="22"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="20" t="s">
+      <c r="A60" s="21"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="20" t="s">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="20" t="s">
+      <c r="A62" s="21"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="20" t="s">
+      <c r="A63" s="21"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="20" t="s">
+      <c r="A64" s="21"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="20" t="s">
+      <c r="A65" s="21"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="22"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="20" t="s">
+      <c r="A67" s="21"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="20" t="s">
+      <c r="A68" s="21"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="22"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="20" t="s">
+      <c r="A69" s="21"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="22"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="20" t="s">
+      <c r="A70" s="21"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="22"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="20" t="s">
+      <c r="A71" s="21"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="22"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="20" t="s">
+      <c r="A72" s="21"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="22"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="20" t="s">
+      <c r="A73" s="21"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="22"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="20" t="s">
+      <c r="A74" s="21"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="22"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="20" t="s">
+      <c r="A75" s="21"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="22"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="20" t="s">
+      <c r="A76" s="21"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="22"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="20" t="s">
+      <c r="A77" s="21"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="22"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="20" t="s">
+      <c r="A78" s="21"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A11:A30"/>
+    <mergeCell ref="B11:B30"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="A52:A65"/>
+    <mergeCell ref="B52:B65"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="A31:A51"/>
+    <mergeCell ref="B31:B51"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C64:G64"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A79:G79"/>
     <mergeCell ref="C73:G73"/>
@@ -3259,79 +3335,6 @@
     <mergeCell ref="C68:G68"/>
     <mergeCell ref="C69:G69"/>
     <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="A52:A65"/>
-    <mergeCell ref="B52:B65"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="A31:A51"/>
-    <mergeCell ref="B31:B51"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A11:A30"/>
-    <mergeCell ref="B11:B30"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3347,15 +3350,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -3364,616 +3367,662 @@
       <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="22"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="20" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="22"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="20" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="22"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="20" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="22"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="20" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="22"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="20" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="22"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="20" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="22"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="20" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="22"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="20" t="s">
+      <c r="A11" s="21"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="22"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="20" t="s">
+      <c r="A12" s="21"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="22"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="20" t="s">
+      <c r="A13" s="21"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="22"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="20" t="s">
+      <c r="A14" s="21"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="22"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="20" t="s">
+      <c r="A15" s="21"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="22"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="20" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="22"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="20" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="22"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="20" t="s">
+      <c r="A18" s="21"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="22"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="20" t="s">
+      <c r="A19" s="21"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="22"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="20" t="s">
+      <c r="A20" s="21"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="22"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="20" t="s">
+      <c r="A22" s="21"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="22"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="20" t="s">
+      <c r="A23" s="21"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="22"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="20" t="s">
+      <c r="A24" s="21"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="22"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="20" t="s">
+      <c r="A25" s="21"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="22"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="20" t="s">
+      <c r="A26" s="21"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="22"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="20" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="22"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="20" t="s">
+      <c r="A28" s="21"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="22"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="20" t="s">
+      <c r="A29" s="21"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="22"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="20" t="s">
+      <c r="A30" s="21"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="22"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="20" t="s">
+      <c r="A31" s="21"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="22"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="20" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="22"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="20" t="s">
+      <c r="A33" s="21"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="22"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="20" t="s">
+      <c r="A34" s="21"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="22"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="20" t="s">
+      <c r="A35" s="21"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="21" t="s">
         <v>307</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="22"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="30"/>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="22"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="30"/>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="22"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="30"/>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="22"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="30"/>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="22"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="30"/>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="22"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="30"/>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="22"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="30"/>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="22"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="30"/>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="22"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="30"/>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="22"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="30"/>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="22"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="30"/>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="21" t="s">
         <v>321</v>
       </c>
       <c r="B48" s="30"/>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="22"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="30"/>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
       <c r="H49" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="22"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="30"/>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="22"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="30"/>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="22"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="30"/>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="22"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="30"/>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="22"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="31"/>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A3:A20"/>
+    <mergeCell ref="B3:B20"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="B21:B35"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="A36:A47"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C54:G54"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="C45:G45"/>
@@ -3990,52 +4039,6 @@
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="C29:G29"/>
-    <mergeCell ref="A36:A47"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="B21:B35"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A3:A20"/>
-    <mergeCell ref="B3:B20"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4054,14 +4057,14 @@
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4070,159 +4073,159 @@
       <c r="A2" s="29">
         <v>10</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="22" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="30"/>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="22"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="30"/>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="22"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="30"/>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="21"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="30"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="30"/>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="22"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="30"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="22"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="30"/>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="22"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="30"/>
       <c r="B10" t="s">
         <v>338</v>
       </c>
-      <c r="H10" s="22"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="30"/>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="22"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:8" ht="14.55" customHeight="1">
       <c r="A12" s="30"/>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="41" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="46" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="31"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="42"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="48"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="29">
         <v>11</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="29" t="s">
         <v>140</v>
       </c>
@@ -4241,190 +4244,190 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="30"/>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="30"/>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="30"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="30"/>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="30"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="30"/>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="30"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="30"/>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="30"/>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
       <c r="H21" s="30"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="30"/>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="30"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="30"/>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="30"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="30"/>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
       <c r="H24" s="30"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="30"/>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
       <c r="H25" s="30"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="30"/>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="31"/>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="43">
+      <c r="A28" s="36">
         <v>12</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="43" t="s">
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="44"/>
-      <c r="B29" s="36" t="s">
+      <c r="A29" s="37"/>
+      <c r="B29" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="44"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="37"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="44"/>
-      <c r="B30" s="36" t="s">
+      <c r="A30" s="37"/>
+      <c r="B30" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="44"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="37"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="44"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="4" t="s">
         <v>40</v>
       </c>
@@ -4433,70 +4436,70 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="44"/>
+      <c r="H31" s="37"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="44"/>
-      <c r="B32" s="36" t="s">
+      <c r="A32" s="37"/>
+      <c r="B32" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="44"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="37"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="44"/>
-      <c r="B33" s="36" t="s">
+      <c r="A33" s="37"/>
+      <c r="B33" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="44"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="37"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="44"/>
-      <c r="B34" s="36" t="s">
+      <c r="A34" s="37"/>
+      <c r="B34" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="44"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="37"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="44"/>
-      <c r="B35" s="36" t="s">
+      <c r="A35" s="37"/>
+      <c r="B35" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="44"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="37"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="44"/>
-      <c r="B36" s="36" t="s">
+      <c r="A36" s="37"/>
+      <c r="B36" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="44"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="37"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="44"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="10" t="s">
         <v>344</v>
       </c>
@@ -4505,755 +4508,755 @@
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="12"/>
-      <c r="H37" s="44"/>
+      <c r="H37" s="37"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="44"/>
-      <c r="B38" s="36" t="s">
+      <c r="A38" s="37"/>
+      <c r="B38" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="44"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="37"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="44"/>
-      <c r="B39" s="36" t="s">
+      <c r="A39" s="37"/>
+      <c r="B39" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="44"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="37"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="44"/>
-      <c r="B40" s="36" t="s">
+      <c r="A40" s="37"/>
+      <c r="B40" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="44"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="37"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="45"/>
-      <c r="B41" s="36" t="s">
+      <c r="A41" s="38"/>
+      <c r="B41" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="45"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="38"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="43">
+      <c r="A42" s="36">
         <v>13</v>
       </c>
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="43" t="s">
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="36" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="44"/>
-      <c r="B43" s="36" t="s">
+      <c r="A43" s="37"/>
+      <c r="B43" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="44"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="37"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="44"/>
-      <c r="B44" s="36" t="s">
+      <c r="A44" s="37"/>
+      <c r="B44" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="44"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="37"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="44"/>
-      <c r="B45" s="36" t="s">
+      <c r="A45" s="37"/>
+      <c r="B45" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="44"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="37"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="44"/>
-      <c r="B46" s="36" t="s">
+      <c r="A46" s="37"/>
+      <c r="B46" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="44"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="37"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="44"/>
-      <c r="B47" s="36" t="s">
+      <c r="A47" s="37"/>
+      <c r="B47" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="44"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="37"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="44"/>
-      <c r="B48" s="36" t="s">
+      <c r="A48" s="37"/>
+      <c r="B48" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="44"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="37"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="44"/>
-      <c r="B49" s="36" t="s">
+      <c r="A49" s="37"/>
+      <c r="B49" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="44"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="37"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="44"/>
-      <c r="B50" s="36" t="s">
+      <c r="A50" s="37"/>
+      <c r="B50" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="44"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="37"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="44"/>
-      <c r="B51" s="36" t="s">
+      <c r="A51" s="37"/>
+      <c r="B51" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="44"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="37"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="44"/>
-      <c r="B52" s="36" t="s">
+      <c r="A52" s="37"/>
+      <c r="B52" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="44"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="37"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="44"/>
-      <c r="B53" s="36" t="s">
+      <c r="A53" s="37"/>
+      <c r="B53" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="44"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="37"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="44"/>
-      <c r="B54" s="36" t="s">
+      <c r="A54" s="37"/>
+      <c r="B54" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="44"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="37"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="44"/>
-      <c r="B55" s="36" t="s">
+      <c r="A55" s="37"/>
+      <c r="B55" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="44"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="37"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="44"/>
-      <c r="B56" s="36" t="s">
+      <c r="A56" s="37"/>
+      <c r="B56" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="45"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="38"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="44"/>
-      <c r="B57" s="36" t="s">
+      <c r="A57" s="37"/>
+      <c r="B57" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="43" t="s">
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="36" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="44"/>
-      <c r="B58" s="36" t="s">
+      <c r="A58" s="37"/>
+      <c r="B58" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="44"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="37"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="44"/>
-      <c r="B59" s="36" t="s">
+      <c r="A59" s="37"/>
+      <c r="B59" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="44"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="37"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="44"/>
-      <c r="B60" s="36" t="s">
+      <c r="A60" s="37"/>
+      <c r="B60" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="44"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="37"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="44"/>
-      <c r="B61" s="36" t="s">
+      <c r="A61" s="37"/>
+      <c r="B61" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="44"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="37"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="44"/>
-      <c r="B62" s="36" t="s">
+      <c r="A62" s="37"/>
+      <c r="B62" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="44"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="37"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="44"/>
-      <c r="B63" s="36" t="s">
+      <c r="A63" s="37"/>
+      <c r="B63" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="45"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="38"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="44">
+      <c r="A64" s="52">
         <v>14</v>
       </c>
-      <c r="B64" s="36" t="s">
+      <c r="B64" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="48" t="s">
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="42" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="44"/>
-      <c r="B65" s="36" t="s">
+      <c r="A65" s="52"/>
+      <c r="B65" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="49"/>
+      <c r="C65" s="34"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="43"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="44"/>
-      <c r="B66" s="36" t="s">
+      <c r="A66" s="52"/>
+      <c r="B66" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="49"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="43"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="44"/>
-      <c r="B67" s="36" t="s">
+      <c r="A67" s="52"/>
+      <c r="B67" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="49"/>
+      <c r="C67" s="34"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="43"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="44"/>
-      <c r="B68" s="36" t="s">
+      <c r="A68" s="52"/>
+      <c r="B68" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="49"/>
+      <c r="C68" s="34"/>
+      <c r="D68" s="34"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="43"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="44"/>
-      <c r="B69" s="36" t="s">
+      <c r="A69" s="52"/>
+      <c r="B69" s="33" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="49"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="43"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="44"/>
-      <c r="B70" s="36" t="s">
+      <c r="A70" s="52"/>
+      <c r="B70" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="49"/>
+      <c r="C70" s="34"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="34"/>
+      <c r="F70" s="34"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="43"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="44"/>
-      <c r="B71" s="36" t="s">
+      <c r="A71" s="52"/>
+      <c r="B71" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="49"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="43"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="44"/>
-      <c r="B72" s="36" t="s">
+      <c r="A72" s="52"/>
+      <c r="B72" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="49"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="43"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="44"/>
-      <c r="B73" s="36" t="s">
+      <c r="A73" s="52"/>
+      <c r="B73" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="49"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="34"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="43"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="44"/>
-      <c r="B74" s="36" t="s">
+      <c r="A74" s="52"/>
+      <c r="B74" s="33" t="s">
         <v>340</v>
       </c>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="49"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="34"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="43"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="44"/>
-      <c r="B75" s="36" t="s">
+      <c r="A75" s="52"/>
+      <c r="B75" s="33" t="s">
         <v>342</v>
       </c>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="50"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="44"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="44"/>
-      <c r="B76" s="36" t="s">
+      <c r="A76" s="52"/>
+      <c r="B76" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="43" t="s">
+      <c r="C76" s="34"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="34"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="36" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="44"/>
-      <c r="B77" s="36" t="s">
+      <c r="A77" s="52"/>
+      <c r="B77" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="44"/>
+      <c r="C77" s="34"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="37"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="44"/>
-      <c r="B78" s="36" t="s">
+      <c r="A78" s="52"/>
+      <c r="B78" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="44"/>
+      <c r="C78" s="34"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="37"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="44"/>
-      <c r="B79" s="36" t="s">
+      <c r="A79" s="52"/>
+      <c r="B79" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="44"/>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="37"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="44"/>
-      <c r="B80" s="36" t="s">
+      <c r="A80" s="52"/>
+      <c r="B80" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="44"/>
+      <c r="C80" s="34"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="35"/>
+      <c r="H80" s="37"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="44"/>
+      <c r="A81" s="52"/>
       <c r="B81" t="s">
         <v>341</v>
       </c>
-      <c r="H81" s="44"/>
+      <c r="H81" s="37"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="45"/>
-      <c r="B82" s="36" t="s">
+      <c r="A82" s="52"/>
+      <c r="B82" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="45"/>
+      <c r="C82" s="34"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="38"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="33">
+      <c r="A83" s="49">
         <v>15</v>
       </c>
-      <c r="B83" s="51" t="s">
+      <c r="B83" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="51"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="22" t="s">
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="34"/>
-      <c r="B84" s="51" t="s">
+      <c r="A84" s="50"/>
+      <c r="B84" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="51"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="22"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="21"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="34"/>
-      <c r="B85" s="51" t="s">
+      <c r="A85" s="50"/>
+      <c r="B85" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="C85" s="51"/>
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="51"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="22"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="21"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="34"/>
-      <c r="B86" s="51" t="s">
+      <c r="A86" s="50"/>
+      <c r="B86" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="22"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="21"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="34"/>
-      <c r="B87" s="51" t="s">
+      <c r="A87" s="50"/>
+      <c r="B87" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="22"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="21"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="34"/>
-      <c r="B88" s="51" t="s">
+      <c r="A88" s="50"/>
+      <c r="B88" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="22"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="21"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="34"/>
-      <c r="B89" s="36" t="s">
+      <c r="A89" s="50"/>
+      <c r="B89" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
-      <c r="G89" s="38"/>
-      <c r="H89" s="41" t="s">
+      <c r="C89" s="34"/>
+      <c r="D89" s="34"/>
+      <c r="E89" s="34"/>
+      <c r="F89" s="34"/>
+      <c r="G89" s="35"/>
+      <c r="H89" s="46" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="34"/>
-      <c r="B90" s="36" t="s">
+      <c r="A90" s="50"/>
+      <c r="B90" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="38"/>
+      <c r="C90" s="34"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="34"/>
+      <c r="F90" s="34"/>
+      <c r="G90" s="35"/>
       <c r="H90" s="47"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="34"/>
-      <c r="B91" s="36" t="s">
+      <c r="A91" s="50"/>
+      <c r="B91" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="38"/>
+      <c r="C91" s="34"/>
+      <c r="D91" s="34"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="34"/>
+      <c r="G91" s="35"/>
       <c r="H91" s="47"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="34"/>
-      <c r="B92" s="36" t="s">
+      <c r="A92" s="50"/>
+      <c r="B92" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="38"/>
+      <c r="C92" s="34"/>
+      <c r="D92" s="34"/>
+      <c r="E92" s="34"/>
+      <c r="F92" s="34"/>
+      <c r="G92" s="35"/>
       <c r="H92" s="47"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="34"/>
-      <c r="B93" s="36" t="s">
+      <c r="A93" s="50"/>
+      <c r="B93" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="37"/>
-      <c r="F93" s="37"/>
-      <c r="G93" s="38"/>
+      <c r="C93" s="34"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="34"/>
+      <c r="F93" s="34"/>
+      <c r="G93" s="35"/>
       <c r="H93" s="47"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="34"/>
-      <c r="B94" s="36" t="s">
+      <c r="A94" s="50"/>
+      <c r="B94" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C94" s="37"/>
-      <c r="D94" s="37"/>
-      <c r="E94" s="37"/>
-      <c r="F94" s="37"/>
-      <c r="G94" s="38"/>
+      <c r="C94" s="34"/>
+      <c r="D94" s="34"/>
+      <c r="E94" s="34"/>
+      <c r="F94" s="34"/>
+      <c r="G94" s="35"/>
       <c r="H94" s="47"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="34"/>
-      <c r="B95" s="36" t="s">
+      <c r="A95" s="50"/>
+      <c r="B95" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="37"/>
-      <c r="D95" s="37"/>
-      <c r="E95" s="37"/>
-      <c r="F95" s="37"/>
-      <c r="G95" s="38"/>
+      <c r="C95" s="34"/>
+      <c r="D95" s="34"/>
+      <c r="E95" s="34"/>
+      <c r="F95" s="34"/>
+      <c r="G95" s="35"/>
       <c r="H95" s="47"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="34"/>
-      <c r="B96" s="36" t="s">
+      <c r="A96" s="50"/>
+      <c r="B96" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="37"/>
-      <c r="D96" s="37"/>
-      <c r="E96" s="37"/>
-      <c r="F96" s="37"/>
-      <c r="G96" s="38"/>
+      <c r="C96" s="34"/>
+      <c r="D96" s="34"/>
+      <c r="E96" s="34"/>
+      <c r="F96" s="34"/>
+      <c r="G96" s="35"/>
       <c r="H96" s="47"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="34"/>
-      <c r="B97" s="36" t="s">
+      <c r="A97" s="50"/>
+      <c r="B97" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="37"/>
-      <c r="D97" s="37"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37"/>
-      <c r="G97" s="38"/>
+      <c r="C97" s="34"/>
+      <c r="D97" s="34"/>
+      <c r="E97" s="34"/>
+      <c r="F97" s="34"/>
+      <c r="G97" s="35"/>
       <c r="H97" s="47"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="34"/>
-      <c r="B98" s="36" t="s">
+      <c r="A98" s="50"/>
+      <c r="B98" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
-      <c r="G98" s="38"/>
+      <c r="C98" s="34"/>
+      <c r="D98" s="34"/>
+      <c r="E98" s="34"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="35"/>
       <c r="H98" s="47"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="34"/>
+      <c r="A99" s="50"/>
       <c r="B99" s="2" t="s">
         <v>100</v>
       </c>
@@ -5262,10 +5265,10 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-      <c r="H99" s="42"/>
+      <c r="H99" s="48"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="34">
+      <c r="A100" s="50">
         <v>16</v>
       </c>
       <c r="B100" s="39" t="s">
@@ -5276,12 +5279,12 @@
       <c r="E100" s="39"/>
       <c r="F100" s="39"/>
       <c r="G100" s="39"/>
-      <c r="H100" s="22" t="s">
+      <c r="H100" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="34"/>
+      <c r="A101" s="50"/>
       <c r="B101" s="39" t="s">
         <v>56</v>
       </c>
@@ -5290,10 +5293,10 @@
       <c r="E101" s="39"/>
       <c r="F101" s="39"/>
       <c r="G101" s="39"/>
-      <c r="H101" s="22"/>
+      <c r="H101" s="21"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="34"/>
+      <c r="A102" s="50"/>
       <c r="B102" s="39" t="s">
         <v>57</v>
       </c>
@@ -5302,10 +5305,10 @@
       <c r="E102" s="39"/>
       <c r="F102" s="39"/>
       <c r="G102" s="39"/>
-      <c r="H102" s="22"/>
+      <c r="H102" s="21"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="34"/>
+      <c r="A103" s="50"/>
       <c r="B103" s="39" t="s">
         <v>58</v>
       </c>
@@ -5314,10 +5317,10 @@
       <c r="E103" s="39"/>
       <c r="F103" s="39"/>
       <c r="G103" s="39"/>
-      <c r="H103" s="22"/>
+      <c r="H103" s="21"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="34"/>
+      <c r="A104" s="50"/>
       <c r="B104" s="39" t="s">
         <v>59</v>
       </c>
@@ -5326,10 +5329,10 @@
       <c r="E104" s="39"/>
       <c r="F104" s="39"/>
       <c r="G104" s="39"/>
-      <c r="H104" s="22"/>
+      <c r="H104" s="21"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="34"/>
+      <c r="A105" s="50"/>
       <c r="B105" s="39" t="s">
         <v>60</v>
       </c>
@@ -5338,10 +5341,10 @@
       <c r="E105" s="39"/>
       <c r="F105" s="39"/>
       <c r="G105" s="39"/>
-      <c r="H105" s="22"/>
+      <c r="H105" s="21"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="34"/>
+      <c r="A106" s="50"/>
       <c r="B106" s="39" t="s">
         <v>61</v>
       </c>
@@ -5350,10 +5353,10 @@
       <c r="E106" s="39"/>
       <c r="F106" s="39"/>
       <c r="G106" s="39"/>
-      <c r="H106" s="22"/>
+      <c r="H106" s="21"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="34"/>
+      <c r="A107" s="50"/>
       <c r="B107" s="39" t="s">
         <v>62</v>
       </c>
@@ -5362,10 +5365,10 @@
       <c r="E107" s="39"/>
       <c r="F107" s="39"/>
       <c r="G107" s="39"/>
-      <c r="H107" s="22"/>
+      <c r="H107" s="21"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="34"/>
+      <c r="A108" s="50"/>
       <c r="B108" s="39" t="s">
         <v>63</v>
       </c>
@@ -5374,10 +5377,10 @@
       <c r="E108" s="39"/>
       <c r="F108" s="39"/>
       <c r="G108" s="39"/>
-      <c r="H108" s="22"/>
+      <c r="H108" s="21"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="34"/>
+      <c r="A109" s="50"/>
       <c r="B109" s="39" t="s">
         <v>65</v>
       </c>
@@ -5386,10 +5389,10 @@
       <c r="E109" s="39"/>
       <c r="F109" s="39"/>
       <c r="G109" s="39"/>
-      <c r="H109" s="22"/>
+      <c r="H109" s="21"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="34"/>
+      <c r="A110" s="50"/>
       <c r="B110" s="39" t="s">
         <v>66</v>
       </c>
@@ -5398,10 +5401,10 @@
       <c r="E110" s="39"/>
       <c r="F110" s="39"/>
       <c r="G110" s="39"/>
-      <c r="H110" s="22"/>
+      <c r="H110" s="21"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="34"/>
+      <c r="A111" s="50"/>
       <c r="B111" s="39" t="s">
         <v>67</v>
       </c>
@@ -5410,10 +5413,10 @@
       <c r="E111" s="39"/>
       <c r="F111" s="39"/>
       <c r="G111" s="39"/>
-      <c r="H111" s="22"/>
+      <c r="H111" s="21"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="34"/>
+      <c r="A112" s="50"/>
       <c r="B112" s="39" t="s">
         <v>69</v>
       </c>
@@ -5422,22 +5425,22 @@
       <c r="E112" s="39"/>
       <c r="F112" s="39"/>
       <c r="G112" s="39"/>
-      <c r="H112" s="22"/>
+      <c r="H112" s="21"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="34"/>
-      <c r="B113" s="40" t="s">
+      <c r="A113" s="50"/>
+      <c r="B113" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="C113" s="40"/>
-      <c r="D113" s="40"/>
-      <c r="E113" s="40"/>
-      <c r="F113" s="40"/>
-      <c r="G113" s="40"/>
-      <c r="H113" s="22"/>
+      <c r="C113" s="41"/>
+      <c r="D113" s="41"/>
+      <c r="E113" s="41"/>
+      <c r="F113" s="41"/>
+      <c r="G113" s="41"/>
+      <c r="H113" s="21"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="34"/>
+      <c r="A114" s="50"/>
       <c r="B114" s="39" t="s">
         <v>68</v>
       </c>
@@ -5446,10 +5449,10 @@
       <c r="E114" s="39"/>
       <c r="F114" s="39"/>
       <c r="G114" s="39"/>
-      <c r="H114" s="22"/>
+      <c r="H114" s="21"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="34"/>
+      <c r="A115" s="50"/>
       <c r="B115" s="39" t="s">
         <v>71</v>
       </c>
@@ -5458,10 +5461,10 @@
       <c r="E115" s="39"/>
       <c r="F115" s="39"/>
       <c r="G115" s="39"/>
-      <c r="H115" s="22"/>
+      <c r="H115" s="21"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="34"/>
+      <c r="A116" s="50"/>
       <c r="B116" s="39" t="s">
         <v>72</v>
       </c>
@@ -5470,10 +5473,10 @@
       <c r="E116" s="39"/>
       <c r="F116" s="39"/>
       <c r="G116" s="39"/>
-      <c r="H116" s="22"/>
+      <c r="H116" s="21"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="34"/>
+      <c r="A117" s="50"/>
       <c r="B117" s="39" t="s">
         <v>73</v>
       </c>
@@ -5482,22 +5485,22 @@
       <c r="E117" s="39"/>
       <c r="F117" s="39"/>
       <c r="G117" s="39"/>
-      <c r="H117" s="22"/>
+      <c r="H117" s="21"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="34"/>
-      <c r="B118" s="40" t="s">
+      <c r="A118" s="50"/>
+      <c r="B118" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C118" s="40"/>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40"/>
+      <c r="C118" s="41"/>
+      <c r="D118" s="41"/>
+      <c r="E118" s="41"/>
+      <c r="F118" s="41"/>
+      <c r="G118" s="41"/>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="34"/>
+      <c r="A119" s="50"/>
       <c r="B119" s="39" t="s">
         <v>75</v>
       </c>
@@ -5506,12 +5509,12 @@
       <c r="E119" s="39"/>
       <c r="F119" s="39"/>
       <c r="G119" s="39"/>
-      <c r="H119" s="22" t="s">
+      <c r="H119" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="34"/>
+      <c r="A120" s="50"/>
       <c r="B120" s="39" t="s">
         <v>76</v>
       </c>
@@ -5520,10 +5523,10 @@
       <c r="E120" s="39"/>
       <c r="F120" s="39"/>
       <c r="G120" s="39"/>
-      <c r="H120" s="22"/>
+      <c r="H120" s="21"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="34"/>
+      <c r="A121" s="50"/>
       <c r="B121" s="39" t="s">
         <v>77</v>
       </c>
@@ -5532,10 +5535,10 @@
       <c r="E121" s="39"/>
       <c r="F121" s="39"/>
       <c r="G121" s="39"/>
-      <c r="H121" s="22"/>
+      <c r="H121" s="21"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="34"/>
+      <c r="A122" s="50"/>
       <c r="B122" s="39" t="s">
         <v>78</v>
       </c>
@@ -5544,10 +5547,10 @@
       <c r="E122" s="39"/>
       <c r="F122" s="39"/>
       <c r="G122" s="39"/>
-      <c r="H122" s="22"/>
+      <c r="H122" s="21"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="34"/>
+      <c r="A123" s="50"/>
       <c r="B123" s="39" t="s">
         <v>79</v>
       </c>
@@ -5556,10 +5559,10 @@
       <c r="E123" s="39"/>
       <c r="F123" s="39"/>
       <c r="G123" s="39"/>
-      <c r="H123" s="22"/>
+      <c r="H123" s="21"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="34"/>
+      <c r="A124" s="50"/>
       <c r="B124" s="39" t="s">
         <v>80</v>
       </c>
@@ -5568,10 +5571,10 @@
       <c r="E124" s="39"/>
       <c r="F124" s="39"/>
       <c r="G124" s="39"/>
-      <c r="H124" s="22"/>
+      <c r="H124" s="21"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="34"/>
+      <c r="A125" s="50"/>
       <c r="B125" s="39" t="s">
         <v>81</v>
       </c>
@@ -5580,440 +5583,594 @@
       <c r="E125" s="39"/>
       <c r="F125" s="39"/>
       <c r="G125" s="39"/>
-      <c r="H125" s="22"/>
+      <c r="H125" s="21"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="34"/>
-      <c r="B126" s="20" t="s">
+      <c r="A126" s="50"/>
+      <c r="B126" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C126" s="20"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="22" t="s">
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="16"/>
+      <c r="G126" s="16"/>
+      <c r="H126" s="21" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="34"/>
-      <c r="B127" s="20" t="s">
+      <c r="A127" s="50"/>
+      <c r="B127" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C127" s="20"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="20"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="22"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="16"/>
+      <c r="G127" s="16"/>
+      <c r="H127" s="21"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="34"/>
-      <c r="B128" s="20" t="s">
+      <c r="A128" s="50"/>
+      <c r="B128" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="22"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="16"/>
+      <c r="F128" s="16"/>
+      <c r="G128" s="16"/>
+      <c r="H128" s="21"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="34"/>
-      <c r="B129" s="20" t="s">
+      <c r="A129" s="50"/>
+      <c r="B129" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="22"/>
+      <c r="C129" s="16"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="16"/>
+      <c r="F129" s="16"/>
+      <c r="G129" s="16"/>
+      <c r="H129" s="21"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="34"/>
-      <c r="B130" s="20" t="s">
+      <c r="A130" s="50"/>
+      <c r="B130" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C130" s="20"/>
-      <c r="D130" s="20"/>
-      <c r="E130" s="20"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="22"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="16"/>
+      <c r="G130" s="16"/>
+      <c r="H130" s="21"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="34"/>
-      <c r="B131" s="20" t="s">
+      <c r="A131" s="50"/>
+      <c r="B131" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C131" s="20"/>
-      <c r="D131" s="20"/>
-      <c r="E131" s="20"/>
-      <c r="F131" s="20"/>
-      <c r="G131" s="20"/>
-      <c r="H131" s="22"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
+      <c r="F131" s="16"/>
+      <c r="G131" s="16"/>
+      <c r="H131" s="21"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="34"/>
-      <c r="B132" s="20" t="s">
+      <c r="A132" s="50"/>
+      <c r="B132" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C132" s="20"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="20"/>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="22" t="s">
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="16"/>
+      <c r="G132" s="16"/>
+      <c r="H132" s="21" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="34"/>
-      <c r="B133" s="20" t="s">
+      <c r="A133" s="50"/>
+      <c r="B133" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C133" s="20"/>
-      <c r="D133" s="20"/>
-      <c r="E133" s="20"/>
-      <c r="F133" s="20"/>
-      <c r="G133" s="20"/>
-      <c r="H133" s="22"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="16"/>
+      <c r="F133" s="16"/>
+      <c r="G133" s="16"/>
+      <c r="H133" s="21"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="34"/>
-      <c r="B134" s="20" t="s">
+      <c r="A134" s="50"/>
+      <c r="B134" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C134" s="20"/>
-      <c r="D134" s="20"/>
-      <c r="E134" s="20"/>
-      <c r="F134" s="20"/>
-      <c r="G134" s="20"/>
-      <c r="H134" s="22"/>
+      <c r="C134" s="16"/>
+      <c r="D134" s="16"/>
+      <c r="E134" s="16"/>
+      <c r="F134" s="16"/>
+      <c r="G134" s="16"/>
+      <c r="H134" s="21"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="34"/>
-      <c r="B135" s="20" t="s">
+      <c r="A135" s="50"/>
+      <c r="B135" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C135" s="20"/>
-      <c r="D135" s="20"/>
-      <c r="E135" s="20"/>
-      <c r="F135" s="20"/>
-      <c r="G135" s="20"/>
-      <c r="H135" s="22"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="16"/>
+      <c r="F135" s="16"/>
+      <c r="G135" s="16"/>
+      <c r="H135" s="21"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="35"/>
-      <c r="B136" s="20" t="s">
+      <c r="A136" s="51"/>
+      <c r="B136" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C136" s="20"/>
-      <c r="D136" s="20"/>
-      <c r="E136" s="20"/>
-      <c r="F136" s="20"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="22"/>
+      <c r="C136" s="16"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="16"/>
+      <c r="F136" s="16"/>
+      <c r="G136" s="16"/>
+      <c r="H136" s="21"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="29">
         <v>17</v>
       </c>
-      <c r="B137" s="20" t="s">
+      <c r="B137" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C137" s="20"/>
-      <c r="D137" s="20"/>
-      <c r="E137" s="20"/>
-      <c r="F137" s="20"/>
-      <c r="G137" s="20"/>
-      <c r="H137" s="28" t="s">
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
+      <c r="H137" s="32" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="30"/>
-      <c r="B138" s="20" t="s">
+      <c r="B138" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C138" s="20"/>
-      <c r="D138" s="20"/>
-      <c r="E138" s="20"/>
-      <c r="F138" s="20"/>
-      <c r="G138" s="20"/>
-      <c r="H138" s="28"/>
+      <c r="C138" s="16"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="16"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="16"/>
+      <c r="H138" s="32"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="30"/>
-      <c r="B139" s="20" t="s">
+      <c r="B139" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C139" s="20"/>
-      <c r="D139" s="20"/>
-      <c r="E139" s="20"/>
-      <c r="F139" s="20"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="28"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="16"/>
+      <c r="H139" s="32"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="30"/>
-      <c r="B140" s="20" t="s">
+      <c r="B140" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C140" s="20"/>
-      <c r="D140" s="20"/>
-      <c r="E140" s="20"/>
-      <c r="F140" s="20"/>
-      <c r="G140" s="20"/>
-      <c r="H140" s="28"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
+      <c r="H140" s="32"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="30"/>
-      <c r="B141" s="20" t="s">
+      <c r="B141" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C141" s="20"/>
-      <c r="D141" s="20"/>
-      <c r="E141" s="20"/>
-      <c r="F141" s="20"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="28"/>
+      <c r="C141" s="16"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="16"/>
+      <c r="F141" s="16"/>
+      <c r="G141" s="16"/>
+      <c r="H141" s="32"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="30"/>
-      <c r="B142" s="20" t="s">
+      <c r="B142" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C142" s="20"/>
-      <c r="D142" s="20"/>
-      <c r="E142" s="20"/>
-      <c r="F142" s="20"/>
-      <c r="G142" s="20"/>
-      <c r="H142" s="28"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="16"/>
+      <c r="G142" s="16"/>
+      <c r="H142" s="32"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="30"/>
-      <c r="B143" s="20" t="s">
+      <c r="B143" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C143" s="20"/>
-      <c r="D143" s="20"/>
-      <c r="E143" s="20"/>
-      <c r="F143" s="20"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="28"/>
+      <c r="C143" s="16"/>
+      <c r="D143" s="16"/>
+      <c r="E143" s="16"/>
+      <c r="F143" s="16"/>
+      <c r="G143" s="16"/>
+      <c r="H143" s="32"/>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="30"/>
-      <c r="B144" s="20" t="s">
+      <c r="B144" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C144" s="20"/>
-      <c r="D144" s="20"/>
-      <c r="E144" s="20"/>
-      <c r="F144" s="20"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="28"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="16"/>
+      <c r="E144" s="16"/>
+      <c r="F144" s="16"/>
+      <c r="G144" s="16"/>
+      <c r="H144" s="32"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="30"/>
-      <c r="B145" s="20" t="s">
+      <c r="B145" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C145" s="20"/>
-      <c r="D145" s="20"/>
-      <c r="E145" s="20"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="28"/>
+      <c r="C145" s="16"/>
+      <c r="D145" s="16"/>
+      <c r="E145" s="16"/>
+      <c r="F145" s="16"/>
+      <c r="G145" s="16"/>
+      <c r="H145" s="32"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="30"/>
-      <c r="B146" s="20" t="s">
+      <c r="B146" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C146" s="20"/>
-      <c r="D146" s="20"/>
-      <c r="E146" s="20"/>
-      <c r="F146" s="20"/>
-      <c r="G146" s="20"/>
-      <c r="H146" s="28"/>
+      <c r="C146" s="16"/>
+      <c r="D146" s="16"/>
+      <c r="E146" s="16"/>
+      <c r="F146" s="16"/>
+      <c r="G146" s="16"/>
+      <c r="H146" s="32"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="30"/>
-      <c r="B147" s="20" t="s">
+      <c r="B147" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C147" s="20"/>
-      <c r="D147" s="20"/>
-      <c r="E147" s="20"/>
-      <c r="F147" s="20"/>
-      <c r="G147" s="20"/>
-      <c r="H147" s="28"/>
+      <c r="C147" s="16"/>
+      <c r="D147" s="16"/>
+      <c r="E147" s="16"/>
+      <c r="F147" s="16"/>
+      <c r="G147" s="16"/>
+      <c r="H147" s="32"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="30"/>
-      <c r="B148" s="20" t="s">
+      <c r="B148" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C148" s="20"/>
-      <c r="D148" s="20"/>
-      <c r="E148" s="20"/>
-      <c r="F148" s="20"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="28"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="16"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
+      <c r="H148" s="32"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="30"/>
-      <c r="B149" s="20" t="s">
+      <c r="B149" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C149" s="20"/>
-      <c r="D149" s="20"/>
-      <c r="E149" s="20"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="20"/>
-      <c r="H149" s="28"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
+      <c r="H149" s="32"/>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="30"/>
-      <c r="B150" s="20" t="s">
+      <c r="B150" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C150" s="20"/>
-      <c r="D150" s="20"/>
-      <c r="E150" s="20"/>
-      <c r="F150" s="20"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="28"/>
+      <c r="C150" s="16"/>
+      <c r="D150" s="16"/>
+      <c r="E150" s="16"/>
+      <c r="F150" s="16"/>
+      <c r="G150" s="16"/>
+      <c r="H150" s="32"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="30"/>
-      <c r="B151" s="20" t="s">
+      <c r="B151" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C151" s="20"/>
-      <c r="D151" s="20"/>
-      <c r="E151" s="20"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="20"/>
-      <c r="H151" s="28"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="16"/>
+      <c r="E151" s="16"/>
+      <c r="F151" s="16"/>
+      <c r="G151" s="16"/>
+      <c r="H151" s="32"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="30"/>
-      <c r="B152" s="20" t="s">
+      <c r="B152" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C152" s="20"/>
-      <c r="D152" s="20"/>
-      <c r="E152" s="20"/>
-      <c r="F152" s="20"/>
-      <c r="G152" s="20"/>
-      <c r="H152" s="28"/>
+      <c r="C152" s="16"/>
+      <c r="D152" s="16"/>
+      <c r="E152" s="16"/>
+      <c r="F152" s="16"/>
+      <c r="G152" s="16"/>
+      <c r="H152" s="32"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="30"/>
-      <c r="B153" s="20" t="s">
+      <c r="B153" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C153" s="20"/>
-      <c r="D153" s="20"/>
-      <c r="E153" s="20"/>
-      <c r="F153" s="20"/>
-      <c r="G153" s="20"/>
-      <c r="H153" s="41"/>
+      <c r="C153" s="16"/>
+      <c r="D153" s="16"/>
+      <c r="E153" s="16"/>
+      <c r="F153" s="16"/>
+      <c r="G153" s="16"/>
+      <c r="H153" s="46"/>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="30"/>
-      <c r="B154" s="20" t="s">
+      <c r="B154" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C154" s="20"/>
-      <c r="D154" s="20"/>
-      <c r="E154" s="20"/>
-      <c r="F154" s="20"/>
-      <c r="G154" s="20"/>
-      <c r="H154" s="28" t="s">
+      <c r="C154" s="16"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="16"/>
+      <c r="F154" s="16"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="32" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="30"/>
-      <c r="B155" s="20" t="s">
+      <c r="B155" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C155" s="20"/>
-      <c r="D155" s="20"/>
-      <c r="E155" s="20"/>
-      <c r="F155" s="20"/>
-      <c r="G155" s="20"/>
-      <c r="H155" s="28"/>
+      <c r="C155" s="16"/>
+      <c r="D155" s="16"/>
+      <c r="E155" s="16"/>
+      <c r="F155" s="16"/>
+      <c r="G155" s="16"/>
+      <c r="H155" s="32"/>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="30"/>
-      <c r="B156" s="20" t="s">
+      <c r="B156" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C156" s="20"/>
-      <c r="D156" s="20"/>
-      <c r="E156" s="20"/>
-      <c r="F156" s="20"/>
-      <c r="G156" s="20"/>
-      <c r="H156" s="28"/>
+      <c r="C156" s="16"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="16"/>
+      <c r="F156" s="16"/>
+      <c r="G156" s="16"/>
+      <c r="H156" s="32"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="30"/>
-      <c r="B157" s="20" t="s">
+      <c r="B157" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C157" s="20"/>
-      <c r="D157" s="20"/>
-      <c r="E157" s="20"/>
-      <c r="F157" s="20"/>
-      <c r="G157" s="20"/>
-      <c r="H157" s="28"/>
+      <c r="C157" s="16"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="16"/>
+      <c r="F157" s="16"/>
+      <c r="G157" s="16"/>
+      <c r="H157" s="32"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="30"/>
-      <c r="B158" s="20" t="s">
+      <c r="B158" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C158" s="20"/>
-      <c r="D158" s="20"/>
-      <c r="E158" s="20"/>
-      <c r="F158" s="20"/>
-      <c r="G158" s="20"/>
-      <c r="H158" s="28"/>
+      <c r="C158" s="16"/>
+      <c r="D158" s="16"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="16"/>
+      <c r="G158" s="16"/>
+      <c r="H158" s="32"/>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="31"/>
-      <c r="B159" s="20" t="s">
+      <c r="B159" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C159" s="20"/>
-      <c r="D159" s="20"/>
-      <c r="E159" s="20"/>
-      <c r="F159" s="20"/>
-      <c r="G159" s="20"/>
-      <c r="H159" s="28"/>
+      <c r="C159" s="16"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="16"/>
+      <c r="F159" s="16"/>
+      <c r="G159" s="16"/>
+      <c r="H159" s="32"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B160" s="16"/>
-      <c r="C160" s="16"/>
-      <c r="D160" s="16"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="16"/>
-      <c r="G160" s="16"/>
-      <c r="H160" s="16"/>
+      <c r="B160" s="15"/>
+      <c r="C160" s="15"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="15"/>
+      <c r="F160" s="15"/>
+      <c r="G160" s="15"/>
+      <c r="H160" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="A83:A99"/>
+    <mergeCell ref="A100:A136"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B117:G117"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="B119:G119"/>
+    <mergeCell ref="B108:G108"/>
+    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H2:H11"/>
+    <mergeCell ref="H14:H27"/>
+    <mergeCell ref="A14:A27"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B155:G155"/>
+    <mergeCell ref="B156:G156"/>
+    <mergeCell ref="B157:G157"/>
+    <mergeCell ref="B158:G158"/>
+    <mergeCell ref="A42:A63"/>
+    <mergeCell ref="A64:A82"/>
+    <mergeCell ref="B133:G133"/>
+    <mergeCell ref="B134:G134"/>
+    <mergeCell ref="B135:G135"/>
+    <mergeCell ref="B136:G136"/>
+    <mergeCell ref="B126:G126"/>
+    <mergeCell ref="B127:G127"/>
+    <mergeCell ref="B128:G128"/>
+    <mergeCell ref="B129:G129"/>
+    <mergeCell ref="B130:G130"/>
+    <mergeCell ref="B131:G131"/>
+    <mergeCell ref="B114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="B159:G159"/>
+    <mergeCell ref="H154:H159"/>
+    <mergeCell ref="H126:H131"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="B137:G137"/>
+    <mergeCell ref="B138:G138"/>
+    <mergeCell ref="H137:H153"/>
+    <mergeCell ref="B139:G139"/>
+    <mergeCell ref="B140:G140"/>
+    <mergeCell ref="B141:G141"/>
+    <mergeCell ref="B142:G142"/>
+    <mergeCell ref="B143:G143"/>
+    <mergeCell ref="B144:G144"/>
+    <mergeCell ref="B145:G145"/>
+    <mergeCell ref="B146:G146"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="B148:G148"/>
+    <mergeCell ref="B149:G149"/>
+    <mergeCell ref="B150:G150"/>
+    <mergeCell ref="B151:G151"/>
+    <mergeCell ref="B152:G152"/>
+    <mergeCell ref="B153:G153"/>
+    <mergeCell ref="B154:G154"/>
+    <mergeCell ref="B132:G132"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B89:G89"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="H89:H99"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="H57:H63"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B91:G91"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H42:H56"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="H76:H82"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="B79:G79"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="B82:G82"/>
+    <mergeCell ref="H64:H75"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="H83:H88"/>
+    <mergeCell ref="B110:G110"/>
+    <mergeCell ref="B111:G111"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B97:G97"/>
+    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B113:G113"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B93:G93"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B105:G105"/>
+    <mergeCell ref="B106:G106"/>
+    <mergeCell ref="B107:G107"/>
     <mergeCell ref="B28:G28"/>
     <mergeCell ref="A28:A41"/>
     <mergeCell ref="H28:H41"/>
@@ -6038,160 +6195,6 @@
     <mergeCell ref="B104:G104"/>
     <mergeCell ref="B87:G87"/>
     <mergeCell ref="B88:G88"/>
-    <mergeCell ref="H83:H88"/>
-    <mergeCell ref="B110:G110"/>
-    <mergeCell ref="B111:G111"/>
-    <mergeCell ref="B112:G112"/>
-    <mergeCell ref="B95:G95"/>
-    <mergeCell ref="B96:G96"/>
-    <mergeCell ref="B97:G97"/>
-    <mergeCell ref="B98:G98"/>
-    <mergeCell ref="B113:G113"/>
-    <mergeCell ref="B92:G92"/>
-    <mergeCell ref="B93:G93"/>
-    <mergeCell ref="B94:G94"/>
-    <mergeCell ref="B105:G105"/>
-    <mergeCell ref="B106:G106"/>
-    <mergeCell ref="B107:G107"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="H76:H82"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="B79:G79"/>
-    <mergeCell ref="B80:G80"/>
-    <mergeCell ref="B82:G82"/>
-    <mergeCell ref="H64:H75"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B68:G68"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H42:H56"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B89:G89"/>
-    <mergeCell ref="B90:G90"/>
-    <mergeCell ref="H89:H99"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="H57:H63"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B91:G91"/>
-    <mergeCell ref="B159:G159"/>
-    <mergeCell ref="H154:H159"/>
-    <mergeCell ref="H126:H131"/>
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="B137:G137"/>
-    <mergeCell ref="B138:G138"/>
-    <mergeCell ref="H137:H153"/>
-    <mergeCell ref="B139:G139"/>
-    <mergeCell ref="B140:G140"/>
-    <mergeCell ref="B141:G141"/>
-    <mergeCell ref="B142:G142"/>
-    <mergeCell ref="B143:G143"/>
-    <mergeCell ref="B144:G144"/>
-    <mergeCell ref="B145:G145"/>
-    <mergeCell ref="B146:G146"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="B148:G148"/>
-    <mergeCell ref="B149:G149"/>
-    <mergeCell ref="B150:G150"/>
-    <mergeCell ref="B151:G151"/>
-    <mergeCell ref="B152:G152"/>
-    <mergeCell ref="B153:G153"/>
-    <mergeCell ref="B154:G154"/>
-    <mergeCell ref="B132:G132"/>
-    <mergeCell ref="H14:H27"/>
-    <mergeCell ref="A14:A27"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B155:G155"/>
-    <mergeCell ref="B156:G156"/>
-    <mergeCell ref="B157:G157"/>
-    <mergeCell ref="B158:G158"/>
-    <mergeCell ref="A42:A63"/>
-    <mergeCell ref="A64:A82"/>
-    <mergeCell ref="B133:G133"/>
-    <mergeCell ref="B134:G134"/>
-    <mergeCell ref="B135:G135"/>
-    <mergeCell ref="B136:G136"/>
-    <mergeCell ref="B126:G126"/>
-    <mergeCell ref="B127:G127"/>
-    <mergeCell ref="B128:G128"/>
-    <mergeCell ref="B129:G129"/>
-    <mergeCell ref="B130:G130"/>
-    <mergeCell ref="B131:G131"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H2:H11"/>
-    <mergeCell ref="A83:A99"/>
-    <mergeCell ref="A100:A136"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B117:G117"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="B119:G119"/>
-    <mergeCell ref="B108:G108"/>
-    <mergeCell ref="B109:G109"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B42:G42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
